--- a/engine/amoc_study/AMOC_Valuation_Model_06082026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_06082026_public.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamental Valuation" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EV Bridge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Legs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Lines" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative &amp; Normalized" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="9" state="visible" r:id="rId9"/>
@@ -36,12 +36,12 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
     <numFmt numFmtId="171" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,10 +77,6 @@
     <font>
       <b val="1"/>
       <color rgb="00008000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000000FF"/>
     </font>
     <font>
       <sz val="10"/>
@@ -125,24 +121,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,31 +147,35 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -754,21 +754,21 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>spreadsheet grid. IT IS NOT USED HERE. AMOC's revenue build has two product legs, each a volume times a</t>
+          <t>spreadsheet grid. IT IS NOT USED HERE. AMOC's revenue build is three product lines, each a volume times a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>dollar price times an exchange rate, and that fits on a sheet. See Product Legs: every cell of the revenue</t>
+          <t>dollar price times an exchange rate, and that fits on a sheet. See Product Lines: every cell of the</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>build is live, including the base-year residual that prices the fuel leg.</t>
+          <t>revenue build is live.</t>
         </is>
       </c>
     </row>
@@ -778,124 +778,132 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>HOW REVENUE IS BUILT. Not as one growth rate. Volume splits into a specialty leg — base oils, fully</t>
+          <t>HOW REVENUE IS BUILT — AND WHAT CHANGED. Not as one growth rate, and no longer from a calibrated price.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>refined paraffin wax, transformer and special oils — and a fuel and by-product leg. Each is priced in US</t>
+          <t>The company reports a product table — tonnes and value for base oils, for paraffin wax, and in total —</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>dollars a tonne and translated at an explicit exchange-rate path, because both legs price off dollar</t>
+          <t>and every realisation in this model is DERIVED from it by division. Base oils, paraffin wax and the fuel</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>product benchmarks even when sold domestically.</t>
+          <t>and by-product slate are carried as three separate lines, each a volume times a dollar price a tonne</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>times an explicit exchange-rate path, because all three price off dollar product benchmarks even when</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>THREE THINGS TO KNOW BEFORE READING THE NUMBERS.</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>sold domestically. An earlier edition of this workbook had TWO legs, a specialty price that was a free</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>input and a fuel price that was the RESIDUAL of base-year revenue — and then offered the implied fuel</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · THE FINANCIAL YEAR CHANGED. The exchange approved a move from a 30 June year-end to 31 December.</t>
+          <t>realisation as evidence that the split was real. A residual cannot corroborate the construction that</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    July-December 2025 is a six-month transition period. History is shown on the reported June years; the</t>
+          <t>produced it. Both are gone: NO PRICE IN THIS MODEL IS CALIBRATED AND NONE IS A RESIDUAL.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    calendar-2025 base year is CONSTRUCTED from two disclosed halves, with no estimated component in</t>
-        </is>
-      </c>
+      <c r="A46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    either; and the forecast runs on calendar years. See Product Legs for the construction.</t>
+          <t>THE GROSS MARGIN IS AN OUTPUT, NOT AN ASSUMPTION. The two line margins are SOLVED from one disclosed</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>blend and one judgment parameter — the ratio of the specialty spread to the fuel spread — and are then</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · THE COMPANY IS NET CASH. Gross debt is a rounding error against the cash pile. That has two</t>
+          <t>held CONSTANT for the whole forecast. Every forecast year's blended margin is those constants re-weighted</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    consequences the workbook makes visible: net debt enters the bridge as a NEGATIVE, so the cash is</t>
+          <t>by that year's revenue mix, so the margin widens only to the extent the mix shifts. Change a volume</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    added; and the weighting on net debt RAISES the discount rate above the cost of equity rather than</t>
+          <t>growth rate on Product Lines and watch the blended margin move with no margin input touched.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    lowering it, because the observed equity cost is diluted by cash that carries almost no risk.</t>
-        </is>
-      </c>
+      <c r="A52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>THE TWO ROUTES TO THE BASE YEAR DISAGREE, AND THE GAP IS ON THE FACE OF THE SHEET. Rolling the reported</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · THE HISTORICAL BALANCE SHEETS ARE A RECONSTRUCTION. Only four balance-sheet lines are disclosed, at</t>
+          <t>product table forward does not reproduce the base year built from two filed halves; a single</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    one date. The rest is built from days drivers and a roll-back through disclosed profit and dividends,</t>
+          <t>reconciliation factor scales every line onto the filed figure. It is shown, not buried. The filed halves</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    and is labelled as such on the sheet.</t>
+          <t>govern the LEVEL; the product table governs only the MIX and the per-tonne economics.</t>
         </is>
       </c>
     </row>
@@ -903,159 +911,286 @@
       <c r="A57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>NO RATING AND NO PRICE TARGET. A fair-value range and a distribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>THREE THINGS TO KNOW BEFORE READING THE NUMBERS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr"/>
+    </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>HEADLINE FIGURES — ALL LIVE LINKS</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="I60" s="6" t="n"/>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · THE FINANCIAL YEAR CHANGED. The exchange approved a move from a 30 June year-end to 31 December.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Spot price (EGP)</t>
-        </is>
-      </c>
-      <c r="C61" s="8">
-        <f>Assumptions!$C$5</f>
-        <v/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    July-December 2025 is a six-month transition period. History is shown on the reported June years; the</t>
+        </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Weighted central fair value (EGP)</t>
-        </is>
-      </c>
-      <c r="C62" s="8">
-        <f>Summary!C10</f>
-        <v/>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    calendar-2025 base year is CONSTRUCTED from two disclosed halves, with no estimated component in</t>
+        </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Implied against spot</t>
-        </is>
-      </c>
-      <c r="C63" s="9">
-        <f>Summary!C12</f>
-        <v/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    either; and the forecast runs on calendar years. See Product Lines for the construction.</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Discounted cash flow lens (EGP)</t>
-        </is>
-      </c>
-      <c r="C64" s="8">
-        <f>'EV Bridge'!$B$12</f>
-        <v/>
-      </c>
+      <c r="A64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>Terminal value as a share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C65" s="9">
-        <f>DCF!$B$35</f>
-        <v/>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · THE COMPANY IS NET CASH. Gross debt is a rounding error against the cash pile. That has two</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Weighted cost of capital — explicit</t>
-        </is>
-      </c>
-      <c r="C66" s="10">
-        <f>DCF!$B$54</f>
-        <v/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    consequences the workbook makes visible: net debt enters the bridge as a NEGATIVE, so the cash is</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Weighted cost of capital — terminal</t>
-        </is>
-      </c>
-      <c r="C67" s="10">
-        <f>DCF!$B$62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68"/>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    added; and the weighting on net debt RAISES the discount rate above the cost of equity rather than</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    lowering it, because the observed equity cost is diluted by cash that carries almost no risk.</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>TWO GATES RUN ON THIS DELIVERED FILE, NOT ON THE SCRIPT THAT WROTE IT.</t>
-        </is>
-      </c>
+      <c r="A69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Cell-level agreement. The builder records the model's own value for every formula cell as it</t>
+          <t xml:space="preserve">  · THE HISTORICAL BALANCE SHEETS ARE A RECONSTRUCTION. Only four balance-sheet lines are disclosed, at</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    writes it. An independent evaluator then re-evaluates the workbook and asserts that every formula</t>
+          <t xml:space="preserve">    one date. The rest is built from days drivers and a roll-back through disclosed profit and dividends,</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cell reproduces that value and that none is left unchecked. A formula that computes the right thing</t>
+          <t xml:space="preserve">    and is labelled as such on the sheet.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    the wrong way, or points one row off, fails here rather than shipping a different number.</t>
-        </is>
-      </c>
+      <c r="A73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>NO RATING AND NO PRICE TARGET. A fair-value range and a distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>HEADLINE FIGURES — ALL LIVE LINKS</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Spot price (EGP)</t>
+        </is>
+      </c>
+      <c r="C77" s="8">
+        <f>Assumptions!$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Weighted central fair value (EGP)</t>
+        </is>
+      </c>
+      <c r="C78" s="8">
+        <f>Summary!C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Implied against spot</t>
+        </is>
+      </c>
+      <c r="C79" s="9">
+        <f>Summary!C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Discounted cash flow lens (EGP)</t>
+        </is>
+      </c>
+      <c r="C80" s="8">
+        <f>'EV Bridge'!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Terminal value as a share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C81" s="9">
+        <f>DCF!$B$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Weighted cost of capital — explicit</t>
+        </is>
+      </c>
+      <c r="C82" s="10">
+        <f>DCF!$B$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Weighted cost of capital — terminal</t>
+        </is>
+      </c>
+      <c r="C83" s="10">
+        <f>DCF!$B$62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>TWO GATES RUN ON THIS DELIVERED FILE, NOT ON THE SCRIPT THAT WROTE IT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Cell-level agreement. The builder records the model's own value for every formula cell as it</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    writes it. An independent evaluator then re-evaluates the workbook and asserts that every formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    cell reproduces that value and that none is left unchecked. A formula that computes the right thing</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the wrong way, or points one row off, fails here rather than shipping a different number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  · Driver propagation. Every input is perturbed in place, the whole workbook is re-evaluated, and the</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    headline is required to move in the asserted direction, with a dead-input sweep over the rest.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    The live-driver claim above is only made because this test passes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>THE CENSUS. The exact split of formula cells against pasted numeric cells is counted on the delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>file and printed by the build, then restated in the study's quality-control gate. Text labels and</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>headings are counted separately and form no part of the claim in either direction. Every pasted numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>cell falls into one of the two classes named above; there is no third bucket and no residual category.</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1421,7 @@
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>Assumptions!$C$35-Assumptions!$C$37-E10-E11-Assumptions!$C$42</f>
+        <f>Assumptions!$C$43-Assumptions!$C$45-E10-E11-Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="F9" s="18">
@@ -1317,39 +1452,39 @@
         </is>
       </c>
       <c r="B10" s="17">
-        <f>B6*Assumptions!$C$40/365</f>
+        <f>B6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="C10" s="17">
-        <f>C6*Assumptions!$C$40/365</f>
+        <f>C6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="D10" s="17">
-        <f>D6*Assumptions!$C$40/365</f>
+        <f>D6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="E10" s="17">
-        <f>E6*Assumptions!$C$40/365</f>
+        <f>E6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>F6*Assumptions!$C$40/365</f>
+        <f>F6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="G10" s="17">
-        <f>G6*Assumptions!$C$40/365</f>
+        <f>G6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>H6*Assumptions!$C$40/365</f>
+        <f>H6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>I6*Assumptions!$C$40/365</f>
+        <f>I6*Assumptions!$C$48/365</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>J6*Assumptions!$C$40/365</f>
+        <f>J6*Assumptions!$C$48/365</f>
         <v/>
       </c>
     </row>
@@ -1360,39 +1495,39 @@
         </is>
       </c>
       <c r="B11" s="17">
-        <f>B5*Assumptions!$C$39/365</f>
+        <f>B5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>C5*Assumptions!$C$39/365</f>
+        <f>C5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>D5*Assumptions!$C$39/365</f>
+        <f>D5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>E5*Assumptions!$C$39/365</f>
+        <f>E5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>F5*Assumptions!$C$39/365</f>
+        <f>F5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>G5*Assumptions!$C$39/365</f>
+        <f>G5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>H5*Assumptions!$C$39/365</f>
+        <f>H5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>I5*Assumptions!$C$39/365</f>
+        <f>I5*Assumptions!$C$47/365</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>J5*Assumptions!$C$39/365</f>
+        <f>J5*Assumptions!$C$47/365</f>
         <v/>
       </c>
     </row>
@@ -1403,39 +1538,39 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="C12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="D12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="E12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="F12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="G12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="I12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="J12" s="18">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
     </row>
@@ -1446,39 +1581,39 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>B20+B21+B17+B19+Assumptions!$C$38-B9-B10-B11-Assumptions!$C$42</f>
+        <f>B20+B21+B17+B19+Assumptions!$C$46-B9-B10-B11-Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>C20+C21+C17+C19+Assumptions!$C$38-C9-C10-C11-Assumptions!$C$42</f>
+        <f>C20+C21+C17+C19+Assumptions!$C$46-C9-C10-C11-Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>D20+D21+D17+D19+Assumptions!$C$38-D9-D10-D11-Assumptions!$C$42</f>
+        <f>D20+D21+D17+D19+Assumptions!$C$46-D9-D10-D11-Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>Assumptions!$C$37</f>
+        <f>Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>Assumptions!$C$38-'Cash Flow'!B$22</f>
+        <f>Assumptions!$C$46-'Cash Flow'!B$22</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>Assumptions!$C$38-'Cash Flow'!C$22</f>
+        <f>Assumptions!$C$46-'Cash Flow'!C$22</f>
         <v/>
       </c>
       <c r="H13" s="17">
-        <f>Assumptions!$C$38-'Cash Flow'!D$22</f>
+        <f>Assumptions!$C$46-'Cash Flow'!D$22</f>
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>Assumptions!$C$38-'Cash Flow'!E$22</f>
+        <f>Assumptions!$C$46-'Cash Flow'!E$22</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>Assumptions!$C$38-'Cash Flow'!F$22</f>
+        <f>Assumptions!$C$46-'Cash Flow'!F$22</f>
         <v/>
       </c>
     </row>
@@ -1488,39 +1623,39 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="33">
         <f>B9+B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="33">
         <f>C9+C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="33">
         <f>D9+D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="33">
         <f>E9+E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="33">
         <f>F9+F10+F11+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="33">
         <f>G9+G10+G11+G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="33">
         <f>H9+H10+H11+H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="33">
         <f>I9+I10+I11+I12+I13</f>
         <v/>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="33">
         <f>J9+J10+J11+J12+J13</f>
         <v/>
       </c>
@@ -1550,39 +1685,39 @@
         </is>
       </c>
       <c r="B17" s="17">
-        <f>B6*Assumptions!$C$41/365</f>
+        <f>B6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>C6*Assumptions!$C$41/365</f>
+        <f>C6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>D6*Assumptions!$C$41/365</f>
+        <f>D6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>E6*Assumptions!$C$41/365</f>
+        <f>E6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>F6*Assumptions!$C$41/365</f>
+        <f>F6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>G6*Assumptions!$C$41/365</f>
+        <f>G6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>H6*Assumptions!$C$41/365</f>
+        <f>H6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>I6*Assumptions!$C$41/365</f>
+        <f>I6*Assumptions!$C$49/365</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>J6*Assumptions!$C$41/365</f>
+        <f>J6*Assumptions!$C$49/365</f>
         <v/>
       </c>
     </row>
@@ -1592,40 +1727,40 @@
           <t>Gross debt</t>
         </is>
       </c>
-      <c r="B18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="C18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="D18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="E18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="F18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="G18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="H18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="I18" s="32">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="J18" s="32">
-        <f>Assumptions!$C$38</f>
+      <c r="B18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="C18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="D18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="E18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="F18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="G18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="H18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="I18" s="23">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="J18" s="23">
+        <f>Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1783,7 @@
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>Assumptions!$C$36-Assumptions!$C$38-E17</f>
+        <f>Assumptions!$C$44-Assumptions!$C$46-E17</f>
         <v/>
       </c>
       <c r="F19" s="17">
@@ -1679,19 +1814,19 @@
         </is>
       </c>
       <c r="B20" s="17">
-        <f>C20/(1-Assumptions!$C$61)-Assumptions!$C$15+Assumptions!$C$43*Assumptions!$C$6-(C20/(1-Assumptions!$C$61)-Assumptions!$C$15+Assumptions!$C$43*Assumptions!$C$6)*Assumptions!$C$61</f>
+        <f>C20/(1-Assumptions!$C$70)-Assumptions!$C$15+Assumptions!$C$52*Assumptions!$C$6-(C20/(1-Assumptions!$C$70)-Assumptions!$C$15+Assumptions!$C$52*Assumptions!$C$6)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>D20/(1-Assumptions!$C$61)-Assumptions!$C$19+Assumptions!$C$43*Assumptions!$C$6-(D20/(1-Assumptions!$C$61)-Assumptions!$C$19+Assumptions!$C$43*Assumptions!$C$6)*Assumptions!$C$61</f>
+        <f>D20/(1-Assumptions!$C$70)-Assumptions!$C$19+Assumptions!$C$52*Assumptions!$C$6-(D20/(1-Assumptions!$C$70)-Assumptions!$C$19+Assumptions!$C$52*Assumptions!$C$6)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>E20/(1-Assumptions!$C$61)-Assumptions!$C$23+0.5*Assumptions!$C$43*Assumptions!$C$6-(E20/(1-Assumptions!$C$61)-Assumptions!$C$23+0.5*Assumptions!$C$43*Assumptions!$C$6)*Assumptions!$C$61</f>
+        <f>E20/(1-Assumptions!$C$70)-Assumptions!$C$23+0.5*Assumptions!$C$52*Assumptions!$C$6-(E20/(1-Assumptions!$C$70)-Assumptions!$C$23+0.5*Assumptions!$C$52*Assumptions!$C$6)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="E20" s="17">
-        <f>(Assumptions!$C$35-Assumptions!$C$36)*(1-Assumptions!$C$61)</f>
+        <f>(Assumptions!$C$43-Assumptions!$C$44)*(1-Assumptions!$C$70)</f>
         <v/>
       </c>
       <c r="F20" s="18">
@@ -1722,39 +1857,39 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>B20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>B20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>C20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>C20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>D20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>D20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="E21" s="17">
-        <f>E20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>E20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F21" s="17">
-        <f>F20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>F20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>G20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>G20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>H20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>H20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I21" s="17">
-        <f>I20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>I20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>J20/(1-Assumptions!$C$61)*Assumptions!$C$61</f>
+        <f>J20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -1764,39 +1899,39 @@
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="33">
         <f>B17+B18+B19+B20+B21</f>
         <v/>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="33">
         <f>C17+C18+C19+C20+C21</f>
         <v/>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="33">
         <f>D17+D18+D19+D20+D21</f>
         <v/>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="33">
         <f>E17+E18+E19+E20+E21</f>
         <v/>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="33">
         <f>F17+F18+F19+F20+F21</f>
         <v/>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="33">
         <f>G17+G18+G19+G20+G21</f>
         <v/>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="33">
         <f>H17+H18+H19+H20+H21</f>
         <v/>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="33">
         <f>I17+I18+I19+I20+I21</f>
         <v/>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="33">
         <f>J17+J18+J19+J20+J21</f>
         <v/>
       </c>
@@ -1873,7 +2008,7 @@
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>E25/E5</f>
+        <f>C25/C5</f>
         <v/>
       </c>
       <c r="D26" s="16">
@@ -2189,23 +2324,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B7*Assumptions!$C$52</f>
+        <f>B7*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C7*Assumptions!$C$52</f>
+        <f>C7*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D7*Assumptions!$C$52</f>
+        <f>D7*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E7*Assumptions!$C$52</f>
+        <f>E7*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>F7*Assumptions!$C$52</f>
+        <f>F7*Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
@@ -2296,23 +2431,23 @@
           <t>OPERATING CASH FLOW</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="33">
         <f>B9+B10-B11</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="33">
         <f>C9+C10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="33">
         <f>D9+D10-D11</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="33">
         <f>E9+E10-E11</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="33">
         <f>F9+F10-F11</f>
         <v/>
       </c>
@@ -2350,23 +2485,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="33">
         <f>B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="33">
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="33">
         <f>D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="33">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="33">
         <f>F12-F13</f>
         <v/>
       </c>
@@ -2378,23 +2513,23 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>MAX(Assumptions!$C$38-B$21,0)</f>
+        <f>MAX(Assumptions!$C$46-B$21,0)</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>MAX(Assumptions!$C$38-C$21,0)</f>
+        <f>MAX(Assumptions!$C$46-C$21,0)</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>MAX(Assumptions!$C$38-D$21,0)</f>
+        <f>MAX(Assumptions!$C$46-D$21,0)</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>MAX(Assumptions!$C$38-E$21,0)</f>
+        <f>MAX(Assumptions!$C$46-E$21,0)</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>MAX(Assumptions!$C$38-F$21,0)</f>
+        <f>MAX(Assumptions!$C$46-F$21,0)</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2540,23 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>Assumptions!$B$78*B15-Assumptions!$B$69*Assumptions!$C$38</f>
+        <f>Assumptions!$B$91*B15-Assumptions!$B$81*Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>Assumptions!$C$78*C15-Assumptions!$C$69*Assumptions!$C$38</f>
+        <f>Assumptions!$C$91*C15-Assumptions!$C$81*Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>Assumptions!$D$78*D15-Assumptions!$D$69*Assumptions!$C$38</f>
+        <f>Assumptions!$D$91*D15-Assumptions!$D$81*Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>Assumptions!$E$78*E15-Assumptions!$E$69*Assumptions!$C$38</f>
+        <f>Assumptions!$E$91*E15-Assumptions!$E$81*Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>Assumptions!$F$78*F15-Assumptions!$F$69*Assumptions!$C$38</f>
+        <f>Assumptions!$F$91*F15-Assumptions!$F$81*Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -2432,23 +2567,23 @@
         </is>
       </c>
       <c r="B17" s="17">
-        <f>(B7+B16)*(1-Assumptions!$C$52)*(1-Assumptions!$C$61)</f>
+        <f>(B7+B16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>(C7+C16)*(1-Assumptions!$C$52)*(1-Assumptions!$C$61)</f>
+        <f>(C7+C16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>(D7+D16)*(1-Assumptions!$C$52)*(1-Assumptions!$C$61)</f>
+        <f>(D7+D16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>(E7+E16)*(1-Assumptions!$C$52)*(1-Assumptions!$C$61)</f>
+        <f>(E7+E16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>(F7+F16)*(1-Assumptions!$C$52)*(1-Assumptions!$C$61)</f>
+        <f>(F7+F16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
         <v/>
       </c>
     </row>
@@ -2459,23 +2594,23 @@
         </is>
       </c>
       <c r="B18" s="17">
-        <f>Assumptions!$C$62*B17</f>
+        <f>Assumptions!$C$71*B17</f>
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>Assumptions!$C$62*C17</f>
+        <f>Assumptions!$C$71*C17</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>Assumptions!$C$62*D17</f>
+        <f>Assumptions!$C$71*D17</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>Assumptions!$C$62*E17</f>
+        <f>Assumptions!$C$71*E17</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>Assumptions!$C$62*F17</f>
+        <f>Assumptions!$C$71*F17</f>
         <v/>
       </c>
     </row>
@@ -2526,24 +2661,24 @@
           <t>Closing net debt</t>
         </is>
       </c>
-      <c r="B22" s="31">
-        <f>B21-(B14+B16*(1-Assumptions!$C$52))+B18</f>
-        <v/>
-      </c>
-      <c r="C22" s="31">
-        <f>C21-(C14+C16*(1-Assumptions!$C$52))+C18</f>
-        <v/>
-      </c>
-      <c r="D22" s="31">
-        <f>D21-(D14+D16*(1-Assumptions!$C$52))+D18</f>
-        <v/>
-      </c>
-      <c r="E22" s="31">
-        <f>E21-(E14+E16*(1-Assumptions!$C$52))+E18</f>
-        <v/>
-      </c>
-      <c r="F22" s="31">
-        <f>F21-(F14+F16*(1-Assumptions!$C$52))+F18</f>
+      <c r="B22" s="33">
+        <f>B21-(B14+B16*(1-Assumptions!$C$61))+B18</f>
+        <v/>
+      </c>
+      <c r="C22" s="33">
+        <f>C21-(C14+C16*(1-Assumptions!$C$61))+C18</f>
+        <v/>
+      </c>
+      <c r="D22" s="33">
+        <f>D21-(D14+D16*(1-Assumptions!$C$61))+D18</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
+        <f>E21-(E14+E16*(1-Assumptions!$C$61))+E18</f>
+        <v/>
+      </c>
+      <c r="F22" s="33">
+        <f>F21-(F14+F16*(1-Assumptions!$C$61))+F18</f>
         <v/>
       </c>
     </row>
@@ -2607,23 +2742,23 @@
           <t>Closing attributable equity</t>
         </is>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="33">
         <f>B24+B17-B18</f>
         <v/>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="33">
         <f>C24+C17-C18</f>
         <v/>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="33">
         <f>D24+D17-D18</f>
         <v/>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="33">
         <f>E24+E17-E18</f>
         <v/>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="33">
         <f>F24+F17-F18</f>
         <v/>
       </c>
@@ -3196,12 +3331,12 @@
           <t>Target date</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
@@ -3213,12 +3348,12 @@
           <t>Grade date</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
@@ -3295,10 +3430,10 @@
           <t>Probability above spot</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="28" t="n">
         <v>0.53284</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="28" t="n">
         <v>0.56048</v>
       </c>
     </row>
@@ -3308,10 +3443,10 @@
           <t>Probability 10% or more up</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="28" t="n">
         <v>0.18262</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="28" t="n">
         <v>0.3318</v>
       </c>
     </row>
@@ -3321,10 +3456,10 @@
           <t>Probability 10% or more down</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="28" t="n">
         <v>0.12658</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="28" t="n">
         <v>0.21574</v>
       </c>
     </row>
@@ -3334,10 +3469,10 @@
           <t>Probability of touching +10%</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="28" t="n">
         <v>0.2999</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="28" t="n">
         <v>0.56412</v>
       </c>
     </row>
@@ -3347,10 +3482,10 @@
           <t>Probability of touching -10%</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="28" t="n">
         <v>0.21706</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="28" t="n">
         <v>0.42922</v>
       </c>
     </row>
@@ -3360,10 +3495,10 @@
           <t>Annualised volatility at the anchor</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="28" t="n">
         <v>0.4179907789031863</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="28" t="n">
         <v>0.4085225075524802</v>
       </c>
     </row>
@@ -3397,7 +3532,7 @@
           <t>First origin</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="50" t="inlineStr">
         <is>
           <t>2022-04-05</t>
         </is>
@@ -3409,7 +3544,7 @@
           <t>Last origin</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B23" s="50" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
@@ -3421,7 +3556,7 @@
           <t>Skill against a carry-anchored random walk</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="28" t="n">
         <v>0.006758984690108827</v>
       </c>
     </row>
@@ -3431,7 +3566,7 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="50" t="inlineStr">
         <is>
           <t>PARITY</t>
         </is>
@@ -3443,7 +3578,7 @@
           <t>Coverage of the 90% band</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="28" t="n">
         <v>0.9411764705882353</v>
       </c>
     </row>
@@ -3453,7 +3588,7 @@
           <t>Probability-integral-transform mean</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="31" t="n">
         <v>0.4612000000000001</v>
       </c>
     </row>
@@ -3463,7 +3598,7 @@
           <t>Cone width against the benchmark</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B28" s="31" t="n">
         <v>0.9693809251589353</v>
       </c>
     </row>
@@ -3473,7 +3608,7 @@
           <t>Market panel verdict</t>
         </is>
       </c>
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="50" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3485,7 +3620,7 @@
           <t>Market panel skill</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="28" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -3500,23 +3635,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sensitivity — each cell is a complete revaluation</t>
+          <t>Sensitivity — the cost-of-capital grids are LIVE formulas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3526,11 +3662,12 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>PASTED VALUES. Every cell re-runs the whole model at a different driver setting, so these grids do NOT redraw when a driver changes on Assumptions.</t>
+          <t>Each cell re-runs the discount path, the terminal block and the bridge off this sheet. Only the sweeps that change REVENUE are pasted, because those need the product build re-run and cannot be a formula in a grid.</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3675,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>TERMINAL COST OF CAPITAL x TERMINAL GROWTH (EGP per share)</t>
+          <t>GRID 1 — TERMINAL COST OF CAPITAL x TERMINAL GROWTH (EGP per share, LIVE)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -3548,506 +3685,1123 @@
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Terminal WACC \ Terminal g</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C5" s="45" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D5" s="45" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E5" s="45" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F5" s="45" t="n">
-        <v>0.07000000000000001</v>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>row: terminal rate · helper columns C:G are that row's discount factors</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Terminal WACC</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>PV explicit</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>df1</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>df2</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>df3</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>df4</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>df5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="n">
         <v>0.1452265</v>
       </c>
-      <c r="B6" s="22" t="n">
-        <v>10.32612246271658</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>10.78288627435288</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>11.33558216616357</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>12.01797853653683</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>12.88179937046304</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="B7" s="17">
+        <f>DCF!B$18*C7+DCF!C$18*D7+DCF!D$18*E7+DCF!E$18*F7+DCF!F$18*G7</f>
+        <v/>
+      </c>
+      <c r="C7" s="25">
+        <f>1/(1+(DCF!$B$54-(DCF!$B$54-$A$7)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
+        <f>C7/(1+(DCF!$B$54-(DCF!$B$54-$A$7)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>D7/(1+(DCF!$B$54-(DCF!$B$54-$A$7)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>E7/(1+(DCF!$B$54-(DCF!$B$54-$A$7)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>F7/(1+(DCF!$B$54-(DCF!$B$54-$A$7)*DCF!F$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="n">
         <v>0.1552265</v>
       </c>
-      <c r="B7" s="22" t="n">
-        <v>9.745971768566928</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>10.1165726792539</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>10.55761229324982</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>11.09128150383827</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>11.75018622464677</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="B8" s="17">
+        <f>DCF!B$18*C8+DCF!C$18*D8+DCF!D$18*E8+DCF!E$18*F8+DCF!F$18*G8</f>
+        <v/>
+      </c>
+      <c r="C8" s="25">
+        <f>1/(1+(DCF!$B$54-(DCF!$B$54-$A$8)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>C8/(1+(DCF!$B$54-(DCF!$B$54-$A$8)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>D8/(1+(DCF!$B$54-(DCF!$B$54-$A$8)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>E8/(1+(DCF!$B$54-(DCF!$B$54-$A$8)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>F8/(1+(DCF!$B$54-(DCF!$B$54-$A$8)*DCF!F$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="n">
         <v>0.1652265</v>
       </c>
-      <c r="B8" s="22" t="n">
-        <v>9.251248707693684</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>9.556180147813706</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>9.914038898946387</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>10.33991449966214</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>10.85523486642848</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="B9" s="17">
+        <f>DCF!B$18*C9+DCF!C$18*D9+DCF!D$18*E9+DCF!E$18*F9+DCF!F$18*G9</f>
+        <v/>
+      </c>
+      <c r="C9" s="25">
+        <f>1/(1+(DCF!$B$54-(DCF!$B$54-$A$9)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
+        <f>C9/(1+(DCF!$B$54-(DCF!$B$54-$A$9)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>D9/(1+(DCF!$B$54-(DCF!$B$54-$A$9)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>E9/(1+(DCF!$B$54-(DCF!$B$54-$A$9)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>F9/(1+(DCF!$B$54-(DCF!$B$54-$A$9)*DCF!F$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="n">
         <v>0.1752265</v>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>8.824310561876638</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <v>9.078217631789881</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>9.372676353296557</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>9.71824462364949</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>10.12949373872365</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="B10" s="17">
+        <f>DCF!B$18*C10+DCF!C$18*D10+DCF!D$18*E10+DCF!E$18*F10+DCF!F$18*G10</f>
+        <v/>
+      </c>
+      <c r="C10" s="25">
+        <f>1/(1+(DCF!$B$54-(DCF!$B$54-$A$10)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="D10" s="25">
+        <f>C10/(1+(DCF!$B$54-(DCF!$B$54-$A$10)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>D10/(1+(DCF!$B$54-(DCF!$B$54-$A$10)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
+        <f>E10/(1+(DCF!$B$54-(DCF!$B$54-$A$10)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="G10" s="25">
+        <f>F10/(1+(DCF!$B$54-(DCF!$B$54-$A$10)*DCF!F$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="n">
         <v>0.1852265</v>
       </c>
-      <c r="B10" s="22" t="n">
-        <v>8.452060888863643</v>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>8.6656641130773</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>8.910859255178893</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>9.195214661617763</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>9.528925972547157</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>EXPLICIT-WINDOW x TERMINAL COST OF CAPITAL (EGP per share)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-    </row>
+      <c r="B11" s="17">
+        <f>DCF!B$18*C11+DCF!C$18*D11+DCF!D$18*E11+DCF!E$18*F11+DCF!F$18*G11</f>
+        <v/>
+      </c>
+      <c r="C11" s="25">
+        <f>1/(1+(DCF!$B$54-(DCF!$B$54-$A$11)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="D11" s="25">
+        <f>C11/(1+(DCF!$B$54-(DCF!$B$54-$A$11)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>D11/(1+(DCF!$B$54-(DCF!$B$54-$A$11)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="F11" s="25">
+        <f>E11/(1+(DCF!$B$54-(DCF!$B$54-$A$11)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="G11" s="25">
+        <f>F11/(1+(DCF!$B$54-(DCF!$B$54-$A$11)*DCF!F$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Explicit WACC \ Terminal WACC</t>
-        </is>
-      </c>
-      <c r="B13" s="45" t="n">
-        <v>0.1452265</v>
-      </c>
-      <c r="C13" s="45" t="n">
-        <v>0.1552265</v>
-      </c>
-      <c r="D13" s="45" t="n">
-        <v>0.1652265</v>
-      </c>
-      <c r="E13" s="45" t="n">
-        <v>0.1752265</v>
-      </c>
-      <c r="F13" s="45" t="n">
-        <v>0.1852265</v>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Terminal WACC \ terminal g</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
-        <v>0.2863274586594906</v>
-      </c>
-      <c r="B14" s="22" t="n">
-        <v>11.80403681275764</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>10.9843592872358</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>10.30629646199505</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>9.73593393103854</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>9.249388875646547</v>
+      <c r="A14" s="43">
+        <f>A7</f>
+        <v/>
+      </c>
+      <c r="B14" s="20">
+        <f>((B7+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A7-0.03)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C14" s="20">
+        <f>((B7+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A7-0.04)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f>((B7+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A7-0.05)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E14" s="20">
+        <f>((B7+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A7-0.06)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F14" s="20">
+        <f>((B7+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A7-0.07)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
-        <v>0.3013274586594906</v>
-      </c>
-      <c r="B15" s="22" t="n">
-        <v>11.56590793035367</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>10.76744487835321</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>10.10692489323954</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>9.551312932964418</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>9.077345433739172</v>
+      <c r="A15" s="43">
+        <f>A8</f>
+        <v/>
+      </c>
+      <c r="B15" s="20">
+        <f>((B8+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A8-0.03)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>((B8+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A8-0.04)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>((B8+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A8-0.05)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>((B8+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A8-0.06)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>((B8+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A8-0.07)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
-        <v>0.3163274586594906</v>
-      </c>
-      <c r="B16" s="22" t="n">
-        <v>11.33558216616357</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>10.55761229324982</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>9.914038898946387</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>9.372676353296557</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>8.910859255178893</v>
+      <c r="A16" s="43">
+        <f>A9</f>
+        <v/>
+      </c>
+      <c r="B16" s="20">
+        <f>((B9+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A9-0.03)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f>((B9+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A9-0.04)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D16" s="20">
+        <f>((B9+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A9-0.05)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E16" s="20">
+        <f>((B9+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A9-0.06)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F16" s="20">
+        <f>((B9+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A9-0.07)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
-        <v>0.3313274586594906</v>
-      </c>
-      <c r="B17" s="22" t="n">
-        <v>11.11273519167019</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>10.35456786785352</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>9.727370155325914</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>9.199777159813573</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>8.749701448772367</v>
+      <c r="A17" s="43">
+        <f>A10</f>
+        <v/>
+      </c>
+      <c r="B17" s="20">
+        <f>((B10+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A10-0.03)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>((B10+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A10-0.04)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D17" s="20">
+        <f>((B10+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A10-0.05)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E17" s="20">
+        <f>((B10+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A10-0.06)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F17" s="20">
+        <f>((B10+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A10-0.07)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>0.3463274586594906</v>
-      </c>
-      <c r="B18" s="22" t="n">
-        <v>10.89705906540662</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>10.15803275184683</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>9.546663852580602</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>9.032380742521237</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>8.593654615635687</v>
+      <c r="A18" s="43">
+        <f>A11</f>
+        <v/>
+      </c>
+      <c r="B18" s="20">
+        <f>((B11+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A11-0.03)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>((B11+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A11-0.04)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D18" s="20">
+        <f>((B11+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A11-0.05)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E18" s="20">
+        <f>((B11+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A11-0.06)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F18" s="20">
+        <f>((B11+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A11-0.07)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="19"/>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SINGLE-DRIVER SWEEPS (EGP per share)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Every cell above is a formula. Change the terminal cost of capital in column A, or the growth rate in the header, and the grid redraws. The previous edition pasted all 25 cells, which is how a stale sweep can ship beside a base case it no longer reproduces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>GRID 2 — BETA (EGP per share, LIVE)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C21" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D21" s="26" t="n">
-        <v>0.9405</v>
-      </c>
-      <c r="E21" s="26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F21" s="26" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Fair value</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="n">
-        <v>12.28183496832688</v>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>10.85359432889467</v>
-      </c>
-      <c r="D22" s="22" t="n">
-        <v>10.04342209747108</v>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>9.050934232680575</v>
-      </c>
-      <c r="F22" s="22" t="n">
-        <v>8.462276598001157</v>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Gross margin shift</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="C24" s="27" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="D24" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="27" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>0.01</v>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Cost of equity, explicit</t>
+        </is>
+      </c>
+      <c r="B24" s="43">
+        <f>DCF!$B$43+0.6*DCF!$B$45</f>
+        <v/>
+      </c>
+      <c r="C24" s="43">
+        <f>DCF!$B$43+0.8*DCF!$B$45</f>
+        <v/>
+      </c>
+      <c r="D24" s="43">
+        <f>DCF!$B$43+0.9405*DCF!$B$45</f>
+        <v/>
+      </c>
+      <c r="E24" s="43">
+        <f>DCF!$B$43+1.15*DCF!$B$45</f>
+        <v/>
+      </c>
+      <c r="F24" s="43">
+        <f>DCF!$B$43+1.3*DCF!$B$45</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Fair value</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>7.86836415284176</v>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>8.891201525894072</v>
-      </c>
-      <c r="D25" s="22" t="n">
-        <v>9.914038898946387</v>
-      </c>
-      <c r="E25" s="22" t="n">
-        <v>10.9368762719987</v>
-      </c>
-      <c r="F25" s="22" t="n">
-        <v>11.95971364505101</v>
-      </c>
-    </row>
-    <row r="26"/>
+          <t>Cost of equity, terminal</t>
+        </is>
+      </c>
+      <c r="B25" s="43">
+        <f>Assumptions!$C$62+0.6*Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="C25" s="43">
+        <f>Assumptions!$C$62+0.8*Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="D25" s="43">
+        <f>Assumptions!$C$62+0.9405*Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="E25" s="43">
+        <f>Assumptions!$C$62+1.15*Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="F25" s="43">
+        <f>Assumptions!$C$62+1.3*Assumptions!$C$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>WACC explicit</t>
+        </is>
+      </c>
+      <c r="B26" s="43">
+        <f>DCF!$B$52*B24+DCF!$B$51*DCF!$B$53</f>
+        <v/>
+      </c>
+      <c r="C26" s="43">
+        <f>DCF!$B$52*C24+DCF!$B$51*DCF!$B$53</f>
+        <v/>
+      </c>
+      <c r="D26" s="43">
+        <f>DCF!$B$52*D24+DCF!$B$51*DCF!$B$53</f>
+        <v/>
+      </c>
+      <c r="E26" s="43">
+        <f>DCF!$B$52*E24+DCF!$B$51*DCF!$B$53</f>
+        <v/>
+      </c>
+      <c r="F26" s="43">
+        <f>DCF!$B$52*F24+DCF!$B$51*DCF!$B$53</f>
+        <v/>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Volume growth multiplier</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D27" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F27" s="26" t="n">
-        <v>2</v>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>WACC terminal</t>
+        </is>
+      </c>
+      <c r="B27" s="43">
+        <f>(1-Assumptions!$C$65)*B25+Assumptions!$C$65*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="C27" s="43">
+        <f>(1-Assumptions!$C$65)*C25+Assumptions!$C$65*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="D27" s="43">
+        <f>(1-Assumptions!$C$65)*D25+Assumptions!$C$65*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="E27" s="43">
+        <f>(1-Assumptions!$C$65)*E25+Assumptions!$C$65*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="F27" s="43">
+        <f>(1-Assumptions!$C$65)*F25+Assumptions!$C$65*DCF!$B$60</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Fair value</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="n">
-        <v>8.636918825277691</v>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>9.251651976568729</v>
-      </c>
-      <c r="D28" s="22" t="n">
-        <v>9.914038898946387</v>
-      </c>
-      <c r="E28" s="22" t="n">
-        <v>10.62701003090676</v>
-      </c>
-      <c r="F28" s="22" t="n">
-        <v>11.39362013348653</v>
-      </c>
-    </row>
-    <row r="29"/>
+          <t>df1</t>
+        </is>
+      </c>
+      <c r="B28" s="25">
+        <f>1/(1+(B26-(B26-B27)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>1/(1+(C26-(C26-C27)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="D28" s="25">
+        <f>1/(1+(D26-(D26-D27)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="E28" s="25">
+        <f>1/(1+(E26-(E26-E27)*DCF!B$67))</f>
+        <v/>
+      </c>
+      <c r="F28" s="25">
+        <f>1/(1+(F26-(F26-F27)*DCF!B$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>df2</t>
+        </is>
+      </c>
+      <c r="B29" s="25">
+        <f>B28/(1+(B26-(B26-B27)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="C29" s="25">
+        <f>C28/(1+(C26-(C26-C27)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="D29" s="25">
+        <f>D28/(1+(D26-(D26-D27)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="E29" s="25">
+        <f>E28/(1+(E26-(E26-E27)*DCF!C$67))</f>
+        <v/>
+      </c>
+      <c r="F29" s="25">
+        <f>F28/(1+(F26-(F26-F27)*DCF!C$67))</f>
+        <v/>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>Exchange-rate path multiplier</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C30" s="26" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D30" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F30" s="26" t="n">
-        <v>1.1</v>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>df3</t>
+        </is>
+      </c>
+      <c r="B30" s="25">
+        <f>B29/(1+(B26-(B26-B27)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>C29/(1+(C26-(C26-C27)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="D30" s="25">
+        <f>D29/(1+(D26-(D26-D27)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="E30" s="25">
+        <f>E29/(1+(E26-(E26-E27)*DCF!D$67))</f>
+        <v/>
+      </c>
+      <c r="F30" s="25">
+        <f>F29/(1+(F26-(F26-F27)*DCF!D$67))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>df4</t>
+        </is>
+      </c>
+      <c r="B31" s="25">
+        <f>B30/(1+(B26-(B26-B27)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="C31" s="25">
+        <f>C30/(1+(C26-(C26-C27)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="D31" s="25">
+        <f>D30/(1+(D26-(D26-D27)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="E31" s="25">
+        <f>E30/(1+(E26-(E26-E27)*DCF!E$67))</f>
+        <v/>
+      </c>
+      <c r="F31" s="25">
+        <f>F30/(1+(F26-(F26-F27)*DCF!E$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>df5</t>
+        </is>
+      </c>
+      <c r="B32" s="25">
+        <f>B31/(1+(B26-(B26-B27)*DCF!F$67))</f>
+        <v/>
+      </c>
+      <c r="C32" s="25">
+        <f>C31/(1+(C26-(C26-C27)*DCF!F$67))</f>
+        <v/>
+      </c>
+      <c r="D32" s="25">
+        <f>D31/(1+(D26-(D26-D27)*DCF!F$67))</f>
+        <v/>
+      </c>
+      <c r="E32" s="25">
+        <f>E31/(1+(E26-(E26-E27)*DCF!F$67))</f>
+        <v/>
+      </c>
+      <c r="F32" s="25">
+        <f>F31/(1+(F26-(F26-F27)*DCF!F$67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>PV explicit</t>
+        </is>
+      </c>
+      <c r="B33" s="17">
+        <f>DCF!B$18*B28+DCF!C$18*B29+DCF!D$18*B30+DCF!E$18*B31+DCF!F$18*B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="17">
+        <f>DCF!B$18*C28+DCF!C$18*C29+DCF!D$18*C30+DCF!E$18*C31+DCF!F$18*C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>DCF!B$18*D28+DCF!C$18*D29+DCF!D$18*D30+DCF!E$18*D31+DCF!F$18*D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>DCF!B$18*E28+DCF!C$18*E29+DCF!D$18*E30+DCF!E$18*E31+DCF!F$18*E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>DCF!B$18*F28+DCF!C$18*F29+DCF!D$18*F30+DCF!E$18*F31+DCF!F$18*F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>FAIR VALUE (EGP per share)</t>
+        </is>
+      </c>
+      <c r="B35" s="20">
+        <f>(((B33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B27-Assumptions!$C$66)*B32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C35" s="20">
+        <f>(((C33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C27-Assumptions!$C$66)*C32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D35" s="20">
+        <f>(((D33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D27-Assumptions!$C$66)*D32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E35" s="20">
+        <f>(((E33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E27-Assumptions!$C$66)*E32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F35" s="20">
+        <f>(((F33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F27-Assumptions!$C$66)*F32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Check: the base column must reproduce the base case</t>
+        </is>
+      </c>
+      <c r="D36" s="25">
+        <f>D35-'EV Bridge'!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>The base column of this sweep is now a formula off the same cells the base case uses, so it cannot drift from it — the row above proves it to four decimals. The previous edition pasted this sweep and it had drifted: its centre column read 10.04 against a base case of 9.91.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>GRID 3 — EXPLICIT x TERMINAL COST OF CAPITAL (EGP per share, LIVE)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>each anchor varied independently around its own base; one formula a cell, no helper block</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Explicit \ terminal</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="n">
+        <v>0.1452265</v>
+      </c>
+      <c r="C42" s="51" t="n">
+        <v>0.1552265</v>
+      </c>
+      <c r="D42" s="51" t="n">
+        <v>0.1652265</v>
+      </c>
+      <c r="E42" s="51" t="n">
+        <v>0.1752265</v>
+      </c>
+      <c r="F42" s="51" t="n">
+        <v>0.1852265</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="n">
+        <v>0.2863274586594906</v>
+      </c>
+      <c r="B43" s="20">
+        <f>(DCF!B$18/((1+($A$43-($A$43-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67))*(1+($A$43-($A$43-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67))*(1+($A$43-($A$43-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f>(DCF!B$18/((1+($A$43-($A$43-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67))*(1+($A$43-($A$43-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67))*(1+($A$43-($A$43-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
+        <f>(DCF!B$18/((1+($A$43-($A$43-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67))*(1+($A$43-($A$43-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67))*(1+($A$43-($A$43-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E43" s="20">
+        <f>(DCF!B$18/((1+($A$43-($A$43-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67))*(1+($A$43-($A$43-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67))*(1+($A$43-($A$43-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f>(DCF!B$18/((1+($A$43-($A$43-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67))*(1+($A$43-($A$43-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67))*(1+($A$43-($A$43-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="n">
+        <v>0.3013274586594906</v>
+      </c>
+      <c r="B44" s="20">
+        <f>(DCF!B$18/((1+($A$44-($A$44-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67))*(1+($A$44-($A$44-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67))*(1+($A$44-($A$44-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C44" s="20">
+        <f>(DCF!B$18/((1+($A$44-($A$44-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67))*(1+($A$44-($A$44-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67))*(1+($A$44-($A$44-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D44" s="20">
+        <f>(DCF!B$18/((1+($A$44-($A$44-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67))*(1+($A$44-($A$44-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67))*(1+($A$44-($A$44-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E44" s="20">
+        <f>(DCF!B$18/((1+($A$44-($A$44-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67))*(1+($A$44-($A$44-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67))*(1+($A$44-($A$44-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F44" s="20">
+        <f>(DCF!B$18/((1+($A$44-($A$44-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67))*(1+($A$44-($A$44-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67))*(1+($A$44-($A$44-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="n">
+        <v>0.3163274586594906</v>
+      </c>
+      <c r="B45" s="20">
+        <f>(DCF!B$18/((1+($A$45-($A$45-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67))*(1+($A$45-($A$45-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67))*(1+($A$45-($A$45-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C45" s="20">
+        <f>(DCF!B$18/((1+($A$45-($A$45-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67))*(1+($A$45-($A$45-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67))*(1+($A$45-($A$45-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D45" s="20">
+        <f>(DCF!B$18/((1+($A$45-($A$45-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67))*(1+($A$45-($A$45-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67))*(1+($A$45-($A$45-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E45" s="20">
+        <f>(DCF!B$18/((1+($A$45-($A$45-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67))*(1+($A$45-($A$45-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67))*(1+($A$45-($A$45-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F45" s="20">
+        <f>(DCF!B$18/((1+($A$45-($A$45-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67))*(1+($A$45-($A$45-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67))*(1+($A$45-($A$45-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="n">
+        <v>0.3313274586594906</v>
+      </c>
+      <c r="B46" s="20">
+        <f>(DCF!B$18/((1+($A$46-($A$46-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67))*(1+($A$46-($A$46-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67))*(1+($A$46-($A$46-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C46" s="20">
+        <f>(DCF!B$18/((1+($A$46-($A$46-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67))*(1+($A$46-($A$46-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67))*(1+($A$46-($A$46-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D46" s="20">
+        <f>(DCF!B$18/((1+($A$46-($A$46-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67))*(1+($A$46-($A$46-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67))*(1+($A$46-($A$46-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E46" s="20">
+        <f>(DCF!B$18/((1+($A$46-($A$46-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67))*(1+($A$46-($A$46-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67))*(1+($A$46-($A$46-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F46" s="20">
+        <f>(DCF!B$18/((1+($A$46-($A$46-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67))*(1+($A$46-($A$46-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67))*(1+($A$46-($A$46-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="30" t="n">
+        <v>0.3463274586594906</v>
+      </c>
+      <c r="B47" s="20">
+        <f>(DCF!B$18/((1+($A$47-($A$47-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67))*(1+($A$47-($A$47-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67))*(1+($A$47-($A$47-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C47" s="20">
+        <f>(DCF!B$18/((1+($A$47-($A$47-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67))*(1+($A$47-($A$47-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67))*(1+($A$47-($A$47-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D47" s="20">
+        <f>(DCF!B$18/((1+($A$47-($A$47-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67))*(1+($A$47-($A$47-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67))*(1+($A$47-($A$47-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E47" s="20">
+        <f>(DCF!B$18/((1+($A$47-($A$47-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67))*(1+($A$47-($A$47-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67))*(1+($A$47-($A$47-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F47" s="20">
+        <f>(DCF!B$18/((1+($A$47-($A$47-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67))*(1+($A$47-($A$47-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67))*(1+($A$47-($A$47-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Check: the centre cell must reproduce the base case</t>
+        </is>
+      </c>
+      <c r="D49" s="25">
+        <f>D45-'EV Bridge'!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>WHOLE-MODEL RE-RUNS — PASTED, and these do NOT redraw</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>The sweeps below change REVENUE, so each cell needs the three-line product build re-run from the top. They are complete revaluations and are the one class of cell on this sheet that cannot be a formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>Margin ratio (specialty over fuel)</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C53" s="29" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D53" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="29" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F53" s="29" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
           <t>Fair value</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
-        <v>9.123929684261853</v>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>9.51898429160412</v>
-      </c>
-      <c r="D31" s="22" t="n">
-        <v>9.914038898946387</v>
-      </c>
-      <c r="E31" s="22" t="n">
-        <v>10.30909350628865</v>
-      </c>
-      <c r="F31" s="22" t="n">
-        <v>10.70414811363093</v>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="B54" s="22" t="n">
+        <v>7.376368355511639</v>
+      </c>
+      <c r="C54" s="22" t="n">
+        <v>8.387952063134712</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>9.399535770757785</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>10.41111947838086</v>
+      </c>
+      <c r="F54" s="22" t="n">
+        <v>11.42270318600393</v>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Volume growth multiplier</t>
+        </is>
+      </c>
+      <c r="B56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D56" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F56" s="29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Fair value</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="n">
+        <v>8.040394454192397</v>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>8.69089639724986</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>9.399535770757785</v>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>10.17033825671128</v>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>11.00751599858174</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>Exchange-rate path multiplier</t>
+        </is>
+      </c>
+      <c r="B59" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C59" s="29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F59" s="29" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Fair value</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n">
+        <v>8.666540392073383</v>
+      </c>
+      <c r="C60" s="22" t="n">
+        <v>9.033038081415583</v>
+      </c>
+      <c r="D60" s="22" t="n">
+        <v>9.399535770757785</v>
+      </c>
+      <c r="E60" s="22" t="n">
+        <v>9.766033460099989</v>
+      </c>
+      <c r="F60" s="22" t="n">
+        <v>10.13253114944219</v>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Net working capital, % of revenue</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B62" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C62" s="30" t="n">
         <v>0.01</v>
       </c>
-      <c r="D33" s="27" t="n">
+      <c r="D62" s="30" t="n">
         <v>0.02021314135515365</v>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E62" s="30" t="n">
         <v>0.03</v>
       </c>
-      <c r="F33" s="27" t="n">
+      <c r="F62" s="30" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
-        <v>10.2773885410665</v>
-      </c>
-      <c r="C34" s="22" t="n">
-        <v>10.09762942508552</v>
-      </c>
-      <c r="D34" s="22" t="n">
-        <v>9.914038898946387</v>
-      </c>
-      <c r="E34" s="22" t="n">
-        <v>9.73811119312354</v>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>9.378592961161562</v>
+      <c r="B63" s="22" t="n">
+        <v>9.754139749992664</v>
+      </c>
+      <c r="C63" s="22" t="n">
+        <v>9.578707355292437</v>
+      </c>
+      <c r="D63" s="22" t="n">
+        <v>9.399535770757785</v>
+      </c>
+      <c r="E63" s="22" t="n">
+        <v>9.227842565891986</v>
+      </c>
+      <c r="F63" s="22" t="n">
+        <v>8.876977776491534</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A38:I38"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4358,39 +5112,39 @@
           <t>Asset turnover (revenue / total assets)</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="46">
         <f>'Income Statement'!B5/'Balance Sheet'!B14</f>
         <v/>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="46">
         <f>'Income Statement'!C5/'Balance Sheet'!C14</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="46">
         <f>'Income Statement'!D5/'Balance Sheet'!D14</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="46">
         <f>'Income Statement'!E5/'Balance Sheet'!E14</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="46">
         <f>'Income Statement'!F5/'Balance Sheet'!F14</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="46">
         <f>'Income Statement'!G5/'Balance Sheet'!G14</f>
         <v/>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="46">
         <f>'Income Statement'!H5/'Balance Sheet'!H14</f>
         <v/>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="46">
         <f>'Income Statement'!I5/'Balance Sheet'!I14</f>
         <v/>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="46">
         <f>'Income Statement'!J5/'Balance Sheet'!J14</f>
         <v/>
       </c>
@@ -4401,39 +5155,39 @@
           <t>Net working capital days</t>
         </is>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="35">
         <f>'Balance Sheet'!B25/'Income Statement'!B5*365</f>
         <v/>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="35">
         <f>'Balance Sheet'!C25/'Income Statement'!C5*365</f>
         <v/>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="35">
         <f>'Balance Sheet'!D25/'Income Statement'!D5*365</f>
         <v/>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="35">
         <f>'Balance Sheet'!E25/'Income Statement'!E5*365</f>
         <v/>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="35">
         <f>'Balance Sheet'!F25/'Income Statement'!F5*365</f>
         <v/>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="35">
         <f>'Balance Sheet'!G25/'Income Statement'!G5*365</f>
         <v/>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="35">
         <f>'Balance Sheet'!H25/'Income Statement'!H5*365</f>
         <v/>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="35">
         <f>'Balance Sheet'!I25/'Income Statement'!I5*365</f>
         <v/>
       </c>
-      <c r="J11" s="46">
+      <c r="J11" s="35">
         <f>'Balance Sheet'!J25/'Income Statement'!J5*365</f>
         <v/>
       </c>
@@ -4445,19 +5199,19 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="C12" s="8">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D12" s="8">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="E12" s="8">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="F12" s="20">
@@ -4544,18 +5298,19 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Company trailing enterprise value / EBITDA</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="n">
-        <v>4.522303508446424</v>
+          <t>Company trailing enterprise value / EBITDA (computed)</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>'Relative &amp; Normalized'!$B$13</f>
+        <v/>
       </c>
       <c r="C5" s="18">
         <f>DCF!C9</f>
         <v/>
       </c>
       <c r="D5" s="20">
-        <f>(B5*C5*DCF!C19-DCF!$B$49)*(1-Assumptions!$C$61)/Assumptions!$C$6</f>
+        <f>B5*C5*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4565,51 +5320,54 @@
           <t>Justified enterprise value / EBITDA (adopted)</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
-        <v>4.5</v>
+      <c r="B6" s="19">
+        <f>Assumptions!$C$72</f>
+        <v/>
       </c>
       <c r="C6" s="18">
         <f>DCF!C9</f>
         <v/>
       </c>
       <c r="D6" s="20">
-        <f>(B6*C6*DCF!C19-DCF!$B$49)*(1-Assumptions!$C$61)/Assumptions!$C$6</f>
+        <f>B6*C6*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Group I base-oil processors, low end</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="n">
-        <v>3.5</v>
+          <t>House low bound — NOT a peer observation</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
+        <f>Assumptions!$C$73</f>
+        <v/>
       </c>
       <c r="C7" s="18">
         <f>DCF!C9</f>
         <v/>
       </c>
       <c r="D7" s="20">
-        <f>(B7*C7*DCF!C19-DCF!$B$49)*(1-Assumptions!$C$61)/Assumptions!$C$6</f>
+        <f>B7*C7*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Group I base-oil processors, high end</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="n">
-        <v>6</v>
+          <t>House high bound — NOT a peer observation</t>
+        </is>
+      </c>
+      <c r="B8" s="19">
+        <f>Assumptions!$C$74</f>
+        <v/>
       </c>
       <c r="C8" s="18">
         <f>DCF!C9</f>
         <v/>
       </c>
       <c r="D8" s="20">
-        <f>(B8*C8*DCF!C19-DCF!$B$49)*(1-Assumptions!$C$61)/Assumptions!$C$6</f>
+        <f>B8*C8*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4665,24 +5423,24 @@
           <t>Throughput (mn tonnes)</t>
         </is>
       </c>
-      <c r="B12" s="47">
-        <f>'Product Legs'!C5</f>
-        <v/>
-      </c>
-      <c r="C12" s="47">
-        <f>'Product Legs'!D5</f>
-        <v/>
-      </c>
-      <c r="D12" s="47">
-        <f>'Product Legs'!E5</f>
-        <v/>
-      </c>
-      <c r="E12" s="47">
-        <f>'Product Legs'!F5</f>
-        <v/>
-      </c>
-      <c r="F12" s="47">
-        <f>'Product Legs'!G5</f>
+      <c r="B12" s="38">
+        <f>'Product Lines'!C54</f>
+        <v/>
+      </c>
+      <c r="C12" s="38">
+        <f>'Product Lines'!D54</f>
+        <v/>
+      </c>
+      <c r="D12" s="38">
+        <f>'Product Lines'!E54</f>
+        <v/>
+      </c>
+      <c r="E12" s="38">
+        <f>'Product Lines'!F54</f>
+        <v/>
+      </c>
+      <c r="F12" s="38">
+        <f>'Product Lines'!G54</f>
         <v/>
       </c>
     </row>
@@ -4693,23 +5451,23 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>DCF!B9/'Product Legs'!C5</f>
+        <f>DCF!B9/'Product Lines'!C54</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>DCF!C9/'Product Legs'!D5</f>
+        <f>DCF!C9/'Product Lines'!D54</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>DCF!D9/'Product Legs'!E5</f>
+        <f>DCF!D9/'Product Lines'!E54</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>DCF!E9/'Product Legs'!F5</f>
+        <f>DCF!E9/'Product Lines'!F54</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>DCF!F9/'Product Legs'!G5</f>
+        <f>DCF!F9/'Product Lines'!G54</f>
         <v/>
       </c>
     </row>
@@ -4720,23 +5478,23 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>'Product Legs'!C16/'Product Legs'!C18</f>
+        <f>'Product Lines'!C51</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>'Product Legs'!D16/'Product Legs'!D18</f>
+        <f>'Product Lines'!D51</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>'Product Legs'!E16/'Product Legs'!E18</f>
+        <f>'Product Lines'!E51</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>'Product Legs'!F16/'Product Legs'!F18</f>
+        <f>'Product Lines'!F51</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>'Product Legs'!G16/'Product Legs'!G18</f>
+        <f>'Product Lines'!G51</f>
         <v/>
       </c>
     </row>
@@ -4747,23 +5505,23 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>DCF!B7/'Product Legs'!C5</f>
+        <f>DCF!B7/'Product Lines'!C54</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>DCF!C7/'Product Legs'!D5</f>
+        <f>DCF!C7/'Product Lines'!D54</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>DCF!D7/'Product Legs'!E5</f>
+        <f>DCF!D7/'Product Lines'!E54</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>DCF!E7/'Product Legs'!F5</f>
+        <f>DCF!E7/'Product Lines'!F54</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>DCF!F7/'Product Legs'!G5</f>
+        <f>DCF!F7/'Product Lines'!G54</f>
         <v/>
       </c>
     </row>
@@ -4774,23 +5532,23 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>DCF!B15/'Product Legs'!C5</f>
+        <f>DCF!B15/'Product Lines'!C54</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>DCF!C15/'Product Legs'!D5</f>
+        <f>DCF!C15/'Product Lines'!D54</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>DCF!D15/'Product Legs'!E5</f>
+        <f>DCF!D15/'Product Lines'!E54</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>DCF!E15/'Product Legs'!F5</f>
+        <f>DCF!E15/'Product Lines'!F54</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>DCF!F15/'Product Legs'!G5</f>
+        <f>DCF!F15/'Product Lines'!G54</f>
         <v/>
       </c>
     </row>
@@ -5094,7 +5852,7 @@
         </is>
       </c>
       <c r="C18" s="18">
-        <f>'Product Legs'!B26</f>
+        <f>'Product Lines'!E26</f>
         <v/>
       </c>
     </row>
@@ -5105,7 +5863,7 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>'Product Legs'!B29</f>
+        <f>'Product Lines'!B56</f>
         <v/>
       </c>
     </row>
@@ -5116,7 +5874,7 @@
         </is>
       </c>
       <c r="C20" s="19">
-        <f>'Relative &amp; Normalized'!$B$13</f>
+        <f>'Relative &amp; Normalized'!$B$14</f>
         <v/>
       </c>
     </row>
@@ -5127,7 +5885,7 @@
         </is>
       </c>
       <c r="C21" s="16">
-        <f>Assumptions!$C$43/Assumptions!$C$5</f>
+        <f>Assumptions!$C$52/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -5138,7 +5896,7 @@
         </is>
       </c>
       <c r="C22" s="20">
-        <f>C10/Assumptions!$C$32</f>
+        <f>C10/Assumptions!$C$40</f>
         <v/>
       </c>
     </row>
@@ -5171,7 +5929,7 @@
         </is>
       </c>
       <c r="C25" s="10">
-        <f>Assumptions!$C$57</f>
+        <f>Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -5197,7 +5955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5263,17 +6021,17 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>6.091950967770007</v>
+        <v>5.699212717526938</v>
       </c>
       <c r="C5" s="8">
         <f>'EV Bridge'!$B$12</f>
         <v/>
       </c>
       <c r="D5" s="22" t="n">
-        <v>16.68993443912786</v>
+        <v>15.9696796013002</v>
       </c>
       <c r="E5" s="9">
-        <f>Assumptions!$C$86</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
       <c r="F5" s="20">
@@ -5288,17 +6046,17 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>6.124257875433853</v>
+        <v>7.314267406614372</v>
       </c>
       <c r="C6" s="8">
-        <f>'Relative &amp; Normalized'!$B$11</f>
+        <f>'Relative &amp; Normalized'!$B$12</f>
         <v/>
       </c>
       <c r="D6" s="22" t="n">
-        <v>9.190723623164919</v>
+        <v>10.28611388710643</v>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$87</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="F6" s="20">
@@ -5313,17 +6071,17 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>9.052461531148765</v>
+        <v>8.623992774195941</v>
       </c>
       <c r="C7" s="8">
-        <f>'Relative &amp; Normalized'!$B$23</f>
+        <f>'Relative &amp; Normalized'!$B$24</f>
         <v/>
       </c>
       <c r="D7" s="22" t="n">
-        <v>15.63606991743878</v>
+        <v>14.89598751906572</v>
       </c>
       <c r="E7" s="9">
-        <f>Assumptions!$C$88</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="F7" s="20">
@@ -5341,14 +6099,14 @@
         <v>3.825843755451646</v>
       </c>
       <c r="C8" s="8">
-        <f>'Relative &amp; Normalized'!$B$31</f>
+        <f>'Relative &amp; Normalized'!$B$32</f>
         <v/>
       </c>
       <c r="D8" s="22" t="n">
         <v>7.994059366782158</v>
       </c>
       <c r="E8" s="9">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="F8" s="20">
@@ -5426,49 +6184,156 @@
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Expert panel median (EGP)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>9.829302563573256</v>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Currency-of-discounting alternative (EGP)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>10.70834398300427</v>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>THE EXPERT PANEL, LIVE — and why the median is not a check</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Rating-basis cost of capital alternative (EGP)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>8.167671249298847</v>
+          <t>Expert 1 — earnings power: 2028E attributable earnings per share</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>'Relative &amp; Normalized'!$B$22</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        × Expert 1 justified multiple</t>
+        </is>
+      </c>
+      <c r="B18" s="23">
+        <f>Assumptions!$C$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        = Expert 1 fair value (EGP)</t>
+        </is>
+      </c>
+      <c r="C19" s="20">
+        <f>B17*B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Expert 2 — free cash flow to equity: present value of the explicit years</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>4772.886445826336</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        plus the present value of the terminal block</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>6492.209855871781</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        = Expert 2 fair value (EGP)</t>
+        </is>
+      </c>
+      <c r="C22" s="20">
+        <f>(B20+B21)/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Expert 3 — economic profit. LINKED, not recomputed: an economic-profit build off the same NOPAT, capital and discount path IS the cash-flow lens</t>
+        </is>
+      </c>
+      <c r="C23" s="8">
+        <f>'EV Bridge'!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Expert 3 less the cash-flow lens — MUST be zero, and that is the point</t>
+        </is>
+      </c>
+      <c r="C24" s="25">
+        <f>C23-'EV Bridge'!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Expert panel median (EGP) — NOT an independent check, see note</t>
+        </is>
+      </c>
+      <c r="C25" s="20">
+        <f>MEDIAN(C19,C22,C23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Spread between the two INDEPENDENT reads (Expert 1 less Expert 2)</t>
+        </is>
+      </c>
+      <c r="C26" s="20">
+        <f>C19-C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative (EGP)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>9.985524031416009</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Rating-basis cost of capital alternative (EGP)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>7.795612915677023</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
           <t>Gross-debt weighting alternative, rejected (EGP)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="n">
-        <v>10.42860919723092</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="C30" s="22" t="n">
+        <v>9.875828732302327</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Bear and bull columns are whole-model re-runs — each is a complete revaluation at a different set of drivers, so they are values rather than formulas. The base column, the weights, the contributions and the weighted central are all live.</t>
         </is>
@@ -5476,7 +6341,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5488,7 +6353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5562,7 +6427,7 @@
           <t>mn</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="26" t="n">
         <v>1291.56</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -5908,7 +6773,7 @@
           <t>mn tonnes</t>
         </is>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="27" t="n">
         <v>1.26</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -5928,7 +6793,7 @@
           <t>mn tonnes</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="27" t="n">
         <v>0.172</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -5948,7 +6813,7 @@
           <t>mn tonnes</t>
         </is>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="27" t="n">
         <v>0.8080000000000001</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -5960,358 +6825,395 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Annualisation shading on the half-year</t>
+          <t>Base oils sold, year to Jun-2024</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="n">
-        <v>0.96</v>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>111256</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>ramp still building</t>
+          <t>disclosed product table</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Specialty realised price</t>
+          <t>Base oils, sales value</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>USD/tonne</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>1105</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>4454.085</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>calibrated to disclosure</t>
+          <t>disclosed</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP average, calendar 2025</t>
+          <t>Paraffin wax sold, year to Jun-2024</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="n">
-        <v>48.7</v>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>65742</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP spot</t>
+          <t>Paraffin wax, sales value</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="n">
-        <v>50.25</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>2408.747</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>6 Aug 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+          <t>disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Total tonnes, year to Jun-2024</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>1433340</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>BALANCE SHEET — DISCLOSED SNAPSHOT AND DAYS DRIVERS</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Total sales value, year to Jun-2024</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>33312.101</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>USD/EGP average, year to Jun-2024</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="n">
-        <v>8136.42</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>36.4</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>month-weighted across the float</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Specialty tonnage ramp to the base year</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>3189.56</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n">
+        <v>0.1</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>on the disclosed +40% export rise</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Cash and equivalents</t>
+          <t>Base oils as a share of specialty tonnage</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="n">
-        <v>2463.52</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n">
+        <v>0.6285720742607261</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>from the disclosed table</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Gross debt</t>
+          <t>Specialty margin as a multiple of the fuel margin</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>25.26</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>3.5</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>the one judgment parameter behind the margin</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Receivable days</t>
+          <t>USD/EGP average, calendar 2025</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>14</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="n">
+        <v>48.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Inventory days on cost of sales</t>
+          <t>USD/EGP spot</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Payable days on cost of sales</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="n">
-        <v>24</v>
-      </c>
-    </row>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>6 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Other current assets</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="n">
-        <v>300</v>
-      </c>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>BALANCE SHEET — DISCLOSED SNAPSHOT AND DAYS DRIVERS</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Dividend per share</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C43" s="22" t="n">
-        <v>0.8</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>8136.42</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>declared</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
+          <t>disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>3189.56</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>COST OF CAPITAL</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Cash and equivalents</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>2463.52</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Risk-free rate — Egypt 10-year</t>
+          <t>Gross debt</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="n">
-        <v>0.2231</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Sovereign default spread</t>
+          <t>Receivable days</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>netted out of rf</t>
-        </is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Equity risk premium — Egypt</t>
+          <t>Inventory days on cost of sales</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Damodaran, CDS basis</t>
-        </is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Payable days on cost of sales</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C49" s="28" t="n">
-        <v>0.9405</v>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>own-stock regression</t>
-        </is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Cost of debt</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="n">
-        <v>0.22</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Yield on cash</t>
+          <t>Historical operating cost load, % of revenue</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -6319,69 +7221,52 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C51" s="27" t="n">
-        <v>0.17</v>
+      <c r="C51" s="30" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>held flat across the reconstructed years</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Effective tax rate</t>
+          <t>Dividend per share</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="n">
-        <v>0.235</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>norm-built</t>
-        </is>
-      </c>
-    </row>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>declared</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Terminal equity risk premium</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C54" s="27" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>normalised</t>
-        </is>
-      </c>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>COST OF CAPITAL</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Risk-free rate — Egypt 10-year</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -6389,14 +7274,14 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C55" s="27" t="n">
-        <v>0.15</v>
+      <c r="C55" s="30" t="n">
+        <v>0.2231</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
+          <t>Sovereign default spread</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -6404,19 +7289,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
-        <v>0.1</v>
+      <c r="C56" s="30" t="n">
+        <v>0.034</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>normalised</t>
+          <t>netted out of rf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Equity risk premium — Egypt</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -6424,32 +7309,54 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C57" s="27" t="n">
-        <v>0.05</v>
+      <c r="C57" s="30" t="n">
+        <v>0.0941</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>sensitised 3-7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
+          <t>Damodaran, CDS basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C58" s="31" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>own-stock regression</t>
+        </is>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>OPERATING DRIVERS</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Cost of debt</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C59" s="30" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Depreciation, % of revenue</t>
+          <t>Yield on cash</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -6457,14 +7364,14 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C60" s="27" t="n">
-        <v>0.011</v>
+      <c r="C60" s="30" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Minority share of group profit</t>
+          <t>Effective tax rate</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -6472,14 +7379,14 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C61" s="29" t="n">
-        <v>0.03</v>
+      <c r="C61" s="30" t="n">
+        <v>0.235</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Dividend payout ratio</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -6487,49 +7394,54 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n">
-        <v>0.694</v>
+      <c r="C62" s="30" t="n">
+        <v>0.105</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>norm-built</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Justified EV / EBITDA</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C63" s="30" t="n">
-        <v>4.5</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Justified price / earnings</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C64" s="30" t="n">
-        <v>7.5</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -6537,408 +7449,623 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C65" s="29" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>PATHS — one column per forecast year</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-    </row>
+      <c r="C65" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>sensitised 3-7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
-      </c>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>OPERATING DRIVERS</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Cost of debt path</t>
-        </is>
-      </c>
-      <c r="B69" s="27" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C69" s="27" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="D69" s="27" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E69" s="27" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>0.15</v>
+          <t>Depreciation, % of revenue</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP average rate path</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="C70" s="23" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="D70" s="23" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="E70" s="23" t="n">
-        <v>58</v>
-      </c>
-      <c r="F70" s="23" t="n">
-        <v>60.1</v>
+          <t>Minority share of group profit</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Capital expenditure, % of revenue</t>
-        </is>
-      </c>
-      <c r="B71" s="27" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="C71" s="27" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="D71" s="27" t="n">
-        <v>0.0135</v>
-      </c>
-      <c r="E71" s="27" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F71" s="27" t="n">
-        <v>0.0125</v>
+          <t>Dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Operating cost load, % of revenue</t>
-        </is>
-      </c>
-      <c r="B72" s="27" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="C72" s="27" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="D72" s="27" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="E72" s="27" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="F72" s="27" t="n">
-        <v>0.0128</v>
+          <t>Justified EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Gross margin (forecast)</t>
-        </is>
-      </c>
-      <c r="B73" s="27" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C73" s="27" t="n">
-        <v>0.0665</v>
-      </c>
-      <c r="D73" s="27" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="E73" s="27" t="n">
-        <v>0.0682</v>
-      </c>
-      <c r="F73" s="27" t="n">
-        <v>0.0688</v>
+          <t>House low bound on the multiple</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>NOT a peer observation</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Total volume growth</t>
-        </is>
-      </c>
-      <c r="B74" s="27" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="C74" s="27" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D74" s="27" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E74" s="27" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F74" s="27" t="n">
-        <v>0.025</v>
+          <t>House high bound on the multiple</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>NOT a peer observation</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Specialty volume growth</t>
-        </is>
-      </c>
-      <c r="B75" s="27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C75" s="27" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D75" s="27" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E75" s="27" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F75" s="27" t="n">
-        <v>0.04</v>
+          <t>Justified price / earnings</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Specialty price growth (USD)</t>
-        </is>
-      </c>
-      <c r="B76" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C76" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D76" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E76" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F76" s="27" t="n">
-        <v>0.02</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C76" s="28" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Fuel price growth (USD)</t>
-        </is>
-      </c>
-      <c r="B77" s="27" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C77" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D77" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E77" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F77" s="27" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Yield on cash path</t>
-        </is>
-      </c>
-      <c r="B78" s="27" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="C78" s="27" t="n">
+          <t>Expert 1 justified price / earnings</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Expert 1 strikes a lower multiple than the main normalised lens deliberately: it is an independent opinion, not a re-run of the house view</t>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>PATHS — one column per forecast year</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B81" s="30" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C81" s="30" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="D81" s="30" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E81" s="30" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F81" s="30" t="n">
         <v>0.15</v>
-      </c>
-      <c r="D78" s="27" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E78" s="27" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F78" s="27" t="n">
-        <v>0.118</v>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>HISTORICAL GROSS MARGIN — one column per period</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>FY2022/23</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>FY2023/24</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>FY2024/25</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>CY2025</t>
-        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Gross margin (historical)</t>
-        </is>
-      </c>
-      <c r="B82" s="27" t="n">
-        <v>0.0576</v>
-      </c>
-      <c r="C82" s="27" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D82" s="27" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="E82" s="27" t="n">
-        <v>0.064</v>
+          <t>USD/EGP average rate path</t>
+        </is>
+      </c>
+      <c r="B82" s="26" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="C82" s="26" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="D82" s="26" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E82" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="F82" s="26" t="n">
+        <v>60.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>FY2022/23 is the DISCLOSED margin: gross profit over cost of sales plus gross profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="84"/>
+          <t>Capital expenditure, % of revenue</t>
+        </is>
+      </c>
+      <c r="B83" s="30" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="C83" s="30" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D83" s="30" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="E83" s="30" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F83" s="30" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>Operating cost load, % of revenue</t>
+        </is>
+      </c>
+      <c r="B84" s="30" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="C84" s="30" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D84" s="30" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="E84" s="30" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F84" s="30" t="n">
+        <v>0.0128</v>
+      </c>
+    </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>LENS WEIGHTS</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Base-oil volume growth</t>
+        </is>
+      </c>
+      <c r="B85" s="30" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C85" s="30" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D85" s="30" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E85" s="30" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F85" s="30" t="n">
+        <v>0.032</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C86" s="29" t="n">
-        <v>0.45</v>
+          <t>Paraffin-wax volume growth</t>
+        </is>
+      </c>
+      <c r="B86" s="30" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C86" s="30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D86" s="30" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E86" s="30" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F86" s="30" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Relative multiples</t>
-        </is>
-      </c>
-      <c r="C87" s="29" t="n">
-        <v>0.2</v>
+          <t>Fuel-slate volume growth</t>
+        </is>
+      </c>
+      <c r="B87" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C87" s="30" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D87" s="30" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="E87" s="30" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F87" s="30" t="n">
+        <v>0.023</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Normalised earnings power</t>
-        </is>
-      </c>
-      <c r="C88" s="29" t="n">
-        <v>0.2</v>
+          <t>Base-oil dollar price growth</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C88" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D88" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E88" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F88" s="30" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
+          <t>Paraffin-wax dollar price growth</t>
+        </is>
+      </c>
+      <c r="B89" s="30" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C89" s="30" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D89" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E89" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F89" s="30" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Fuel-slate dollar price growth</t>
+        </is>
+      </c>
+      <c r="B90" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C90" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D90" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E90" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F90" s="30" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Yield on cash path</t>
+        </is>
+      </c>
+      <c r="B91" s="30" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C91" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D91" s="30" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="E91" s="30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F91" s="30" t="n">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>HISTORICAL GROSS MARGIN — one column per period</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>FY2022/23</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>FY2023/24</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>FY2024/25</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>CY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin (historical)</t>
+        </is>
+      </c>
+      <c r="B95" s="30" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="C95" s="30" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D95" s="30" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E95" s="30" t="n">
+        <v>0.064</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>FY2022/23 is the DISCLOSED margin: gross profit over cost of sales plus gross profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>LENS WEIGHTS</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C99" s="28" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>Relative multiples</t>
+        </is>
+      </c>
+      <c r="C100" s="28" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Normalised earnings power</t>
+        </is>
+      </c>
+      <c r="C101" s="28" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
           <t>Book and sustainable return</t>
         </is>
       </c>
-      <c r="C89" s="29" t="n">
+      <c r="C102" s="28" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C90" s="15">
-        <f>C86+C87+C88+C89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91"/>
-    <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
+      <c r="C103" s="15">
+        <f>C99+C100+C101+C102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104"/>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
         <is>
           <t>Blue cells are the only inputs in this workbook. Everything on every other sheet is a formula pointing back here, except audited history and the two whole-model re-run grids (Monte Carlo, Sensitivity), which are labelled as such on their own sheets.</t>
         </is>
@@ -6946,7 +8073,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A105:F105"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6958,7 +8085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7020,26 +8147,22 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>less net debt (negative = net cash added)</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
-        <f>DCF!$B$49</f>
-        <v/>
-      </c>
-      <c r="C6" s="20">
-        <f>B6/Assumptions!$C$6</f>
+          <t>Minority share of group profit</t>
+        </is>
+      </c>
+      <c r="B6" s="9">
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Equity value before minority interests</t>
+          <t>less minority interests — ON THE ENTERPRISE VALUE, BEFORE THE CASH</t>
         </is>
       </c>
       <c r="B7" s="17">
-        <f>B5-B6</f>
+        <f>B5*B6</f>
         <v/>
       </c>
       <c r="C7" s="20">
@@ -7050,22 +8173,26 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Minority share of group profit</t>
-        </is>
-      </c>
-      <c r="B8" s="9">
-        <f>Assumptions!$C$61</f>
+          <t>Operating assets attributable to shareholders</t>
+        </is>
+      </c>
+      <c r="B8" s="17">
+        <f>B5-B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="20">
+        <f>B8/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>less minority interests</t>
-        </is>
-      </c>
-      <c r="B9" s="17">
-        <f>B7*B8</f>
+          <t>less net debt (negative = net cash added, IN FULL)</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>DCF!$B$49</f>
         <v/>
       </c>
       <c r="C9" s="20">
@@ -7079,8 +8206,8 @@
           <t>EQUITY ATTRIBUTABLE TO SHAREHOLDERS</t>
         </is>
       </c>
-      <c r="B10" s="31">
-        <f>B7-B9</f>
+      <c r="B10" s="33">
+        <f>B8-B9</f>
         <v/>
       </c>
     </row>
@@ -7090,7 +8217,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="23">
         <f>Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7112,7 +8239,7 @@
           <t>TERMINAL VALUE AS A SHARE OF ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>DCF!$B$35</f>
         <v/>
       </c>
@@ -7139,17 +8266,54 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>The minority deduction is taken on the equity value AFTER net debt, not on the enterprise value, so the minority does not carry a share of the parent's cash. Doubling the minority share to 6% is one of the contested choices computed in the study and moves the answer by roughly three per cent.</t>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>MEMO — what the WRONG order would have given</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Minority taken AFTER the cash, on the combined total (the rejected order)</t>
+        </is>
+      </c>
+      <c r="B17" s="17">
+        <f>(B5-B9)*(1-B6)</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>B17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Value the rejected order would have handed the minority</t>
+        </is>
+      </c>
+      <c r="B18" s="17">
+        <f>B10-B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>B18/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>THE ORDER OF THESE ROWS IS THE SUBSTANTIVE POINT. The minority is deducted from the OPERATING enterprise value, before the cash is added, and the cash is then added back in full because it belongs to the parent. An earlier edition of this model did it the other way round — added the cash first, then took the minority share off the combined total — and defended it in a note reading "the minority deduction is taken on the equity value AFTER net debt, so the minority does not carry a share of the parent's cash". That defence was algebraically inverted: deducting a percentage of a total that ALREADY includes the cash is exactly how you hand the minority a slice of it. An external review caught it, the correction is accepted, and the memo rows above compute what the rejected order would have produced so the reader can see the size of it rather than take it on trust. Doubling the minority share to 6% is a separate contested choice, computed on the Fundamental Valuation sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7161,22 +8325,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Revenue build — two product legs, volume x dollar price x exchange rate</t>
+          <t>Revenue and margin built from the disclosed product table</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7185,520 +8350,960 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Not one growth rate. The specialty leg (base oils, paraffin wax, special oils) carries the margin; the fuel and by-product leg is close to pass-through.</t>
+          <t>Three lines, each a tonnage times a dollar realisation times an exchange rate. No price is calibrated and none is a residual. The blended gross margin is an OUTPUT of the mix.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr"/>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>CY2025</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
-      </c>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>THE DISCLOSED PRODUCT TABLE — year to 30 June 2024</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Total sales volume (mn tonnes)</t>
-        </is>
-      </c>
-      <c r="B5" s="34">
-        <f>Assumptions!$C$28*2*Assumptions!$C$29</f>
-        <v/>
-      </c>
-      <c r="C5" s="34">
-        <f>B5*(1+Assumptions!$B$74)</f>
-        <v/>
-      </c>
-      <c r="D5" s="34">
-        <f>C5*(1+Assumptions!$C$74)</f>
-        <v/>
-      </c>
-      <c r="E5" s="34">
-        <f>D5*(1+Assumptions!$D$74)</f>
-        <v/>
-      </c>
-      <c r="F5" s="34">
-        <f>E5*(1+Assumptions!$E$74)</f>
-        <v/>
-      </c>
-      <c r="G5" s="34">
-        <f>F5*(1+Assumptions!$F$74)</f>
-        <v/>
+      <c r="A5" s="12" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Tonnes</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>EGP / tonne</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>USD / tonne</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Share of tonnage</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Share of value</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Specialty volume (mn tonnes)</t>
-        </is>
-      </c>
-      <c r="B6" s="34">
-        <f>Assumptions!$C$27*(B5/Assumptions!$C$26)</f>
-        <v/>
-      </c>
-      <c r="C6" s="34">
-        <f>B6*(1+Assumptions!$B$75)</f>
-        <v/>
-      </c>
-      <c r="D6" s="34">
-        <f>C6*(1+Assumptions!$C$75)</f>
-        <v/>
-      </c>
-      <c r="E6" s="34">
-        <f>D6*(1+Assumptions!$D$75)</f>
-        <v/>
-      </c>
-      <c r="F6" s="34">
-        <f>E6*(1+Assumptions!$E$75)</f>
-        <v/>
-      </c>
-      <c r="G6" s="34">
-        <f>F6*(1+Assumptions!$F$75)</f>
+          <t>Base oils</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>Assumptions!$C$29</f>
+        <v/>
+      </c>
+      <c r="C6" s="23">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>C6*1000000/B6</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>D6/Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>B6/B9</f>
+        <v/>
+      </c>
+      <c r="G6" s="16">
+        <f>C6/C9</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Fuel and by-product volume (mn tonnes)</t>
-        </is>
-      </c>
-      <c r="B7" s="34">
-        <f>B5-B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="34">
-        <f>C5-C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="34">
-        <f>D5-D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="34">
-        <f>E5-E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="34">
-        <f>F5-F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="34">
-        <f>G5-G6</f>
+          <t>Paraffin wax</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>Assumptions!$C$31</f>
+        <v/>
+      </c>
+      <c r="C7" s="23">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>C7*1000000/B7</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>D7/Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>B7/B9</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>C7/C9</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Specialty share of volume</t>
-        </is>
-      </c>
-      <c r="B8" s="16">
-        <f>B6/B5</f>
-        <v/>
-      </c>
-      <c r="C8" s="16">
-        <f>C6/C5</f>
-        <v/>
-      </c>
-      <c r="D8" s="16">
-        <f>D6/D5</f>
-        <v/>
-      </c>
-      <c r="E8" s="16">
-        <f>E6/E5</f>
+          <t>Fuel and by-products</t>
+        </is>
+      </c>
+      <c r="B8" s="17">
+        <f>Assumptions!$C$33-B6-B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="35">
+        <f>Assumptions!$C$34-C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>C8*1000000/B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>D8/Assumptions!$C$35</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>F6/F5</f>
+        <f>B8/B9</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>G6/G5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>REALISED PRICES</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Specialty price (USD / tonne)</t>
-        </is>
-      </c>
-      <c r="B11" s="18">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="C11" s="17">
-        <f>B11*(1+Assumptions!$B$76)</f>
-        <v/>
-      </c>
-      <c r="D11" s="17">
-        <f>C11*(1+Assumptions!$C$76)</f>
-        <v/>
-      </c>
-      <c r="E11" s="17">
-        <f>D11*(1+Assumptions!$D$76)</f>
-        <v/>
-      </c>
-      <c r="F11" s="17">
-        <f>E11*(1+Assumptions!$E$76)</f>
-        <v/>
-      </c>
-      <c r="G11" s="17">
-        <f>F11*(1+Assumptions!$F$76)</f>
-        <v/>
+        <f>C8/C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Total (disclosed)</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="C9" s="37">
+        <f>Assumptions!$C$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Every realisation on this sheet is DERIVED from the disclosed tonnage and value. The previous build had a specialty price that was a free input and a fuel price that was the residual of the base-year revenue — which meant the "implied fuel price" offered as a plausibility check was a residual of the very construction it was said to validate. Nothing here is a residual.</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Fuel price (USD / tonne)</t>
-        </is>
-      </c>
-      <c r="B12" s="17">
-        <f>B27</f>
-        <v/>
-      </c>
-      <c r="C12" s="17">
-        <f>B12*(1+Assumptions!$B$77)</f>
-        <v/>
-      </c>
-      <c r="D12" s="17">
-        <f>C12*(1+Assumptions!$C$77)</f>
-        <v/>
-      </c>
-      <c r="E12" s="17">
-        <f>D12*(1+Assumptions!$D$77)</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
-        <f>E12*(1+Assumptions!$E$77)</f>
-        <v/>
-      </c>
-      <c r="G12" s="17">
-        <f>F12*(1+Assumptions!$F$77)</f>
-        <v/>
-      </c>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>THE CALENDAR-2025 BASE — volume built the same way as revenue</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP average rate</t>
-        </is>
-      </c>
-      <c r="B13" s="32">
-        <f>Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="C13" s="32">
-        <f>Assumptions!$B$70</f>
-        <v/>
-      </c>
-      <c r="D13" s="32">
-        <f>Assumptions!$C$70</f>
-        <v/>
-      </c>
-      <c r="E13" s="32">
-        <f>Assumptions!$D$70</f>
-        <v/>
-      </c>
-      <c r="F13" s="32">
-        <f>Assumptions!$E$70</f>
-        <v/>
-      </c>
-      <c r="G13" s="32">
-        <f>Assumptions!$F$70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>Jul-Dec 2025 tonnage (disclosed)</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>Assumptions!$C$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Jul-Dec 2024, off the disclosed +14.5%</t>
+        </is>
+      </c>
+      <c r="B14" s="39">
+        <f>B13/1.145</f>
+        <v/>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>REVENUE BY LEG (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>FY2024/25 tonnage (disclosed)</t>
+        </is>
+      </c>
+      <c r="B15" s="38">
+        <f>Assumptions!$C$26</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Specialty oils and waxes</t>
-        </is>
-      </c>
-      <c r="B16" s="17">
-        <f>B6*B11*B13</f>
-        <v/>
-      </c>
-      <c r="C16" s="17">
-        <f>C6*C11*C13</f>
-        <v/>
-      </c>
-      <c r="D16" s="17">
-        <f>D6*D11*D13</f>
-        <v/>
-      </c>
-      <c r="E16" s="17">
-        <f>E6*E11*E13</f>
-        <v/>
-      </c>
-      <c r="F16" s="17">
-        <f>F6*F11*F13</f>
-        <v/>
-      </c>
-      <c r="G16" s="17">
-        <f>G6*G11*G13</f>
+          <t>Jan-Jun 2025 (the residual half)</t>
+        </is>
+      </c>
+      <c r="B16" s="39">
+        <f>B15-B14</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Fuel and by-products</t>
-        </is>
-      </c>
-      <c r="B17" s="17">
-        <f>B7*B12*B13</f>
-        <v/>
-      </c>
-      <c r="C17" s="17">
-        <f>C7*C12*C13</f>
-        <v/>
-      </c>
-      <c r="D17" s="17">
-        <f>D7*D12*D13</f>
-        <v/>
-      </c>
-      <c r="E17" s="17">
-        <f>E7*E12*E13</f>
-        <v/>
-      </c>
-      <c r="F17" s="17">
-        <f>F7*F12*F13</f>
-        <v/>
-      </c>
-      <c r="G17" s="17">
-        <f>G7*G12*G13</f>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>CALENDAR 2025 TONNAGE</t>
+        </is>
+      </c>
+      <c r="B17" s="40">
+        <f>B16+B13</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>B16+B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="31">
-        <f>C16+C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="31">
-        <f>D16+D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="31">
-        <f>E16+E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="31">
-        <f>F16+F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="31">
-        <f>G16+G17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Specialty share of revenue</t>
-        </is>
-      </c>
-      <c r="B19" s="16">
-        <f>B16/B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="16">
-        <f>C16/C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f>D16/D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="16">
-        <f>E16/E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="16">
-        <f>F16/F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="16">
-        <f>G16/G18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Specialty tonnage (FY2024/25 disclosed, plus the export ramp)</t>
+        </is>
+      </c>
+      <c r="B18" s="39">
+        <f>Assumptions!$C$27*(1+Assumptions!$C$36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>BASE-YEAR LINES AND THE RECONCILIATION</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>CALENDAR-2025 BASE, CONSTRUCTED FROM TWO DISCLOSED HALVES</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="A21" s="12" t="inlineStr"/>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>USD / tonne</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>USD/EGP</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Revenue (EGP mn)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>FY2024/25 revenue (average of three disclosed methods)</t>
-        </is>
-      </c>
-      <c r="B22" s="17">
-        <f>(Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18)/3</f>
+          <t>Base oils</t>
+        </is>
+      </c>
+      <c r="B22" s="39">
+        <f>B18*Assumptions!$C$37</f>
+        <v/>
+      </c>
+      <c r="C22" s="17">
+        <f>E6*(1+Assumptions!$B$88)^1.5</f>
+        <v/>
+      </c>
+      <c r="D22" s="23">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="E22" s="17">
+        <f>B22*C22*D22</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>less July-December 2024 half (disclosed)</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
-        <f>Assumptions!$C$20</f>
+          <t>Paraffin wax</t>
+        </is>
+      </c>
+      <c r="B23" s="39">
+        <f>B18*(1-Assumptions!$C$37)</f>
+        <v/>
+      </c>
+      <c r="C23" s="17">
+        <f>E7*(1+Assumptions!$B$89)^1.5</f>
+        <v/>
+      </c>
+      <c r="D23" s="23">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>B23*C23*D23</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>January-June 2025</t>
-        </is>
-      </c>
-      <c r="B24" s="17">
-        <f>B22-B23</f>
+          <t>Fuel and by-products</t>
+        </is>
+      </c>
+      <c r="B24" s="39">
+        <f>B17-B18</f>
+        <v/>
+      </c>
+      <c r="C24" s="17">
+        <f>E8*(1+Assumptions!$B$90)^1.5</f>
+        <v/>
+      </c>
+      <c r="D24" s="23">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>B24*C24*D24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>plus July-December 2025 transition period (disclosed)</t>
-        </is>
-      </c>
-      <c r="B25" s="18">
-        <f>Assumptions!$C$22</f>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Bottom-up total</t>
+        </is>
+      </c>
+      <c r="E25" s="33">
+        <f>E22+E23+E24</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>CALENDAR 2025 REVENUE</t>
-        </is>
-      </c>
-      <c r="B26" s="31">
-        <f>B24+B25</f>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Calendar-2025 revenue from two disclosed halves</t>
+        </is>
+      </c>
+      <c r="E26" s="17">
+        <f>(Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18)/3-Assumptions!$C$20+Assumptions!$C$22</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Implied fuel-leg price (USD / tonne), the residual</t>
-        </is>
-      </c>
-      <c r="B27" s="17">
-        <f>(B26-B16)/B7/B13</f>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>RECONCILIATION FACTOR</t>
+        </is>
+      </c>
+      <c r="E27" s="41">
+        <f>E26/E25</f>
         <v/>
       </c>
     </row>
     <row r="28"/>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Calendar 2025 profit after tax, same construction</t>
-        </is>
-      </c>
-      <c r="B29" s="17">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Two independent routes to the same base-year revenue, agreeing within the factor shown. The factor is APPLIED to every line and every forecast year and it is on the face of the sheet — a bottom-up build that absorbs its own gap into one residual line is not a bottom-up build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>THE TWO LEG MARGINS, SOLVED FROM ONE DISCLOSED BLEND</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Specialty share of base-year revenue</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>(E22+E23)/E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Base-year blended gross margin (disclosed anchor path)</t>
+        </is>
+      </c>
+      <c r="B32" s="10">
+        <f>Assumptions!$E$95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Specialty margin as a multiple of the fuel margin</t>
+        </is>
+      </c>
+      <c r="B33" s="42">
+        <f>Assumptions!$C$38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Fuel and by-product gross margin (solved)</t>
+        </is>
+      </c>
+      <c r="B34" s="43">
+        <f>B32/(B31*B33+1-B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Specialty gross margin (solved)</t>
+        </is>
+      </c>
+      <c r="B35" s="43">
+        <f>B33*B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Check: the two remix to the disclosed blend</t>
+        </is>
+      </c>
+      <c r="B36" s="43">
+        <f>B31*B35+(1-B31)*B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>THE FORECAST</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr"/>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Base oils — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C40" s="39">
+        <f>B22*(1+Assumptions!$B$85)</f>
+        <v/>
+      </c>
+      <c r="D40" s="39">
+        <f>C40*(1+Assumptions!$C$85)</f>
+        <v/>
+      </c>
+      <c r="E40" s="39">
+        <f>D40*(1+Assumptions!$D$85)</f>
+        <v/>
+      </c>
+      <c r="F40" s="39">
+        <f>E40*(1+Assumptions!$E$85)</f>
+        <v/>
+      </c>
+      <c r="G40" s="39">
+        <f>F40*(1+Assumptions!$F$85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Paraffin wax — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C41" s="39">
+        <f>B23*(1+Assumptions!$B$86)</f>
+        <v/>
+      </c>
+      <c r="D41" s="39">
+        <f>C41*(1+Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="E41" s="39">
+        <f>D41*(1+Assumptions!$D$86)</f>
+        <v/>
+      </c>
+      <c r="F41" s="39">
+        <f>E41*(1+Assumptions!$E$86)</f>
+        <v/>
+      </c>
+      <c r="G41" s="39">
+        <f>F41*(1+Assumptions!$F$86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Fuel and by-products — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C42" s="39">
+        <f>B24*(1+Assumptions!$B$87)</f>
+        <v/>
+      </c>
+      <c r="D42" s="39">
+        <f>C42*(1+Assumptions!$C$87)</f>
+        <v/>
+      </c>
+      <c r="E42" s="39">
+        <f>D42*(1+Assumptions!$D$87)</f>
+        <v/>
+      </c>
+      <c r="F42" s="39">
+        <f>E42*(1+Assumptions!$E$87)</f>
+        <v/>
+      </c>
+      <c r="G42" s="39">
+        <f>F42*(1+Assumptions!$F$87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Base oils — USD / tonne</t>
+        </is>
+      </c>
+      <c r="C43" s="17">
+        <f>C22*(1+Assumptions!$B$88)</f>
+        <v/>
+      </c>
+      <c r="D43" s="17">
+        <f>C43*(1+Assumptions!$C$88)</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f>D43*(1+Assumptions!$D$88)</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>E43*(1+Assumptions!$E$88)</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>F43*(1+Assumptions!$F$88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Paraffin wax — USD / tonne</t>
+        </is>
+      </c>
+      <c r="C44" s="17">
+        <f>C23*(1+Assumptions!$B$89)</f>
+        <v/>
+      </c>
+      <c r="D44" s="17">
+        <f>C44*(1+Assumptions!$C$89)</f>
+        <v/>
+      </c>
+      <c r="E44" s="17">
+        <f>D44*(1+Assumptions!$D$89)</f>
+        <v/>
+      </c>
+      <c r="F44" s="17">
+        <f>E44*(1+Assumptions!$E$89)</f>
+        <v/>
+      </c>
+      <c r="G44" s="17">
+        <f>F44*(1+Assumptions!$F$89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Fuel and by-products — USD / tonne</t>
+        </is>
+      </c>
+      <c r="C45" s="17">
+        <f>C24*(1+Assumptions!$B$90)</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>C45*(1+Assumptions!$C$90)</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f>D45*(1+Assumptions!$D$90)</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>E45*(1+Assumptions!$E$90)</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>F45*(1+Assumptions!$F$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>USD/EGP average</t>
+        </is>
+      </c>
+      <c r="C46" s="23">
+        <f>Assumptions!$B$82</f>
+        <v/>
+      </c>
+      <c r="D46" s="23">
+        <f>Assumptions!$C$82</f>
+        <v/>
+      </c>
+      <c r="E46" s="23">
+        <f>Assumptions!$D$82</f>
+        <v/>
+      </c>
+      <c r="F46" s="23">
+        <f>Assumptions!$E$82</f>
+        <v/>
+      </c>
+      <c r="G46" s="23">
+        <f>Assumptions!$F$82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Base oils — revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C47" s="17">
+        <f>C40*C43*C46*$E$27</f>
+        <v/>
+      </c>
+      <c r="D47" s="17">
+        <f>D40*D43*D46*$E$27</f>
+        <v/>
+      </c>
+      <c r="E47" s="17">
+        <f>E40*E43*E46*$E$27</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>F40*F43*F46*$E$27</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>G40*G43*G46*$E$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Paraffin wax — revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C48" s="17">
+        <f>C41*C44*C46*$E$27</f>
+        <v/>
+      </c>
+      <c r="D48" s="17">
+        <f>D41*D44*D46*$E$27</f>
+        <v/>
+      </c>
+      <c r="E48" s="17">
+        <f>E41*E44*E46*$E$27</f>
+        <v/>
+      </c>
+      <c r="F48" s="17">
+        <f>F41*F44*F46*$E$27</f>
+        <v/>
+      </c>
+      <c r="G48" s="17">
+        <f>G41*G44*G46*$E$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Fuel and by-products — revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C49" s="17">
+        <f>C42*C45*C46*$E$27</f>
+        <v/>
+      </c>
+      <c r="D49" s="17">
+        <f>D42*D45*D46*$E$27</f>
+        <v/>
+      </c>
+      <c r="E49" s="17">
+        <f>E42*E45*E46*$E$27</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>F42*F45*F46*$E$27</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>G42*G45*G46*$E$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="C50" s="33">
+        <f>C47+C48+C49</f>
+        <v/>
+      </c>
+      <c r="D50" s="33">
+        <f>D47+D48+D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="33">
+        <f>E47+E48+E49</f>
+        <v/>
+      </c>
+      <c r="F50" s="33">
+        <f>F47+F48+F49</f>
+        <v/>
+      </c>
+      <c r="G50" s="33">
+        <f>G47+G48+G49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Specialty share of revenue</t>
+        </is>
+      </c>
+      <c r="C51" s="16">
+        <f>(C47+C48)/C50</f>
+        <v/>
+      </c>
+      <c r="D51" s="16">
+        <f>(D47+D48)/D50</f>
+        <v/>
+      </c>
+      <c r="E51" s="16">
+        <f>(E47+E48)/E50</f>
+        <v/>
+      </c>
+      <c r="F51" s="16">
+        <f>(F47+F48)/F50</f>
+        <v/>
+      </c>
+      <c r="G51" s="16">
+        <f>(G47+G48)/G50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>GROSS PROFIT — the two leg margins on that mix</t>
+        </is>
+      </c>
+      <c r="C52" s="33">
+        <f>(C47+C48)*$B$35+C49*$B$34</f>
+        <v/>
+      </c>
+      <c r="D52" s="33">
+        <f>(D47+D48)*$B$35+D49*$B$34</f>
+        <v/>
+      </c>
+      <c r="E52" s="33">
+        <f>(E47+E48)*$B$35+E49*$B$34</f>
+        <v/>
+      </c>
+      <c r="F52" s="33">
+        <f>(F47+F48)*$B$35+F49*$B$34</f>
+        <v/>
+      </c>
+      <c r="G52" s="33">
+        <f>(G47+G48)*$B$35+G49*$B$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>BLENDED GROSS MARGIN — an output, not an input</t>
+        </is>
+      </c>
+      <c r="C53" s="44">
+        <f>C52/C50</f>
+        <v/>
+      </c>
+      <c r="D53" s="44">
+        <f>D52/D50</f>
+        <v/>
+      </c>
+      <c r="E53" s="44">
+        <f>E52/E50</f>
+        <v/>
+      </c>
+      <c r="F53" s="44">
+        <f>F52/F50</f>
+        <v/>
+      </c>
+      <c r="G53" s="44">
+        <f>G52/G50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Total tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C54" s="39">
+        <f>C40+C41+C42</f>
+        <v/>
+      </c>
+      <c r="D54" s="39">
+        <f>D40+D41+D42</f>
+        <v/>
+      </c>
+      <c r="E54" s="39">
+        <f>E40+E41+E42</f>
+        <v/>
+      </c>
+      <c r="F54" s="39">
+        <f>F40+F41+F42</f>
+        <v/>
+      </c>
+      <c r="G54" s="39">
+        <f>G40+G41+G42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Calendar-2025 profit after tax, same halves construction</t>
+        </is>
+      </c>
+      <c r="B56" s="17">
         <f>(Assumptions!$C$19-Assumptions!$C$21)+Assumptions!$C$23</f>
         <v/>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
-        <is>
-          <t>Every cell on this sheet is a formula. The base-year fuel price is deliberately the residual: the specialty leg is priced off an observable and the fuel leg absorbs whatever is left, so the split can be checked against a plausible gas-oil / naphtha / fuel-oil realisation rather than being fitted to a target.</t>
+    <row r="57"/>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="21" t="inlineStr">
+        <is>
+          <t>The blended margin widens across the forecast ONLY because the specialty share of revenue rises against two fixed leg margins. Neither leg margin improves. That is what "the margin widens on mix" has to mean if it is to mean anything, and it is now a property of the arithmetic on this sheet rather than a caption on a chart.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A31:G31"/>
+  <mergeCells count="3">
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A29:H29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7710,7 +9315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7771,7 +9376,7 @@
         </is>
       </c>
       <c r="B6" s="19">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
     </row>
@@ -7792,7 +9397,7 @@
           <t>Year-2 discount factor</t>
         </is>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="45">
         <f>DCF!C19</f>
         <v/>
       </c>
@@ -7811,241 +9416,252 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>add the interim free cash flow the multiple year does not cover</t>
+        </is>
+      </c>
+      <c r="B10" s="17">
+        <f>DCF!B20+DCF!C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>less net debt (net cash added)</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B11" s="18">
         <f>DCF!$B$49</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>IMPLIED VALUE PER SHARE (EGP)</t>
         </is>
       </c>
-      <c r="B11" s="14">
-        <f>(B9-B10)*(1-Assumptions!$C$61)/Assumptions!$C$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Trailing enterprise value / EBITDA (company)</t>
-        </is>
-      </c>
-      <c r="B12" s="36">
-        <f>(Assumptions!$C$5*Assumptions!$C$6+DCF!$B$49)/'Income Statement'!E9</f>
+      <c r="B12" s="14">
+        <f>(B9+B10)*(1-Assumptions!$C$70)/Assumptions!$C$6-B11/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>Trailing enterprise value / EBITDA (company)</t>
+        </is>
+      </c>
+      <c r="B13" s="46">
+        <f>(Assumptions!$C$5*Assumptions!$C$6+DCF!$B$49)/'Income Statement'!E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>Trailing price / earnings (company)</t>
         </is>
       </c>
-      <c r="B13" s="36">
+      <c r="B14" s="46">
         <f>Assumptions!$C$5/'Income Statement'!E20</f>
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>LENS 3 — NORMALISED EARNINGS POWER</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2028E EBITDA</t>
-        </is>
-      </c>
-      <c r="B16" s="18">
-        <f>DCF!D9</f>
-        <v/>
-      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>less depreciation and amortisation</t>
+          <t>2028E EBITDA</t>
         </is>
       </c>
       <c r="B17" s="18">
-        <f>DCF!D11</f>
+        <f>DCF!D9</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B18" s="17">
-        <f>B16-B17</f>
+          <t>less depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B18" s="18">
+        <f>DCF!D11</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>add net finance income</t>
-        </is>
-      </c>
-      <c r="B19" s="18">
-        <f>'Cash Flow'!D16</f>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B19" s="17">
+        <f>B17-B18</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Attributable normalised earnings</t>
-        </is>
-      </c>
-      <c r="B20" s="17">
-        <f>(B18+B19)*(1-Assumptions!$C$52)*(1-Assumptions!$C$61)</f>
+          <t>add net finance income</t>
+        </is>
+      </c>
+      <c r="B20" s="18">
+        <f>'Cash Flow'!D16</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Normalised earnings per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B21" s="20">
-        <f>B20/Assumptions!$C$6</f>
+          <t>Attributable normalised earnings</t>
+        </is>
+      </c>
+      <c r="B21" s="17">
+        <f>(B19+B20)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
+          <t>Normalised earnings per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B22" s="20">
+        <f>B21/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="B22" s="19">
-        <f>Assumptions!$C$64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B23" s="19">
+        <f>Assumptions!$C$75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>IMPLIED VALUE PER SHARE (EGP)</t>
         </is>
       </c>
-      <c r="B23" s="14">
-        <f>B21*B22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="B24" s="14">
+        <f>B22*B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>LENS 4 — BOOK VALUE AND SUSTAINABLE RETURN</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Attributable book value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B26" s="20">
-        <f>'Balance Sheet'!E20/Assumptions!$C$6</f>
-        <v/>
-      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="B27" s="9">
-        <f>Assumptions!$C$65</f>
+          <t>Attributable book value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B27" s="20">
+        <f>'Balance Sheet'!E20/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Perpetual cost of equity</t>
-        </is>
-      </c>
-      <c r="B28" s="10">
-        <f>DCF!$B$59</f>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Perpetual cost of equity</t>
         </is>
       </c>
       <c r="B29" s="10">
-        <f>Assumptions!$C$57</f>
+        <f>DCF!$B$59</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B30" s="10">
+        <f>Assumptions!$C$66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="B30" s="36">
-        <f>(B27-B29)/(B28-B29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="B31" s="46">
+        <f>(B28-B30)/(B29-B30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>IMPLIED VALUE PER SHARE (EGP)</t>
         </is>
       </c>
-      <c r="B31" s="14">
-        <f>B30*B26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="B32" s="14">
+        <f>B31*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Trailing return on average attributable equity</t>
         </is>
       </c>
-      <c r="B32" s="16">
+      <c r="B33" s="16">
         <f>'Income Statement'!E19/(('Balance Sheet'!D20+'Balance Sheet'!E20)/2)</f>
         <v/>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
+    <row r="34"/>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>The relative lens discounts a FORWARD enterprise value back to today; a multiple applied to a future year produces a value as at that year, not now. The book lens uses the PERPETUAL cost of equity inside the perpetuity identity, because a blended rate inside a perpetuity formula is internally inconsistent.</t>
         </is>
@@ -8053,7 +9669,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8137,50 +9753,50 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>'Product Legs'!$C$18</f>
+        <f>'Product Lines'!$C$50</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>'Product Legs'!$D$18</f>
+        <f>'Product Lines'!$D$50</f>
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>'Product Legs'!$E$18</f>
+        <f>'Product Lines'!$E$50</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>'Product Legs'!$F$18</f>
+        <f>'Product Lines'!$F$50</f>
         <v/>
       </c>
       <c r="F5" s="18">
-        <f>'Product Legs'!$G$18</f>
+        <f>'Product Lines'!$G$50</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Gross margin (from the product-line mix)</t>
         </is>
       </c>
       <c r="B6" s="10">
-        <f>Assumptions!$B$73</f>
+        <f>'Product Lines'!$C$53</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>Assumptions!$C$73</f>
+        <f>'Product Lines'!$D$53</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>Assumptions!$D$73</f>
+        <f>'Product Lines'!$E$53</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>Assumptions!$E$73</f>
+        <f>'Product Lines'!$F$53</f>
         <v/>
       </c>
       <c r="F6" s="10">
-        <f>Assumptions!$F$73</f>
+        <f>'Product Lines'!$G$53</f>
         <v/>
       </c>
     </row>
@@ -8190,24 +9806,24 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B7" s="17">
-        <f>B5*B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="17">
-        <f>C5*C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="17">
-        <f>D5*D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="17">
-        <f>E5*E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="17">
-        <f>F5*F6</f>
+      <c r="B7" s="18">
+        <f>'Product Lines'!$C$52</f>
+        <v/>
+      </c>
+      <c r="C7" s="18">
+        <f>'Product Lines'!$D$52</f>
+        <v/>
+      </c>
+      <c r="D7" s="18">
+        <f>'Product Lines'!$E$52</f>
+        <v/>
+      </c>
+      <c r="E7" s="18">
+        <f>'Product Lines'!$F$52</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>'Product Lines'!$G$52</f>
         <v/>
       </c>
     </row>
@@ -8218,23 +9834,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B5*Assumptions!$B$72</f>
+        <f>B5*Assumptions!$B$84</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C5*Assumptions!$C$72</f>
+        <f>C5*Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D5*Assumptions!$D$72</f>
+        <f>D5*Assumptions!$D$84</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E5*Assumptions!$E$72</f>
+        <f>E5*Assumptions!$E$84</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>F5*Assumptions!$F$72</f>
+        <f>F5*Assumptions!$F$84</f>
         <v/>
       </c>
     </row>
@@ -8244,23 +9860,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="33">
         <f>B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="33">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="33">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="33">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="33">
         <f>F7-F8</f>
         <v/>
       </c>
@@ -8299,23 +9915,23 @@
         </is>
       </c>
       <c r="B11" s="17">
-        <f>B5*Assumptions!$C$60</f>
+        <f>B5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>C5*Assumptions!$C$60</f>
+        <f>C5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>D5*Assumptions!$C$60</f>
+        <f>D5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>E5*Assumptions!$C$60</f>
+        <f>E5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>F5*Assumptions!$C$60</f>
+        <f>F5*Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
@@ -8325,23 +9941,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="33">
         <f>B9-B11</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="33">
         <f>C9-C11</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="33">
         <f>D9-D11</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="33">
         <f>E9-E11</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="33">
         <f>F9-F11</f>
         <v/>
       </c>
@@ -8353,23 +9969,23 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>B12*(1-Assumptions!$C$52)</f>
+        <f>B12*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>C12*(1-Assumptions!$C$52)</f>
+        <f>C12*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>D12*(1-Assumptions!$C$52)</f>
+        <f>D12*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>E12*(1-Assumptions!$C$52)</f>
+        <f>E12*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>F12*(1-Assumptions!$C$52)</f>
+        <f>F12*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
     </row>
@@ -8407,23 +10023,23 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>B5*Assumptions!$B$71</f>
+        <f>B5*Assumptions!$B$83</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>C5*Assumptions!$C$71</f>
+        <f>C5*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>D5*Assumptions!$D$71</f>
+        <f>D5*Assumptions!$D$83</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>E5*Assumptions!$E$71</f>
+        <f>E5*Assumptions!$E$83</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>F5*Assumptions!$F$71</f>
+        <f>F5*Assumptions!$F$83</f>
         <v/>
       </c>
     </row>
@@ -8434,23 +10050,23 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>B5*'Balance Sheet'!$C$26</f>
+        <f>B5*'Balance Sheet'!$E$26</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>C5*'Balance Sheet'!$C$26</f>
+        <f>C5*'Balance Sheet'!$E$26</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>D5*'Balance Sheet'!$C$26</f>
+        <f>D5*'Balance Sheet'!$E$26</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>E5*'Balance Sheet'!$C$26</f>
+        <f>E5*'Balance Sheet'!$E$26</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>F5*'Balance Sheet'!$C$26</f>
+        <f>F5*'Balance Sheet'!$E$26</f>
         <v/>
       </c>
     </row>
@@ -8487,23 +10103,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="33">
         <f>B13+B11-B15-B17</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="33">
         <f>C13+C11-C15-C17</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="33">
         <f>D13+D11-D15-D17</f>
         <v/>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="33">
         <f>E13+E11-E15-E17</f>
         <v/>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="33">
         <f>F13+F11-F15-F17</f>
         <v/>
       </c>
@@ -8514,23 +10130,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="25">
         <f>B69</f>
         <v/>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="25">
         <f>C69</f>
         <v/>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="25">
         <f>D69</f>
         <v/>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="25">
         <f>E69</f>
         <v/>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="25">
         <f>F69</f>
         <v/>
       </c>
@@ -8541,23 +10157,23 @@
           <t>PRESENT VALUE OF FREE CASH FLOW</t>
         </is>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="33">
         <f>B18*B19</f>
         <v/>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="33">
         <f>C18*C19</f>
         <v/>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="33">
         <f>D18*D19</f>
         <v/>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="33">
         <f>E18*E19</f>
         <v/>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="33">
         <f>F18*F19</f>
         <v/>
       </c>
@@ -8664,7 +10280,7 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>Assumptions!$C$57</f>
+        <f>Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -8707,7 +10323,7 @@
           <t>TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="33">
         <f>B29*(1-B28)/(B62-B26)</f>
         <v/>
       </c>
@@ -8765,7 +10381,7 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="33">
         <f>B33+B34</f>
         <v/>
       </c>
@@ -8776,7 +10392,7 @@
           <t>Fair value per share (from the bridge)</t>
         </is>
       </c>
-      <c r="B37" s="38">
+      <c r="B37" s="47">
         <f>'EV Bridge'!$B$12</f>
         <v/>
       </c>
@@ -8809,7 +10425,7 @@
         </is>
       </c>
       <c r="B41" s="10">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -8820,7 +10436,7 @@
         </is>
       </c>
       <c r="B42" s="10">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -8830,7 +10446,7 @@
           <t>Risk-free net of sovereign risk</t>
         </is>
       </c>
-      <c r="B43" s="39">
+      <c r="B43" s="43">
         <f>B41-B42</f>
         <v/>
       </c>
@@ -8841,8 +10457,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B44" s="40">
-        <f>Assumptions!$C$49</f>
+      <c r="B44" s="48">
+        <f>Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -8853,7 +10469,7 @@
         </is>
       </c>
       <c r="B45" s="10">
-        <f>Assumptions!$C$48</f>
+        <f>Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -8863,7 +10479,7 @@
           <t>Cost of equity</t>
         </is>
       </c>
-      <c r="B46" s="41">
+      <c r="B46" s="44">
         <f>B43+B44*B45</f>
         <v/>
       </c>
@@ -8874,8 +10490,8 @@
           <t>Gross debt</t>
         </is>
       </c>
-      <c r="B47" s="32">
-        <f>Assumptions!$C$38</f>
+      <c r="B47" s="23">
+        <f>Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -8886,7 +10502,7 @@
         </is>
       </c>
       <c r="B48" s="18">
-        <f>Assumptions!$C$37</f>
+        <f>Assumptions!$C$45</f>
         <v/>
       </c>
     </row>
@@ -8940,8 +10556,8 @@
           <t>After-tax cost of net debt</t>
         </is>
       </c>
-      <c r="B53" s="39">
-        <f>(Assumptions!$C$50*B47-Assumptions!$C$51*B48)/(B47-B48)*(1-Assumptions!$C$52)</f>
+      <c r="B53" s="43">
+        <f>(Assumptions!$C$59*B47-Assumptions!$C$60*B48)/(B47-B48)*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
     </row>
@@ -8951,7 +10567,7 @@
           <t>WEIGHTED COST OF CAPITAL — EXPLICIT</t>
         </is>
       </c>
-      <c r="B54" s="41">
+      <c r="B54" s="44">
         <f>B52*B46+B51*B53</f>
         <v/>
       </c>
@@ -8977,7 +10593,7 @@
         </is>
       </c>
       <c r="B57" s="10">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$62</f>
         <v/>
       </c>
     </row>
@@ -8988,7 +10604,7 @@
         </is>
       </c>
       <c r="B58" s="10">
-        <f>Assumptions!$C$54</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -8998,7 +10614,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="B59" s="39">
+      <c r="B59" s="43">
         <f>B57+B44*B58</f>
         <v/>
       </c>
@@ -9009,8 +10625,8 @@
           <t>Terminal after-tax cost of debt</t>
         </is>
       </c>
-      <c r="B60" s="39">
-        <f>Assumptions!$C$55*(1-Assumptions!$C$52)</f>
+      <c r="B60" s="43">
+        <f>Assumptions!$C$64*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
     </row>
@@ -9021,7 +10637,7 @@
         </is>
       </c>
       <c r="B61" s="9">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -9031,7 +10647,7 @@
           <t>WEIGHTED COST OF CAPITAL — TERMINAL</t>
         </is>
       </c>
-      <c r="B62" s="41">
+      <c r="B62" s="44">
         <f>(1-B61)*B59+B61*B60</f>
         <v/>
       </c>
@@ -9085,23 +10701,23 @@
         </is>
       </c>
       <c r="B66" s="10">
-        <f>Assumptions!$B$69</f>
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
       <c r="C66" s="10">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="D66" s="10">
-        <f>Assumptions!$D$69</f>
+        <f>Assumptions!$D$81</f>
         <v/>
       </c>
       <c r="E66" s="10">
-        <f>Assumptions!$E$69</f>
+        <f>Assumptions!$E$81</f>
         <v/>
       </c>
       <c r="F66" s="10">
-        <f>Assumptions!$F$69</f>
+        <f>Assumptions!$F$81</f>
         <v/>
       </c>
     </row>
@@ -9111,23 +10727,23 @@
           <t>Cumulative progress (glide fraction)</t>
         </is>
       </c>
-      <c r="B67" s="42">
+      <c r="B67" s="49">
         <f>(B66-B66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="C67" s="42">
+      <c r="C67" s="49">
         <f>(B66-C66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="D67" s="42">
+      <c r="D67" s="49">
         <f>(B66-D66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="E67" s="42">
+      <c r="E67" s="49">
         <f>(B66-E66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="F67" s="42">
+      <c r="F67" s="49">
         <f>(B66-F66)/(B66-F66)</f>
         <v/>
       </c>
@@ -9138,23 +10754,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B68" s="41">
+      <c r="B68" s="44">
         <f>$B$54-($B$54-$B$62)*B67</f>
         <v/>
       </c>
-      <c r="C68" s="41">
+      <c r="C68" s="44">
         <f>$B$54-($B$54-$B$62)*C67</f>
         <v/>
       </c>
-      <c r="D68" s="41">
+      <c r="D68" s="44">
         <f>$B$54-($B$54-$B$62)*D67</f>
         <v/>
       </c>
-      <c r="E68" s="41">
+      <c r="E68" s="44">
         <f>$B$54-($B$54-$B$62)*E67</f>
         <v/>
       </c>
-      <c r="F68" s="41">
+      <c r="F68" s="44">
         <f>$B$54-($B$54-$B$62)*F67</f>
         <v/>
       </c>
@@ -9165,23 +10781,23 @@
           <t>Cumulative discount factor</t>
         </is>
       </c>
-      <c r="B69" s="37">
+      <c r="B69" s="25">
         <f>1/(1+B68)</f>
         <v/>
       </c>
-      <c r="C69" s="37">
+      <c r="C69" s="25">
         <f>B69/(1+C68)</f>
         <v/>
       </c>
-      <c r="D69" s="37">
+      <c r="D69" s="25">
         <f>C69/(1+D68)</f>
         <v/>
       </c>
-      <c r="E69" s="37">
+      <c r="E69" s="25">
         <f>D69/(1+E68)</f>
         <v/>
       </c>
-      <c r="F69" s="37">
+      <c r="F69" s="25">
         <f>E69/(1+F68)</f>
         <v/>
       </c>
@@ -9307,12 +10923,12 @@
         <f>(Assumptions!$C$13+Assumptions!$C$14)/2</f>
         <v/>
       </c>
-      <c r="D5" s="18">
-        <f>'Product Legs'!B22</f>
+      <c r="D5" s="17">
+        <f>(Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18)/3</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>'Product Legs'!B26</f>
+        <f>'Product Lines'!E26</f>
         <v/>
       </c>
       <c r="F5" s="18">
@@ -9343,39 +10959,39 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>Assumptions!$B$82</f>
+        <f>Assumptions!$B$95</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>Assumptions!$C$82</f>
+        <f>Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>Assumptions!$D$82</f>
+        <f>Assumptions!$D$95</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>Assumptions!$E$82</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>Assumptions!$B$73</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>Assumptions!$C$73</f>
-        <v/>
-      </c>
-      <c r="H6" s="16">
-        <f>Assumptions!$D$73</f>
-        <v/>
-      </c>
-      <c r="I6" s="16">
-        <f>Assumptions!$E$73</f>
-        <v/>
-      </c>
-      <c r="J6" s="16">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$E$95</f>
+        <v/>
+      </c>
+      <c r="F6" s="9">
+        <f>DCF!B6</f>
+        <v/>
+      </c>
+      <c r="G6" s="9">
+        <f>DCF!C6</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>DCF!D6</f>
+        <v/>
+      </c>
+      <c r="I6" s="9">
+        <f>DCF!E6</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>DCF!F6</f>
         <v/>
       </c>
     </row>
@@ -9429,19 +11045,19 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B5*Assumptions!$B$72</f>
+        <f>B5*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C5*Assumptions!$B$72</f>
+        <f>C5*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D5*Assumptions!$B$72</f>
+        <f>D5*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E5*Assumptions!$B$72</f>
+        <f>E5*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="F8" s="18">
@@ -9471,39 +11087,39 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="33">
         <f>B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="33">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="33">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="33">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="33">
         <f>F7-F8</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="33">
         <f>G7-G8</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="33">
         <f>H7-H8</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="33">
         <f>I7-I8</f>
         <v/>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="33">
         <f>J7-J8</f>
         <v/>
       </c>
@@ -9558,19 +11174,19 @@
         </is>
       </c>
       <c r="B11" s="17">
-        <f>B5*Assumptions!$C$60</f>
+        <f>B5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>C5*Assumptions!$C$60</f>
+        <f>C5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>D5*Assumptions!$C$60</f>
+        <f>D5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>E5*Assumptions!$C$60</f>
+        <f>E5*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="F11" s="18">
@@ -9600,39 +11216,39 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="33">
         <f>B9-B11</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="33">
         <f>C9-C11</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="33">
         <f>D9-D11</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="33">
         <f>E9-E11</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="33">
         <f>F9-F11</f>
         <v/>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="33">
         <f>G9-G11</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="33">
         <f>H9-H11</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="33">
         <f>I9-I11</f>
         <v/>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="33">
         <f>J9-J11</f>
         <v/>
       </c>
@@ -9656,7 +11272,7 @@
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>Assumptions!$C$51*Assumptions!$C$37-Assumptions!$C$50*Assumptions!$C$38</f>
+        <f>Assumptions!$C$60*Assumptions!$C$45-Assumptions!$C$59*Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="F13" s="18">
@@ -9686,36 +11302,40 @@
           <t>Profit after tax (disclosed for history)</t>
         </is>
       </c>
-      <c r="B14" s="43" t="n">
-        <v>1320</v>
-      </c>
-      <c r="C14" s="43" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D14" s="43" t="n">
-        <v>1550</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>1562.828</v>
-      </c>
-      <c r="F14" s="31">
-        <f>(F12+F13)*(1-Assumptions!$C$52)</f>
-        <v/>
-      </c>
-      <c r="G14" s="31">
-        <f>(G12+G13)*(1-Assumptions!$C$52)</f>
-        <v/>
-      </c>
-      <c r="H14" s="31">
-        <f>(H12+H13)*(1-Assumptions!$C$52)</f>
-        <v/>
-      </c>
-      <c r="I14" s="31">
-        <f>(I12+I13)*(1-Assumptions!$C$52)</f>
-        <v/>
-      </c>
-      <c r="J14" s="31">
-        <f>(J12+J13)*(1-Assumptions!$C$52)</f>
+      <c r="B14" s="33">
+        <f>Assumptions!$C$12</f>
+        <v/>
+      </c>
+      <c r="C14" s="33">
+        <f>Assumptions!$C$15</f>
+        <v/>
+      </c>
+      <c r="D14" s="33">
+        <f>Assumptions!$C$19</f>
+        <v/>
+      </c>
+      <c r="E14" s="33">
+        <f>'Product Lines'!B56</f>
+        <v/>
+      </c>
+      <c r="F14" s="33">
+        <f>(F12+F13)*(1-Assumptions!$C$61)</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>(G12+G13)*(1-Assumptions!$C$61)</f>
+        <v/>
+      </c>
+      <c r="H14" s="33">
+        <f>(H12+H13)*(1-Assumptions!$C$61)</f>
+        <v/>
+      </c>
+      <c r="I14" s="33">
+        <f>(I12+I13)*(1-Assumptions!$C$61)</f>
+        <v/>
+      </c>
+      <c r="J14" s="33">
+        <f>(J12+J13)*(1-Assumptions!$C$61)</f>
         <v/>
       </c>
     </row>
@@ -9726,39 +11346,39 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>B14/(1-Assumptions!$C$52)</f>
+        <f>B14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>C14/(1-Assumptions!$C$52)</f>
+        <f>C14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>D14/(1-Assumptions!$C$52)</f>
+        <f>D14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>E14/(1-Assumptions!$C$52)</f>
+        <f>E14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>F14/(1-Assumptions!$C$52)</f>
+        <f>F14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="G15" s="17">
-        <f>G14/(1-Assumptions!$C$52)</f>
+        <f>G14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>H14/(1-Assumptions!$C$52)</f>
+        <f>H14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>I14/(1-Assumptions!$C$52)</f>
+        <f>I14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>J14/(1-Assumptions!$C$52)</f>
+        <f>J14/(1-Assumptions!$C$61)</f>
         <v/>
       </c>
     </row>
@@ -9855,39 +11475,39 @@
         </is>
       </c>
       <c r="B18" s="17">
-        <f>B14*Assumptions!$C$61</f>
+        <f>B14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>C14*Assumptions!$C$61</f>
+        <f>C14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>D14*Assumptions!$C$61</f>
+        <f>D14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>E14*Assumptions!$C$61</f>
+        <f>E14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>F14*Assumptions!$C$61</f>
+        <f>F14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>G14*Assumptions!$C$61</f>
+        <f>G14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>H14*Assumptions!$C$61</f>
+        <f>H14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I18" s="17">
-        <f>I14*Assumptions!$C$61</f>
+        <f>I14*Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>J14*Assumptions!$C$61</f>
+        <f>J14*Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -9897,39 +11517,39 @@
           <t>PROFIT ATTRIBUTABLE TO SHAREHOLDERS</t>
         </is>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="33">
         <f>B14-B18</f>
         <v/>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="33">
         <f>C14-C18</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="33">
         <f>D14-D18</f>
         <v/>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="33">
         <f>E14-E18</f>
         <v/>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="33">
         <f>F14-F18</f>
         <v/>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="33">
         <f>G14-G18</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="33">
         <f>H14-H18</f>
         <v/>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="33">
         <f>I14-I18</f>
         <v/>
       </c>
-      <c r="J19" s="31">
+      <c r="J19" s="33">
         <f>J14-J18</f>
         <v/>
       </c>

--- a/engine/amoc_study/AMOC_Valuation_Model_06082026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_06082026_public.xlsx
@@ -38,8 +38,8 @@
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.00x"/>
-    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="171" formatCode="0.00x"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -141,7 +141,7 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -149,14 +149,16 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,15 +167,13 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1421,7 +1421,7 @@
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>Assumptions!$C$43-Assumptions!$C$45-E10-E11-Assumptions!$C$50</f>
+        <f>Assumptions!$C$68-Assumptions!$C$70-E10-E11-Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F9" s="18">
@@ -1452,39 +1452,39 @@
         </is>
       </c>
       <c r="B10" s="17">
-        <f>B6*Assumptions!$C$48/365</f>
+        <f>B6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="C10" s="17">
-        <f>C6*Assumptions!$C$48/365</f>
+        <f>C6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="D10" s="17">
-        <f>D6*Assumptions!$C$48/365</f>
+        <f>D6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="E10" s="17">
-        <f>E6*Assumptions!$C$48/365</f>
+        <f>E6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>F6*Assumptions!$C$48/365</f>
+        <f>F6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="G10" s="17">
-        <f>G6*Assumptions!$C$48/365</f>
+        <f>G6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>H6*Assumptions!$C$48/365</f>
+        <f>H6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>I6*Assumptions!$C$48/365</f>
+        <f>I6*Assumptions!$C$73/365</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>J6*Assumptions!$C$48/365</f>
+        <f>J6*Assumptions!$C$73/365</f>
         <v/>
       </c>
     </row>
@@ -1495,39 +1495,39 @@
         </is>
       </c>
       <c r="B11" s="17">
-        <f>B5*Assumptions!$C$47/365</f>
+        <f>B5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>C5*Assumptions!$C$47/365</f>
+        <f>C5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>D5*Assumptions!$C$47/365</f>
+        <f>D5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>E5*Assumptions!$C$47/365</f>
+        <f>E5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>F5*Assumptions!$C$47/365</f>
+        <f>F5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>G5*Assumptions!$C$47/365</f>
+        <f>G5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>H5*Assumptions!$C$47/365</f>
+        <f>H5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>I5*Assumptions!$C$47/365</f>
+        <f>I5*Assumptions!$C$72/365</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>J5*Assumptions!$C$47/365</f>
+        <f>J5*Assumptions!$C$72/365</f>
         <v/>
       </c>
     </row>
@@ -1538,39 +1538,39 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="C12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="D12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="E12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="J12" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -1581,39 +1581,39 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>B20+B21+B17+B19+Assumptions!$C$46-B9-B10-B11-Assumptions!$C$50</f>
+        <f>B20+B21+B17+B19+Assumptions!$C$71-B9-B10-B11-Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>C20+C21+C17+C19+Assumptions!$C$46-C9-C10-C11-Assumptions!$C$50</f>
+        <f>C20+C21+C17+C19+Assumptions!$C$71-C9-C10-C11-Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>D20+D21+D17+D19+Assumptions!$C$46-D9-D10-D11-Assumptions!$C$50</f>
+        <f>D20+D21+D17+D19+Assumptions!$C$71-D9-D10-D11-Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>Assumptions!$C$45</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>Assumptions!$C$46-'Cash Flow'!B$22</f>
+        <f>Assumptions!$C$71-'Cash Flow'!B$22</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>Assumptions!$C$46-'Cash Flow'!C$22</f>
+        <f>Assumptions!$C$71-'Cash Flow'!C$22</f>
         <v/>
       </c>
       <c r="H13" s="17">
-        <f>Assumptions!$C$46-'Cash Flow'!D$22</f>
+        <f>Assumptions!$C$71-'Cash Flow'!D$22</f>
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>Assumptions!$C$46-'Cash Flow'!E$22</f>
+        <f>Assumptions!$C$71-'Cash Flow'!E$22</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>Assumptions!$C$46-'Cash Flow'!F$22</f>
+        <f>Assumptions!$C$71-'Cash Flow'!F$22</f>
         <v/>
       </c>
     </row>
@@ -1623,39 +1623,39 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="35">
         <f>B9+B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="35">
         <f>C9+C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="35">
         <f>D9+D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="35">
         <f>E9+E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="35">
         <f>F9+F10+F11+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="35">
         <f>G9+G10+G11+G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="35">
         <f>H9+H10+H11+H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="35">
         <f>I9+I10+I11+I12+I13</f>
         <v/>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="35">
         <f>J9+J10+J11+J12+J13</f>
         <v/>
       </c>
@@ -1685,39 +1685,39 @@
         </is>
       </c>
       <c r="B17" s="17">
-        <f>B6*Assumptions!$C$49/365</f>
+        <f>B6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>C6*Assumptions!$C$49/365</f>
+        <f>C6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>D6*Assumptions!$C$49/365</f>
+        <f>D6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>E6*Assumptions!$C$49/365</f>
+        <f>E6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>F6*Assumptions!$C$49/365</f>
+        <f>F6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>G6*Assumptions!$C$49/365</f>
+        <f>G6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>H6*Assumptions!$C$49/365</f>
+        <f>H6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>I6*Assumptions!$C$49/365</f>
+        <f>I6*Assumptions!$C$74/365</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>J6*Assumptions!$C$49/365</f>
+        <f>J6*Assumptions!$C$74/365</f>
         <v/>
       </c>
     </row>
@@ -1728,39 +1728,39 @@
         </is>
       </c>
       <c r="B18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="C18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="D18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="E18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="J18" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>Assumptions!$C$44-Assumptions!$C$46-E17</f>
+        <f>Assumptions!$C$69-Assumptions!$C$71-E17</f>
         <v/>
       </c>
       <c r="F19" s="17">
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B20" s="17">
-        <f>C20/(1-Assumptions!$C$70)-Assumptions!$C$15+Assumptions!$C$52*Assumptions!$C$6-(C20/(1-Assumptions!$C$70)-Assumptions!$C$15+Assumptions!$C$52*Assumptions!$C$6)*Assumptions!$C$70</f>
+        <f>C20/(1-Assumptions!$C$95)-Assumptions!$C$15+Assumptions!$C$77*Assumptions!$C$6-(C20/(1-Assumptions!$C$95)-Assumptions!$C$15+Assumptions!$C$77*Assumptions!$C$6)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>D20/(1-Assumptions!$C$70)-Assumptions!$C$19+Assumptions!$C$52*Assumptions!$C$6-(D20/(1-Assumptions!$C$70)-Assumptions!$C$19+Assumptions!$C$52*Assumptions!$C$6)*Assumptions!$C$70</f>
+        <f>D20/(1-Assumptions!$C$95)-Assumptions!$C$19+Assumptions!$C$77*Assumptions!$C$6-(D20/(1-Assumptions!$C$95)-Assumptions!$C$19+Assumptions!$C$77*Assumptions!$C$6)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>E20/(1-Assumptions!$C$70)-Assumptions!$C$23+0.5*Assumptions!$C$52*Assumptions!$C$6-(E20/(1-Assumptions!$C$70)-Assumptions!$C$23+0.5*Assumptions!$C$52*Assumptions!$C$6)*Assumptions!$C$70</f>
+        <f>E20/(1-Assumptions!$C$95)-Assumptions!$C$23+0.5*Assumptions!$C$77*Assumptions!$C$6-(E20/(1-Assumptions!$C$95)-Assumptions!$C$23+0.5*Assumptions!$C$77*Assumptions!$C$6)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="E20" s="17">
-        <f>(Assumptions!$C$43-Assumptions!$C$44)*(1-Assumptions!$C$70)</f>
+        <f>(Assumptions!$C$68-Assumptions!$C$69)*(1-Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F20" s="18">
@@ -1857,39 +1857,39 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>B20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>B20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>C20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>C20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>D20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>D20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="E21" s="17">
-        <f>E20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>E20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="F21" s="17">
-        <f>F20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>F20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>G20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>G20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>H20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>H20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="I21" s="17">
-        <f>I20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>I20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>J20/(1-Assumptions!$C$70)*Assumptions!$C$70</f>
+        <f>J20/(1-Assumptions!$C$95)*Assumptions!$C$95</f>
         <v/>
       </c>
     </row>
@@ -1899,39 +1899,39 @@
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="35">
         <f>B17+B18+B19+B20+B21</f>
         <v/>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="35">
         <f>C17+C18+C19+C20+C21</f>
         <v/>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="35">
         <f>D17+D18+D19+D20+D21</f>
         <v/>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="35">
         <f>E17+E18+E19+E20+E21</f>
         <v/>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="35">
         <f>F17+F18+F19+F20+F21</f>
         <v/>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="35">
         <f>G17+G18+G19+G20+G21</f>
         <v/>
       </c>
-      <c r="H22" s="33">
+      <c r="H22" s="35">
         <f>H17+H18+H19+H20+H21</f>
         <v/>
       </c>
-      <c r="I22" s="33">
+      <c r="I22" s="35">
         <f>I17+I18+I19+I20+I21</f>
         <v/>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="35">
         <f>J17+J18+J19+J20+J21</f>
         <v/>
       </c>
@@ -2324,23 +2324,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B7*Assumptions!$C$61</f>
+        <f>B7*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C7*Assumptions!$C$61</f>
+        <f>C7*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D7*Assumptions!$C$61</f>
+        <f>D7*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E7*Assumptions!$C$61</f>
+        <f>E7*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>F7*Assumptions!$C$61</f>
+        <f>F7*Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -2431,23 +2431,23 @@
           <t>OPERATING CASH FLOW</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="35">
         <f>B9+B10-B11</f>
         <v/>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="35">
         <f>C9+C10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="35">
         <f>D9+D10-D11</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="35">
         <f>E9+E10-E11</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="35">
         <f>F9+F10-F11</f>
         <v/>
       </c>
@@ -2485,23 +2485,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="35">
         <f>B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="35">
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="35">
         <f>D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="35">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="35">
         <f>F12-F13</f>
         <v/>
       </c>
@@ -2513,23 +2513,23 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>MAX(Assumptions!$C$46-B$21,0)</f>
+        <f>MAX(Assumptions!$C$71-B$21,0)</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>MAX(Assumptions!$C$46-C$21,0)</f>
+        <f>MAX(Assumptions!$C$71-C$21,0)</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>MAX(Assumptions!$C$46-D$21,0)</f>
+        <f>MAX(Assumptions!$C$71-D$21,0)</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>MAX(Assumptions!$C$46-E$21,0)</f>
+        <f>MAX(Assumptions!$C$71-E$21,0)</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>MAX(Assumptions!$C$46-F$21,0)</f>
+        <f>MAX(Assumptions!$C$71-F$21,0)</f>
         <v/>
       </c>
     </row>
@@ -2540,23 +2540,23 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>Assumptions!$B$91*B15-Assumptions!$B$81*Assumptions!$C$46</f>
+        <f>Assumptions!$B$113*B15-Assumptions!$B$106*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>Assumptions!$C$91*C15-Assumptions!$C$81*Assumptions!$C$46</f>
+        <f>Assumptions!$C$113*C15-Assumptions!$C$106*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>Assumptions!$D$91*D15-Assumptions!$D$81*Assumptions!$C$46</f>
+        <f>Assumptions!$D$113*D15-Assumptions!$D$106*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>Assumptions!$E$91*E15-Assumptions!$E$81*Assumptions!$C$46</f>
+        <f>Assumptions!$E$113*E15-Assumptions!$E$106*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>Assumptions!$F$91*F15-Assumptions!$F$81*Assumptions!$C$46</f>
+        <f>Assumptions!$F$113*F15-Assumptions!$F$106*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -2567,23 +2567,23 @@
         </is>
       </c>
       <c r="B17" s="17">
-        <f>(B7+B16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
+        <f>(B7+B16)*(1-Assumptions!$C$86)*(1-Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>(C7+C16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
+        <f>(C7+C16)*(1-Assumptions!$C$86)*(1-Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>(D7+D16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
+        <f>(D7+D16)*(1-Assumptions!$C$86)*(1-Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>(E7+E16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
+        <f>(E7+E16)*(1-Assumptions!$C$86)*(1-Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>(F7+F16)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
+        <f>(F7+F16)*(1-Assumptions!$C$86)*(1-Assumptions!$C$95)</f>
         <v/>
       </c>
     </row>
@@ -2594,23 +2594,23 @@
         </is>
       </c>
       <c r="B18" s="17">
-        <f>Assumptions!$C$71*B17</f>
+        <f>Assumptions!$C$96*B17</f>
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>Assumptions!$C$71*C17</f>
+        <f>Assumptions!$C$96*C17</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>Assumptions!$C$71*D17</f>
+        <f>Assumptions!$C$96*D17</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>Assumptions!$C$71*E17</f>
+        <f>Assumptions!$C$96*E17</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>Assumptions!$C$71*F17</f>
+        <f>Assumptions!$C$96*F17</f>
         <v/>
       </c>
     </row>
@@ -2661,24 +2661,24 @@
           <t>Closing net debt</t>
         </is>
       </c>
-      <c r="B22" s="33">
-        <f>B21-(B14+B16*(1-Assumptions!$C$61))+B18</f>
-        <v/>
-      </c>
-      <c r="C22" s="33">
-        <f>C21-(C14+C16*(1-Assumptions!$C$61))+C18</f>
-        <v/>
-      </c>
-      <c r="D22" s="33">
-        <f>D21-(D14+D16*(1-Assumptions!$C$61))+D18</f>
-        <v/>
-      </c>
-      <c r="E22" s="33">
-        <f>E21-(E14+E16*(1-Assumptions!$C$61))+E18</f>
-        <v/>
-      </c>
-      <c r="F22" s="33">
-        <f>F21-(F14+F16*(1-Assumptions!$C$61))+F18</f>
+      <c r="B22" s="35">
+        <f>B21-(B14+B16*(1-Assumptions!$C$86))+B18</f>
+        <v/>
+      </c>
+      <c r="C22" s="35">
+        <f>C21-(C14+C16*(1-Assumptions!$C$86))+C18</f>
+        <v/>
+      </c>
+      <c r="D22" s="35">
+        <f>D21-(D14+D16*(1-Assumptions!$C$86))+D18</f>
+        <v/>
+      </c>
+      <c r="E22" s="35">
+        <f>E21-(E14+E16*(1-Assumptions!$C$86))+E18</f>
+        <v/>
+      </c>
+      <c r="F22" s="35">
+        <f>F21-(F14+F16*(1-Assumptions!$C$86))+F18</f>
         <v/>
       </c>
     </row>
@@ -2742,23 +2742,23 @@
           <t>Closing attributable equity</t>
         </is>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="35">
         <f>B24+B17-B18</f>
         <v/>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="35">
         <f>C24+C17-C18</f>
         <v/>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="35">
         <f>D24+D17-D18</f>
         <v/>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="35">
         <f>E24+E17-E18</f>
         <v/>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="35">
         <f>F24+F17-F18</f>
         <v/>
       </c>
@@ -3588,7 +3588,7 @@
           <t>Probability-integral-transform mean</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="30" t="n">
         <v>0.4612000000000001</v>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
           <t>Cone width against the benchmark</t>
         </is>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="30" t="n">
         <v>0.9693809251589353</v>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="32" t="n">
         <v>0.1452265</v>
       </c>
       <c r="B7" s="17">
@@ -3761,7 +3761,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="32" t="n">
         <v>0.1552265</v>
       </c>
       <c r="B8" s="17">
@@ -3790,7 +3790,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="32" t="n">
         <v>0.1652265</v>
       </c>
       <c r="B9" s="17">
@@ -3819,7 +3819,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="32" t="n">
         <v>0.1752265</v>
       </c>
       <c r="B10" s="17">
@@ -3848,7 +3848,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="32" t="n">
         <v>0.1852265</v>
       </c>
       <c r="B11" s="17">
@@ -3910,132 +3910,132 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43">
+      <c r="A14" s="34">
         <f>A7</f>
         <v/>
       </c>
       <c r="B14" s="20">
-        <f>((B7+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A7-0.03)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B7+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A7-0.03)*G7))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C14" s="20">
-        <f>((B7+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A7-0.04)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B7+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A7-0.04)*G7))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D14" s="20">
-        <f>((B7+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A7-0.05)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B7+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A7-0.05)*G7))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E14" s="20">
-        <f>((B7+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A7-0.06)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B7+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A7-0.06)*G7))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F14" s="20">
-        <f>((B7+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A7-0.07)*G7))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B7+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A7-0.07)*G7))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43">
+      <c r="A15" s="34">
         <f>A8</f>
         <v/>
       </c>
       <c r="B15" s="20">
-        <f>((B8+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A8-0.03)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B8+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A8-0.03)*G8))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C15" s="20">
-        <f>((B8+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A8-0.04)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B8+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A8-0.04)*G8))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D15" s="20">
-        <f>((B8+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A8-0.05)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B8+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A8-0.05)*G8))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E15" s="20">
-        <f>((B8+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A8-0.06)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B8+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A8-0.06)*G8))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>((B8+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A8-0.07)*G8))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B8+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A8-0.07)*G8))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43">
+      <c r="A16" s="34">
         <f>A9</f>
         <v/>
       </c>
       <c r="B16" s="20">
-        <f>((B9+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A9-0.03)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B9+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A9-0.03)*G9))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>((B9+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A9-0.04)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B9+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A9-0.04)*G9))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D16" s="20">
-        <f>((B9+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A9-0.05)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B9+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A9-0.05)*G9))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>((B9+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A9-0.06)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B9+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A9-0.06)*G9))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>((B9+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A9-0.07)*G9))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B9+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A9-0.07)*G9))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43">
+      <c r="A17" s="34">
         <f>A10</f>
         <v/>
       </c>
       <c r="B17" s="20">
-        <f>((B10+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A10-0.03)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B10+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A10-0.03)*G10))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>((B10+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A10-0.04)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B10+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A10-0.04)*G10))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D17" s="20">
-        <f>((B10+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A10-0.05)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B10+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A10-0.05)*G10))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>((B10+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A10-0.06)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B10+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A10-0.06)*G10))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>((B10+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A10-0.07)*G10))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B10+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A10-0.07)*G10))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43">
+      <c r="A18" s="34">
         <f>A11</f>
         <v/>
       </c>
       <c r="B18" s="20">
-        <f>((B11+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A11-0.03)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B11+DCF!F$13*(1+0.03)*(1-0.03/(DCF!F$13*(1+0.03)/DCF!F$24))/(A11-0.03)*G11))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C18" s="20">
-        <f>((B11+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A11-0.04)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B11+DCF!F$13*(1+0.04)*(1-0.04/(DCF!F$13*(1+0.04)/DCF!F$24))/(A11-0.04)*G11))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D18" s="20">
-        <f>((B11+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A11-0.05)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B11+DCF!F$13*(1+0.05)*(1-0.05/(DCF!F$13*(1+0.05)/DCF!F$24))/(A11-0.05)*G11))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E18" s="20">
-        <f>((B11+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A11-0.06)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B11+DCF!F$13*(1+0.06)*(1-0.06/(DCF!F$13*(1+0.06)/DCF!F$24))/(A11-0.06)*G11))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F18" s="20">
-        <f>((B11+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A11-0.07)*G11))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>((B11+DCF!F$13*(1+0.07)*(1-0.07/(DCF!F$13*(1+0.07)/DCF!F$24))/(A11-0.07)*G11))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4101,23 +4101,23 @@
           <t>Cost of equity, explicit</t>
         </is>
       </c>
-      <c r="B24" s="43">
+      <c r="B24" s="34">
         <f>DCF!$B$43+0.6*DCF!$B$45</f>
         <v/>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="34">
         <f>DCF!$B$43+0.8*DCF!$B$45</f>
         <v/>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="34">
         <f>DCF!$B$43+0.9405*DCF!$B$45</f>
         <v/>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="34">
         <f>DCF!$B$43+1.15*DCF!$B$45</f>
         <v/>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="34">
         <f>DCF!$B$43+1.3*DCF!$B$45</f>
         <v/>
       </c>
@@ -4128,24 +4128,24 @@
           <t>Cost of equity, terminal</t>
         </is>
       </c>
-      <c r="B25" s="43">
-        <f>Assumptions!$C$62+0.6*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="C25" s="43">
-        <f>Assumptions!$C$62+0.8*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="D25" s="43">
-        <f>Assumptions!$C$62+0.9405*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="E25" s="43">
-        <f>Assumptions!$C$62+1.15*Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="F25" s="43">
-        <f>Assumptions!$C$62+1.3*Assumptions!$C$63</f>
+      <c r="B25" s="34">
+        <f>Assumptions!$C$87+0.6*Assumptions!$C$88</f>
+        <v/>
+      </c>
+      <c r="C25" s="34">
+        <f>Assumptions!$C$87+0.8*Assumptions!$C$88</f>
+        <v/>
+      </c>
+      <c r="D25" s="34">
+        <f>Assumptions!$C$87+0.9405*Assumptions!$C$88</f>
+        <v/>
+      </c>
+      <c r="E25" s="34">
+        <f>Assumptions!$C$87+1.15*Assumptions!$C$88</f>
+        <v/>
+      </c>
+      <c r="F25" s="34">
+        <f>Assumptions!$C$87+1.3*Assumptions!$C$88</f>
         <v/>
       </c>
     </row>
@@ -4155,23 +4155,23 @@
           <t>WACC explicit</t>
         </is>
       </c>
-      <c r="B26" s="43">
+      <c r="B26" s="34">
         <f>DCF!$B$52*B24+DCF!$B$51*DCF!$B$53</f>
         <v/>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="34">
         <f>DCF!$B$52*C24+DCF!$B$51*DCF!$B$53</f>
         <v/>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="34">
         <f>DCF!$B$52*D24+DCF!$B$51*DCF!$B$53</f>
         <v/>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="34">
         <f>DCF!$B$52*E24+DCF!$B$51*DCF!$B$53</f>
         <v/>
       </c>
-      <c r="F26" s="43">
+      <c r="F26" s="34">
         <f>DCF!$B$52*F24+DCF!$B$51*DCF!$B$53</f>
         <v/>
       </c>
@@ -4182,24 +4182,24 @@
           <t>WACC terminal</t>
         </is>
       </c>
-      <c r="B27" s="43">
-        <f>(1-Assumptions!$C$65)*B25+Assumptions!$C$65*DCF!$B$60</f>
-        <v/>
-      </c>
-      <c r="C27" s="43">
-        <f>(1-Assumptions!$C$65)*C25+Assumptions!$C$65*DCF!$B$60</f>
-        <v/>
-      </c>
-      <c r="D27" s="43">
-        <f>(1-Assumptions!$C$65)*D25+Assumptions!$C$65*DCF!$B$60</f>
-        <v/>
-      </c>
-      <c r="E27" s="43">
-        <f>(1-Assumptions!$C$65)*E25+Assumptions!$C$65*DCF!$B$60</f>
-        <v/>
-      </c>
-      <c r="F27" s="43">
-        <f>(1-Assumptions!$C$65)*F25+Assumptions!$C$65*DCF!$B$60</f>
+      <c r="B27" s="34">
+        <f>(1-Assumptions!$C$90)*B25+Assumptions!$C$90*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="C27" s="34">
+        <f>(1-Assumptions!$C$90)*C25+Assumptions!$C$90*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="D27" s="34">
+        <f>(1-Assumptions!$C$90)*D25+Assumptions!$C$90*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="E27" s="34">
+        <f>(1-Assumptions!$C$90)*E25+Assumptions!$C$90*DCF!$B$60</f>
+        <v/>
+      </c>
+      <c r="F27" s="34">
+        <f>(1-Assumptions!$C$90)*F25+Assumptions!$C$90*DCF!$B$60</f>
         <v/>
       </c>
     </row>
@@ -4373,23 +4373,23 @@
         </is>
       </c>
       <c r="B35" s="20">
-        <f>(((B33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B27-Assumptions!$C$66)*B32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(((B33)+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(B27-Assumptions!$C$91)*B32))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C35" s="20">
-        <f>(((C33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C27-Assumptions!$C$66)*C32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(((C33)+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(C27-Assumptions!$C$91)*C32))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D35" s="20">
-        <f>(((D33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D27-Assumptions!$C$66)*D32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(((D33)+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(D27-Assumptions!$C$91)*D32))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E35" s="20">
-        <f>(((E33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E27-Assumptions!$C$66)*E32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(((E33)+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(E27-Assumptions!$C$91)*E32))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F35" s="20">
-        <f>(((F33)+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F27-Assumptions!$C$66)*F32))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(((F33)+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(F27-Assumptions!$C$91)*F32))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4458,127 +4458,127 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="32" t="n">
         <v>0.2863274586594906</v>
       </c>
       <c r="B43" s="20">
-        <f>(DCF!B$18/((1+($A$43-($A$43-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67))*(1+($A$43-($A$43-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67))*(1+($A$43-($A$43-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$43-($A$43-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67))*(1+($A$43-($A$43-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(B$42-Assumptions!$C$91)/((1+($A$43-($A$43-B$42)*DCF!B$67))*(1+($A$43-($A$43-B$42)*DCF!C$67))*(1+($A$43-($A$43-B$42)*DCF!D$67))*(1+($A$43-($A$43-B$42)*DCF!E$67))*(1+($A$43-($A$43-B$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f>(DCF!B$18/((1+($A$43-($A$43-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67))*(1+($A$43-($A$43-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67))*(1+($A$43-($A$43-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$43-($A$43-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67))*(1+($A$43-($A$43-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(C$42-Assumptions!$C$91)/((1+($A$43-($A$43-C$42)*DCF!B$67))*(1+($A$43-($A$43-C$42)*DCF!C$67))*(1+($A$43-($A$43-C$42)*DCF!D$67))*(1+($A$43-($A$43-C$42)*DCF!E$67))*(1+($A$43-($A$43-C$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f>(DCF!B$18/((1+($A$43-($A$43-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67))*(1+($A$43-($A$43-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67))*(1+($A$43-($A$43-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$43-($A$43-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67))*(1+($A$43-($A$43-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(D$42-Assumptions!$C$91)/((1+($A$43-($A$43-D$42)*DCF!B$67))*(1+($A$43-($A$43-D$42)*DCF!C$67))*(1+($A$43-($A$43-D$42)*DCF!D$67))*(1+($A$43-($A$43-D$42)*DCF!E$67))*(1+($A$43-($A$43-D$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E43" s="20">
-        <f>(DCF!B$18/((1+($A$43-($A$43-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67))*(1+($A$43-($A$43-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67))*(1+($A$43-($A$43-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$43-($A$43-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67))*(1+($A$43-($A$43-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(E$42-Assumptions!$C$91)/((1+($A$43-($A$43-E$42)*DCF!B$67))*(1+($A$43-($A$43-E$42)*DCF!C$67))*(1+($A$43-($A$43-E$42)*DCF!D$67))*(1+($A$43-($A$43-E$42)*DCF!E$67))*(1+($A$43-($A$43-E$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F43" s="20">
-        <f>(DCF!B$18/((1+($A$43-($A$43-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67))*(1+($A$43-($A$43-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67))*(1+($A$43-($A$43-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$43-($A$43-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67))*(1+($A$43-($A$43-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(F$42-Assumptions!$C$91)/((1+($A$43-($A$43-F$42)*DCF!B$67))*(1+($A$43-($A$43-F$42)*DCF!C$67))*(1+($A$43-($A$43-F$42)*DCF!D$67))*(1+($A$43-($A$43-F$42)*DCF!E$67))*(1+($A$43-($A$43-F$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="32" t="n">
         <v>0.3013274586594906</v>
       </c>
       <c r="B44" s="20">
-        <f>(DCF!B$18/((1+($A$44-($A$44-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67))*(1+($A$44-($A$44-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67))*(1+($A$44-($A$44-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$44-($A$44-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67))*(1+($A$44-($A$44-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(B$42-Assumptions!$C$91)/((1+($A$44-($A$44-B$42)*DCF!B$67))*(1+($A$44-($A$44-B$42)*DCF!C$67))*(1+($A$44-($A$44-B$42)*DCF!D$67))*(1+($A$44-($A$44-B$42)*DCF!E$67))*(1+($A$44-($A$44-B$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C44" s="20">
-        <f>(DCF!B$18/((1+($A$44-($A$44-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67))*(1+($A$44-($A$44-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67))*(1+($A$44-($A$44-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$44-($A$44-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67))*(1+($A$44-($A$44-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(C$42-Assumptions!$C$91)/((1+($A$44-($A$44-C$42)*DCF!B$67))*(1+($A$44-($A$44-C$42)*DCF!C$67))*(1+($A$44-($A$44-C$42)*DCF!D$67))*(1+($A$44-($A$44-C$42)*DCF!E$67))*(1+($A$44-($A$44-C$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D44" s="20">
-        <f>(DCF!B$18/((1+($A$44-($A$44-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67))*(1+($A$44-($A$44-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67))*(1+($A$44-($A$44-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$44-($A$44-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67))*(1+($A$44-($A$44-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(D$42-Assumptions!$C$91)/((1+($A$44-($A$44-D$42)*DCF!B$67))*(1+($A$44-($A$44-D$42)*DCF!C$67))*(1+($A$44-($A$44-D$42)*DCF!D$67))*(1+($A$44-($A$44-D$42)*DCF!E$67))*(1+($A$44-($A$44-D$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E44" s="20">
-        <f>(DCF!B$18/((1+($A$44-($A$44-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67))*(1+($A$44-($A$44-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67))*(1+($A$44-($A$44-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$44-($A$44-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67))*(1+($A$44-($A$44-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(E$42-Assumptions!$C$91)/((1+($A$44-($A$44-E$42)*DCF!B$67))*(1+($A$44-($A$44-E$42)*DCF!C$67))*(1+($A$44-($A$44-E$42)*DCF!D$67))*(1+($A$44-($A$44-E$42)*DCF!E$67))*(1+($A$44-($A$44-E$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F44" s="20">
-        <f>(DCF!B$18/((1+($A$44-($A$44-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67))*(1+($A$44-($A$44-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67))*(1+($A$44-($A$44-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$44-($A$44-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67))*(1+($A$44-($A$44-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(F$42-Assumptions!$C$91)/((1+($A$44-($A$44-F$42)*DCF!B$67))*(1+($A$44-($A$44-F$42)*DCF!C$67))*(1+($A$44-($A$44-F$42)*DCF!D$67))*(1+($A$44-($A$44-F$42)*DCF!E$67))*(1+($A$44-($A$44-F$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="32" t="n">
         <v>0.3163274586594906</v>
       </c>
       <c r="B45" s="20">
-        <f>(DCF!B$18/((1+($A$45-($A$45-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67))*(1+($A$45-($A$45-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67))*(1+($A$45-($A$45-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$45-($A$45-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67))*(1+($A$45-($A$45-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(B$42-Assumptions!$C$91)/((1+($A$45-($A$45-B$42)*DCF!B$67))*(1+($A$45-($A$45-B$42)*DCF!C$67))*(1+($A$45-($A$45-B$42)*DCF!D$67))*(1+($A$45-($A$45-B$42)*DCF!E$67))*(1+($A$45-($A$45-B$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f>(DCF!B$18/((1+($A$45-($A$45-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67))*(1+($A$45-($A$45-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67))*(1+($A$45-($A$45-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$45-($A$45-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67))*(1+($A$45-($A$45-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(C$42-Assumptions!$C$91)/((1+($A$45-($A$45-C$42)*DCF!B$67))*(1+($A$45-($A$45-C$42)*DCF!C$67))*(1+($A$45-($A$45-C$42)*DCF!D$67))*(1+($A$45-($A$45-C$42)*DCF!E$67))*(1+($A$45-($A$45-C$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f>(DCF!B$18/((1+($A$45-($A$45-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67))*(1+($A$45-($A$45-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67))*(1+($A$45-($A$45-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$45-($A$45-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67))*(1+($A$45-($A$45-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(D$42-Assumptions!$C$91)/((1+($A$45-($A$45-D$42)*DCF!B$67))*(1+($A$45-($A$45-D$42)*DCF!C$67))*(1+($A$45-($A$45-D$42)*DCF!D$67))*(1+($A$45-($A$45-D$42)*DCF!E$67))*(1+($A$45-($A$45-D$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E45" s="20">
-        <f>(DCF!B$18/((1+($A$45-($A$45-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67))*(1+($A$45-($A$45-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67))*(1+($A$45-($A$45-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$45-($A$45-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67))*(1+($A$45-($A$45-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(E$42-Assumptions!$C$91)/((1+($A$45-($A$45-E$42)*DCF!B$67))*(1+($A$45-($A$45-E$42)*DCF!C$67))*(1+($A$45-($A$45-E$42)*DCF!D$67))*(1+($A$45-($A$45-E$42)*DCF!E$67))*(1+($A$45-($A$45-E$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F45" s="20">
-        <f>(DCF!B$18/((1+($A$45-($A$45-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67))*(1+($A$45-($A$45-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67))*(1+($A$45-($A$45-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$45-($A$45-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67))*(1+($A$45-($A$45-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(F$42-Assumptions!$C$91)/((1+($A$45-($A$45-F$42)*DCF!B$67))*(1+($A$45-($A$45-F$42)*DCF!C$67))*(1+($A$45-($A$45-F$42)*DCF!D$67))*(1+($A$45-($A$45-F$42)*DCF!E$67))*(1+($A$45-($A$45-F$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="32" t="n">
         <v>0.3313274586594906</v>
       </c>
       <c r="B46" s="20">
-        <f>(DCF!B$18/((1+($A$46-($A$46-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67))*(1+($A$46-($A$46-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67))*(1+($A$46-($A$46-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$46-($A$46-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67))*(1+($A$46-($A$46-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(B$42-Assumptions!$C$91)/((1+($A$46-($A$46-B$42)*DCF!B$67))*(1+($A$46-($A$46-B$42)*DCF!C$67))*(1+($A$46-($A$46-B$42)*DCF!D$67))*(1+($A$46-($A$46-B$42)*DCF!E$67))*(1+($A$46-($A$46-B$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C46" s="20">
-        <f>(DCF!B$18/((1+($A$46-($A$46-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67))*(1+($A$46-($A$46-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67))*(1+($A$46-($A$46-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$46-($A$46-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67))*(1+($A$46-($A$46-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(C$42-Assumptions!$C$91)/((1+($A$46-($A$46-C$42)*DCF!B$67))*(1+($A$46-($A$46-C$42)*DCF!C$67))*(1+($A$46-($A$46-C$42)*DCF!D$67))*(1+($A$46-($A$46-C$42)*DCF!E$67))*(1+($A$46-($A$46-C$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D46" s="20">
-        <f>(DCF!B$18/((1+($A$46-($A$46-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67))*(1+($A$46-($A$46-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67))*(1+($A$46-($A$46-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$46-($A$46-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67))*(1+($A$46-($A$46-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(D$42-Assumptions!$C$91)/((1+($A$46-($A$46-D$42)*DCF!B$67))*(1+($A$46-($A$46-D$42)*DCF!C$67))*(1+($A$46-($A$46-D$42)*DCF!D$67))*(1+($A$46-($A$46-D$42)*DCF!E$67))*(1+($A$46-($A$46-D$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E46" s="20">
-        <f>(DCF!B$18/((1+($A$46-($A$46-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67))*(1+($A$46-($A$46-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67))*(1+($A$46-($A$46-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$46-($A$46-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67))*(1+($A$46-($A$46-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(E$42-Assumptions!$C$91)/((1+($A$46-($A$46-E$42)*DCF!B$67))*(1+($A$46-($A$46-E$42)*DCF!C$67))*(1+($A$46-($A$46-E$42)*DCF!D$67))*(1+($A$46-($A$46-E$42)*DCF!E$67))*(1+($A$46-($A$46-E$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F46" s="20">
-        <f>(DCF!B$18/((1+($A$46-($A$46-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67))*(1+($A$46-($A$46-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67))*(1+($A$46-($A$46-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$46-($A$46-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67))*(1+($A$46-($A$46-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(F$42-Assumptions!$C$91)/((1+($A$46-($A$46-F$42)*DCF!B$67))*(1+($A$46-($A$46-F$42)*DCF!C$67))*(1+($A$46-($A$46-F$42)*DCF!D$67))*(1+($A$46-($A$46-F$42)*DCF!E$67))*(1+($A$46-($A$46-F$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="32" t="n">
         <v>0.3463274586594906</v>
       </c>
       <c r="B47" s="20">
-        <f>(DCF!B$18/((1+($A$47-($A$47-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67))*(1+($A$47-($A$47-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(B$42-Assumptions!$C$66)/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67))*(1+($A$47-($A$47-B$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$47-($A$47-B$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67))*(1+($A$47-($A$47-B$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(B$42-Assumptions!$C$91)/((1+($A$47-($A$47-B$42)*DCF!B$67))*(1+($A$47-($A$47-B$42)*DCF!C$67))*(1+($A$47-($A$47-B$42)*DCF!D$67))*(1+($A$47-($A$47-B$42)*DCF!E$67))*(1+($A$47-($A$47-B$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f>(DCF!B$18/((1+($A$47-($A$47-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67))*(1+($A$47-($A$47-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(C$42-Assumptions!$C$66)/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67))*(1+($A$47-($A$47-C$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$47-($A$47-C$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67))*(1+($A$47-($A$47-C$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(C$42-Assumptions!$C$91)/((1+($A$47-($A$47-C$42)*DCF!B$67))*(1+($A$47-($A$47-C$42)*DCF!C$67))*(1+($A$47-($A$47-C$42)*DCF!D$67))*(1+($A$47-($A$47-C$42)*DCF!E$67))*(1+($A$47-($A$47-C$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f>(DCF!B$18/((1+($A$47-($A$47-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67))*(1+($A$47-($A$47-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(D$42-Assumptions!$C$66)/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67))*(1+($A$47-($A$47-D$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$47-($A$47-D$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67))*(1+($A$47-($A$47-D$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(D$42-Assumptions!$C$91)/((1+($A$47-($A$47-D$42)*DCF!B$67))*(1+($A$47-($A$47-D$42)*DCF!C$67))*(1+($A$47-($A$47-D$42)*DCF!D$67))*(1+($A$47-($A$47-D$42)*DCF!E$67))*(1+($A$47-($A$47-D$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E47" s="20">
-        <f>(DCF!B$18/((1+($A$47-($A$47-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67))*(1+($A$47-($A$47-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(E$42-Assumptions!$C$66)/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67))*(1+($A$47-($A$47-E$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$47-($A$47-E$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67))*(1+($A$47-($A$47-E$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(E$42-Assumptions!$C$91)/((1+($A$47-($A$47-E$42)*DCF!B$67))*(1+($A$47-($A$47-E$42)*DCF!C$67))*(1+($A$47-($A$47-E$42)*DCF!D$67))*(1+($A$47-($A$47-E$42)*DCF!E$67))*(1+($A$47-($A$47-E$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F47" s="20">
-        <f>(DCF!B$18/((1+($A$47-($A$47-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67))*(1+($A$47-($A$47-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$66)*(1-DCF!$B$28)/(F$42-Assumptions!$C$66)/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67))*(1+($A$47-($A$47-F$42)*DCF!F$67))))*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>(DCF!B$18/((1+($A$47-($A$47-F$42)*DCF!B$67)))+DCF!C$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67)))+DCF!D$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67)))+DCF!E$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67)))+DCF!F$18/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67))*(1+($A$47-($A$47-F$42)*DCF!F$67)))+DCF!F$13*(1+Assumptions!$C$91)*(1-DCF!$B$28)/(F$42-Assumptions!$C$91)/((1+($A$47-($A$47-F$42)*DCF!B$67))*(1+($A$47-($A$47-F$42)*DCF!C$67))*(1+($A$47-($A$47-F$42)*DCF!D$67))*(1+($A$47-($A$47-F$42)*DCF!E$67))*(1+($A$47-($A$47-F$42)*DCF!F$67))))*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4646,19 +4646,19 @@
         </is>
       </c>
       <c r="B54" s="22" t="n">
-        <v>7.376368355511639</v>
+        <v>7.659966468071677</v>
       </c>
       <c r="C54" s="22" t="n">
-        <v>8.387952063134712</v>
+        <v>8.660518450544181</v>
       </c>
       <c r="D54" s="22" t="n">
-        <v>9.399535770757785</v>
+        <v>9.661070433016686</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>10.41111947838086</v>
+        <v>10.66162241548919</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>11.42270318600393</v>
+        <v>11.6621743979617</v>
       </c>
     </row>
     <row r="55"/>
@@ -4691,19 +4691,19 @@
         </is>
       </c>
       <c r="B57" s="22" t="n">
-        <v>8.040394454192397</v>
+        <v>6.48277602457541</v>
       </c>
       <c r="C57" s="22" t="n">
-        <v>8.69089639724986</v>
+        <v>7.996417820922662</v>
       </c>
       <c r="D57" s="22" t="n">
-        <v>9.399535770757785</v>
+        <v>9.661070433016686</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>10.17033825671128</v>
+        <v>11.48791512741575</v>
       </c>
       <c r="F57" s="22" t="n">
-        <v>11.00751599858174</v>
+        <v>13.48867216264404</v>
       </c>
     </row>
     <row r="58"/>
@@ -4736,19 +4736,19 @@
         </is>
       </c>
       <c r="B60" s="22" t="n">
-        <v>8.666540392073383</v>
+        <v>8.189185609814601</v>
       </c>
       <c r="C60" s="22" t="n">
-        <v>9.033038081415583</v>
+        <v>8.92512802141564</v>
       </c>
       <c r="D60" s="22" t="n">
-        <v>9.399535770757785</v>
+        <v>9.661070433016686</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>9.766033460099989</v>
+        <v>10.39701284461773</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>10.13253114944219</v>
+        <v>11.13295525621877</v>
       </c>
     </row>
     <row r="61"/>
@@ -4758,19 +4758,19 @@
           <t>Net working capital, % of revenue</t>
         </is>
       </c>
-      <c r="B62" s="30" t="n">
+      <c r="B62" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C62" s="30" t="n">
+      <c r="C62" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="D62" s="30" t="n">
-        <v>0.02021314135515365</v>
-      </c>
-      <c r="E62" s="30" t="n">
+      <c r="D62" s="32" t="n">
+        <v>0.02012030113973292</v>
+      </c>
+      <c r="E62" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="F62" s="30" t="n">
+      <c r="F62" s="32" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4781,19 +4781,19 @@
         </is>
       </c>
       <c r="B63" s="22" t="n">
-        <v>9.754139749992664</v>
+        <v>10.00510956514931</v>
       </c>
       <c r="C63" s="22" t="n">
-        <v>9.578707355292437</v>
+        <v>9.834118519963992</v>
       </c>
       <c r="D63" s="22" t="n">
-        <v>9.399535770757785</v>
+        <v>9.661070433016686</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>9.227842565891986</v>
+        <v>9.492136429593366</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>8.876977776491534</v>
+        <v>9.150154339222739</v>
       </c>
     </row>
   </sheetData>
@@ -5112,39 +5112,39 @@
           <t>Asset turnover (revenue / total assets)</t>
         </is>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="47">
         <f>'Income Statement'!B5/'Balance Sheet'!B14</f>
         <v/>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="47">
         <f>'Income Statement'!C5/'Balance Sheet'!C14</f>
         <v/>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>'Income Statement'!D5/'Balance Sheet'!D14</f>
         <v/>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="47">
         <f>'Income Statement'!E5/'Balance Sheet'!E14</f>
         <v/>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="47">
         <f>'Income Statement'!F5/'Balance Sheet'!F14</f>
         <v/>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="47">
         <f>'Income Statement'!G5/'Balance Sheet'!G14</f>
         <v/>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="47">
         <f>'Income Statement'!H5/'Balance Sheet'!H14</f>
         <v/>
       </c>
-      <c r="I10" s="46">
+      <c r="I10" s="47">
         <f>'Income Statement'!I5/'Balance Sheet'!I14</f>
         <v/>
       </c>
-      <c r="J10" s="46">
+      <c r="J10" s="47">
         <f>'Income Statement'!J5/'Balance Sheet'!J14</f>
         <v/>
       </c>
@@ -5155,39 +5155,39 @@
           <t>Net working capital days</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>'Balance Sheet'!B25/'Income Statement'!B5*365</f>
         <v/>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="37">
         <f>'Balance Sheet'!C25/'Income Statement'!C5*365</f>
         <v/>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="37">
         <f>'Balance Sheet'!D25/'Income Statement'!D5*365</f>
         <v/>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="37">
         <f>'Balance Sheet'!E25/'Income Statement'!E5*365</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="37">
         <f>'Balance Sheet'!F25/'Income Statement'!F5*365</f>
         <v/>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="37">
         <f>'Balance Sheet'!G25/'Income Statement'!G5*365</f>
         <v/>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="37">
         <f>'Balance Sheet'!H25/'Income Statement'!H5*365</f>
         <v/>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="37">
         <f>'Balance Sheet'!I25/'Income Statement'!I5*365</f>
         <v/>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="37">
         <f>'Balance Sheet'!J25/'Income Statement'!J5*365</f>
         <v/>
       </c>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="C12" s="8">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="D12" s="8">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="E12" s="8">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="F12" s="20">
@@ -5310,7 +5310,7 @@
         <v/>
       </c>
       <c r="D5" s="20">
-        <f>B5*C5*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>B5*C5*DCF!C19*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="B6" s="19">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="C6" s="18">
@@ -5329,7 +5329,7 @@
         <v/>
       </c>
       <c r="D6" s="20">
-        <f>B6*C6*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>B6*C6*DCF!C19*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="B7" s="19">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="C7" s="18">
@@ -5348,7 +5348,7 @@
         <v/>
       </c>
       <c r="D7" s="20">
-        <f>B7*C7*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>B7*C7*DCF!C19*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="B8" s="19">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
       <c r="C8" s="18">
@@ -5367,7 +5367,7 @@
         <v/>
       </c>
       <c r="D8" s="20">
-        <f>B8*C8*DCF!C19*(1-Assumptions!$C$70)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
+        <f>B8*C8*DCF!C19*(1-Assumptions!$C$95)/Assumptions!$C$6-DCF!$B$49/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5423,24 +5423,24 @@
           <t>Throughput (mn tonnes)</t>
         </is>
       </c>
-      <c r="B12" s="38">
-        <f>'Product Lines'!C54</f>
-        <v/>
-      </c>
-      <c r="C12" s="38">
-        <f>'Product Lines'!D54</f>
-        <v/>
-      </c>
-      <c r="D12" s="38">
-        <f>'Product Lines'!E54</f>
-        <v/>
-      </c>
-      <c r="E12" s="38">
-        <f>'Product Lines'!F54</f>
-        <v/>
-      </c>
-      <c r="F12" s="38">
-        <f>'Product Lines'!G54</f>
+      <c r="B12" s="40">
+        <f>'Product Lines'!C77</f>
+        <v/>
+      </c>
+      <c r="C12" s="40">
+        <f>'Product Lines'!D77</f>
+        <v/>
+      </c>
+      <c r="D12" s="40">
+        <f>'Product Lines'!E77</f>
+        <v/>
+      </c>
+      <c r="E12" s="40">
+        <f>'Product Lines'!F77</f>
+        <v/>
+      </c>
+      <c r="F12" s="40">
+        <f>'Product Lines'!G77</f>
         <v/>
       </c>
     </row>
@@ -5451,23 +5451,23 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>DCF!B9/'Product Lines'!C54</f>
+        <f>DCF!B9/'Product Lines'!C77</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>DCF!C9/'Product Lines'!D54</f>
+        <f>DCF!C9/'Product Lines'!D77</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>DCF!D9/'Product Lines'!E54</f>
+        <f>DCF!D9/'Product Lines'!E77</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>DCF!E9/'Product Lines'!F54</f>
+        <f>DCF!E9/'Product Lines'!F77</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>DCF!F9/'Product Lines'!G54</f>
+        <f>DCF!F9/'Product Lines'!G77</f>
         <v/>
       </c>
     </row>
@@ -5478,23 +5478,23 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>'Product Lines'!C51</f>
+        <f>'Product Lines'!C86</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>'Product Lines'!D51</f>
+        <f>'Product Lines'!D86</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>'Product Lines'!E51</f>
+        <f>'Product Lines'!E86</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>'Product Lines'!F51</f>
+        <f>'Product Lines'!F86</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>'Product Lines'!G51</f>
+        <f>'Product Lines'!G86</f>
         <v/>
       </c>
     </row>
@@ -5505,23 +5505,23 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>DCF!B7/'Product Lines'!C54</f>
+        <f>DCF!B7/'Product Lines'!C77</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>DCF!C7/'Product Lines'!D54</f>
+        <f>DCF!C7/'Product Lines'!D77</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>DCF!D7/'Product Lines'!E54</f>
+        <f>DCF!D7/'Product Lines'!E77</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>DCF!E7/'Product Lines'!F54</f>
+        <f>DCF!E7/'Product Lines'!F77</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>DCF!F7/'Product Lines'!G54</f>
+        <f>DCF!F7/'Product Lines'!G77</f>
         <v/>
       </c>
     </row>
@@ -5532,23 +5532,23 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>DCF!B15/'Product Lines'!C54</f>
+        <f>DCF!B15/'Product Lines'!C77</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>DCF!C15/'Product Lines'!D54</f>
+        <f>DCF!C15/'Product Lines'!D77</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>DCF!D15/'Product Lines'!E54</f>
+        <f>DCF!D15/'Product Lines'!E77</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>DCF!E15/'Product Lines'!F54</f>
+        <f>DCF!E15/'Product Lines'!F77</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>DCF!F15/'Product Lines'!G54</f>
+        <f>DCF!F15/'Product Lines'!G77</f>
         <v/>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="C18" s="18">
-        <f>'Product Lines'!E26</f>
+        <f>'Product Lines'!E25</f>
         <v/>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>'Product Lines'!B56</f>
+        <f>'Product Lines'!B105</f>
         <v/>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="C21" s="16">
-        <f>Assumptions!$C$52/Assumptions!$C$5</f>
+        <f>Assumptions!$C$77/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="C22" s="20">
-        <f>C10/Assumptions!$C$40</f>
+        <f>C10/Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="C25" s="10">
-        <f>Assumptions!$C$66</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -6021,17 +6021,17 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>5.699212717526938</v>
+        <v>4.870019380904797</v>
       </c>
       <c r="C5" s="8">
         <f>'EV Bridge'!$B$12</f>
         <v/>
       </c>
       <c r="D5" s="22" t="n">
-        <v>15.9696796013002</v>
+        <v>18.12390932093694</v>
       </c>
       <c r="E5" s="9">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$121</f>
         <v/>
       </c>
       <c r="F5" s="20">
@@ -6046,17 +6046,17 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>7.314267406614372</v>
+        <v>7.055968259821388</v>
       </c>
       <c r="C6" s="8">
         <f>'Relative &amp; Normalized'!$B$12</f>
         <v/>
       </c>
       <c r="D6" s="22" t="n">
-        <v>10.28611388710643</v>
+        <v>9.913240238587324</v>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$100</f>
+        <f>Assumptions!$C$122</f>
         <v/>
       </c>
       <c r="F6" s="20">
@@ -6071,17 +6071,17 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>8.623992774195941</v>
+        <v>8.55724387165677</v>
       </c>
       <c r="C7" s="8">
         <f>'Relative &amp; Normalized'!$B$24</f>
         <v/>
       </c>
       <c r="D7" s="22" t="n">
-        <v>14.89598751906572</v>
+        <v>14.78069396013442</v>
       </c>
       <c r="E7" s="9">
-        <f>Assumptions!$C$101</f>
+        <f>Assumptions!$C$123</f>
         <v/>
       </c>
       <c r="F7" s="20">
@@ -6106,7 +6106,7 @@
         <v>7.994059366782158</v>
       </c>
       <c r="E8" s="9">
-        <f>Assumptions!$C$102</f>
+        <f>Assumptions!$C$124</f>
         <v/>
       </c>
       <c r="F8" s="20">
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="B18" s="23">
-        <f>Assumptions!$C$77</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="B20" s="24" t="n">
-        <v>4772.886445826336</v>
+        <v>4701.463208721381</v>
       </c>
     </row>
     <row r="21">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="B21" s="24" t="n">
-        <v>6492.209855871781</v>
+        <v>6895.942067331197</v>
       </c>
     </row>
     <row r="22">
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>9.985524031416009</v>
+        <v>10.26691216453544</v>
       </c>
     </row>
     <row r="29">
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>7.795612915677023</v>
+        <v>7.95450637434835</v>
       </c>
     </row>
     <row r="30">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="C30" s="22" t="n">
-        <v>9.875828732302327</v>
+        <v>10.15835951869177</v>
       </c>
     </row>
     <row r="31"/>
@@ -6353,7 +6353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7005,95 +7005,127 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Specialty margin as a multiple of the fuel margin</t>
+          <t>Process loss and internal fuel burn</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C38" s="29" t="n">
-        <v>3.5</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>0.03</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>the one judgment parameter behind the margin</t>
+          <t>share of feedstock intake</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP average, calendar 2025</t>
+          <t>Barrels per tonne of feedstock</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C39" s="26" t="n">
-        <v>48.7</v>
+          <t>bbl</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>heavier than light crude at 7.33</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP spot</t>
+          <t>Energy and utilities</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>USD/t feed</t>
         </is>
       </c>
       <c r="C40" s="26" t="n">
-        <v>50.25</v>
+        <v>22</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>6 Aug 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+          <t>lube trains are energy-intensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Chemicals and catalyst — oil</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>solvent and catalyst; near nil on the fuel slate</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>BALANCE SHEET — DISCLOSED SNAPSHOT AND DAYS DRIVERS</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Chemicals and catalyst — wax</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>solvent and catalyst; near nil on the fuel slate</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Chemicals and catalyst — fuel</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="n">
-        <v>8136.42</v>
+          <t>USD/t</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>solvent and catalyst; near nil on the fuel slate</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Fixed conversion cost, year to Jun-2023</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -7102,226 +7134,278 @@
         </is>
       </c>
       <c r="C44" s="24" t="n">
-        <v>3189.56</v>
+        <v>700</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>labour, maintenance, plant overhead</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Cash and equivalents</t>
+          <t>Fixed-cost inflation factor, year 1</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="n">
-        <v>2463.52</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="n">
+        <v>1.33</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>Egyptian headline inflation easing to target</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Gross debt</t>
+          <t>Fixed-cost inflation factor, year 2</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="n">
-        <v>25.26</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>1.28</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>disclosed</t>
+          <t>Egyptian headline inflation easing to target</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Receivable days</t>
+          <t>Fixed-cost inflation factor, year 3</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="n">
-        <v>14</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Egyptian headline inflation easing to target</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Inventory days on cost of sales</t>
+          <t>Fixed-cost inflation factor, year 4</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="n">
-        <v>14</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Egyptian headline inflation easing to target</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Payable days on cost of sales</t>
+          <t>Fixed-cost inflation factor, year 5</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="n">
-        <v>24</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C49" s="30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Egyptian headline inflation easing to target</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Fixed-cost inflation factor, year 6</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="n">
-        <v>300</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Egyptian headline inflation easing to target</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Historical operating cost load, % of revenue</t>
+          <t>Fixed-cost inflation factor, year 7</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C51" s="30" t="n">
-        <v>0.0125</v>
+        <v>1.1</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>held flat across the reconstructed years</t>
+          <t>Egyptian headline inflation easing to target</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Dividend per share</t>
+          <t>Fixed-cost inflation factor, year 8</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n">
-        <v>0.8</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="n">
+        <v>1.095</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>declared</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
+          <t>Egyptian headline inflation easing to target</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Specialty fixed-cost intensity vs the fuel slate</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>allocates the fixed leg between lines</t>
+        </is>
+      </c>
+    </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>COST OF CAPITAL</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Brent average, year to Jun-2023</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>USD/bbl</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="n">
+        <v>85</v>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>house estimate</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Risk-free rate — Egypt 10-year</t>
+          <t>Brent average, year to Jun-2024</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C55" s="30" t="n">
-        <v>0.2231</v>
+          <t>USD/bbl</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>house estimate</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Sovereign default spread</t>
+          <t>USD/EGP average, year to Jun-2023</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C56" s="30" t="n">
-        <v>0.034</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="n">
+        <v>28.5</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>netted out of rf</t>
+          <t>house estimate</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Equity risk premium — Egypt</t>
+          <t>USD/EGP average, year to Jun-2025</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C57" s="30" t="n">
-        <v>0.0941</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="n">
+        <v>48.9</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Damodaran, CDS basis</t>
+          <t>house estimate</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Base-year realisation premium over the Brent deck</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -7330,291 +7414,306 @@
         </is>
       </c>
       <c r="C58" s="31" t="n">
-        <v>0.9405</v>
+        <v>1.119865118686094</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>own-stock regression</t>
+          <t>carried forward rather than dropped</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Cost of debt</t>
+          <t>Brent deck, 2026E</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C59" s="30" t="n">
-        <v>0.22</v>
+          <t>USD/bbl</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>now drives BOTH sides of the margin</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Yield on cash</t>
+          <t>Brent deck, 2027E</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C60" s="30" t="n">
-        <v>0.17</v>
+          <t>USD/bbl</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>now drives BOTH sides of the margin</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Effective tax rate</t>
+          <t>Brent deck, 2028E</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C61" s="30" t="n">
-        <v>0.235</v>
+          <t>USD/bbl</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>now drives BOTH sides of the margin</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Brent deck, 2029E</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="n">
-        <v>0.105</v>
+          <t>USD/bbl</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>74.5</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>norm-built</t>
+          <t>now drives BOTH sides of the margin</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Brent deck, 2030E</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C63" s="30" t="n">
-        <v>0.07000000000000001</v>
+          <t>USD/bbl</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>76</v>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>normalised</t>
+          <t>now drives BOTH sides of the margin</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>USD/EGP average, calendar 2025</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C64" s="30" t="n">
-        <v>0.15</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>48.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
+          <t>USD/EGP spot</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C65" s="28" t="n">
-        <v>0.1</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="n">
+        <v>50.25</v>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>normalised</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C66" s="30" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>sensitised 3-7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
+          <t>6 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>BALANCE SHEET — DISCLOSED SNAPSHOT AND DAYS DRIVERS</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+    </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>OPERATING DRIVERS</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="n">
+        <v>8136.42</v>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Depreciation, % of revenue</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="n">
-        <v>0.011</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="n">
+        <v>3189.56</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Minority share of group profit</t>
+          <t>Cash and equivalents</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="n">
-        <v>0.03</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="n">
+        <v>2463.52</v>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>disclosed</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Dividend payout ratio</t>
+          <t>Gross debt</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C71" s="28" t="n">
-        <v>0.694</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="n">
+        <v>25.26</v>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>disclosed</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Justified EV / EBITDA</t>
+          <t>Receivable days</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>4.5</v>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>House low bound on the multiple</t>
+          <t>Inventory days on cost of sales</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>NOT a peer observation</t>
-        </is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>House high bound on the multiple</t>
+          <t>Payable days on cost of sales</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>NOT a peer observation</t>
-        </is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Justified price / earnings</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>7.5</v>
+          <t>EGP mn</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>Historical operating cost load, % of revenue</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -7622,27 +7721,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C76" s="28" t="n">
-        <v>0.28</v>
+      <c r="C76" s="32" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>held flat across the reconstructed years</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Expert 1 justified price / earnings</t>
+          <t>Dividend per share</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>7</v>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="n">
+        <v>0.8</v>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Expert 1 strikes a lower multiple than the main normalised lens deliberately: it is an independent opinion, not a re-run of the house view</t>
+          <t>declared</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7754,7 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>PATHS — one column per forecast year</t>
+          <t>COST OF CAPITAL</t>
         </is>
       </c>
       <c r="B79" s="6" t="n"/>
@@ -7660,284 +7764,225 @@
       <c r="F79" s="6" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Risk-free rate — Egypt 10-year</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.2231</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Cost of debt path</t>
-        </is>
-      </c>
-      <c r="B81" s="30" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C81" s="30" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="D81" s="30" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E81" s="30" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F81" s="30" t="n">
-        <v>0.15</v>
+          <t>Sovereign default spread</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>netted out of rf</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP average rate path</t>
-        </is>
-      </c>
-      <c r="B82" s="26" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="C82" s="26" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="D82" s="26" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="E82" s="26" t="n">
-        <v>58</v>
-      </c>
-      <c r="F82" s="26" t="n">
-        <v>60.1</v>
+          <t>Equity risk premium — Egypt</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Damodaran, CDS basis</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Capital expenditure, % of revenue</t>
-        </is>
-      </c>
-      <c r="B83" s="30" t="n">
-        <v>0.0145</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
       </c>
       <c r="C83" s="30" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="D83" s="30" t="n">
-        <v>0.0135</v>
-      </c>
-      <c r="E83" s="30" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F83" s="30" t="n">
-        <v>0.0125</v>
+        <v>0.9405</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>own-stock regression</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Operating cost load, % of revenue</t>
-        </is>
-      </c>
-      <c r="B84" s="30" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="C84" s="30" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="D84" s="30" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="E84" s="30" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="F84" s="30" t="n">
-        <v>0.0128</v>
+          <t>Cost of debt</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Base-oil volume growth</t>
-        </is>
-      </c>
-      <c r="B85" s="30" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="C85" s="30" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="D85" s="30" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E85" s="30" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="F85" s="30" t="n">
-        <v>0.032</v>
+          <t>Yield on cash</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Paraffin-wax volume growth</t>
-        </is>
-      </c>
-      <c r="B86" s="30" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C86" s="30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D86" s="30" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E86" s="30" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F86" s="30" t="n">
-        <v>0.04</v>
+          <t>Effective tax rate</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="n">
+        <v>0.235</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Fuel-slate volume growth</t>
-        </is>
-      </c>
-      <c r="B87" s="30" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C87" s="30" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="D87" s="30" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="E87" s="30" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F87" s="30" t="n">
-        <v>0.023</v>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C87" s="32" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>norm-built</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Base-oil dollar price growth</t>
-        </is>
-      </c>
-      <c r="B88" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C88" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D88" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E88" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F88" s="30" t="n">
-        <v>0.02</v>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Paraffin-wax dollar price growth</t>
-        </is>
-      </c>
-      <c r="B89" s="30" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="C89" s="30" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D89" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E89" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F89" s="30" t="n">
-        <v>0.02</v>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C89" s="32" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Fuel-slate dollar price growth</t>
-        </is>
-      </c>
-      <c r="B90" s="30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C90" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D90" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E90" s="30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F90" s="30" t="n">
-        <v>0.02</v>
+          <t>Terminal debt weight</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Yield on cash path</t>
-        </is>
-      </c>
-      <c r="B91" s="30" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="C91" s="30" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D91" s="30" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E91" s="30" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F91" s="30" t="n">
-        <v>0.118</v>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>sensitised 3-7%</t>
+        </is>
       </c>
     </row>
     <row r="92"/>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>HISTORICAL GROSS MARGIN — one column per period</t>
+          <t>OPERATING DRIVERS</t>
         </is>
       </c>
       <c r="B93" s="6" t="n"/>
@@ -7947,125 +7992,518 @@
       <c r="F93" s="6" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>FY2022/23</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>FY2023/24</t>
-        </is>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>FY2024/25</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="inlineStr">
-        <is>
-          <t>CY2025</t>
-        </is>
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Depreciation, % of revenue</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Gross margin (historical)</t>
-        </is>
-      </c>
-      <c r="B95" s="30" t="n">
-        <v>0.0576</v>
-      </c>
-      <c r="C95" s="30" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D95" s="30" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="E95" s="30" t="n">
-        <v>0.064</v>
+          <t>Minority share of group profit</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>FY2022/23 is the DISCLOSED margin: gross profit over cost of sales plus gross profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="97"/>
+          <t>Dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Justified EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C97" s="33" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>LENS WEIGHTS</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="6" t="n"/>
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>House low bound on the multiple</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C98" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>NOT a peer observation</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C99" s="28" t="n">
-        <v>0.45</v>
+          <t>House high bound on the multiple</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C99" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>NOT a peer observation</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Relative multiples</t>
-        </is>
-      </c>
-      <c r="C100" s="28" t="n">
-        <v>0.2</v>
+          <t>Justified price / earnings</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C100" s="33" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Normalised earnings power</t>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
       <c r="C101" s="28" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
+          <t>Expert 1 justified price / earnings</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C102" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Expert 1 strikes a lower multiple than the main normalised lens deliberately: it is an independent opinion, not a re-run of the house view</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>PATHS — one column per forecast year</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B106" s="32" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C106" s="32" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="D106" s="32" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E106" s="32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F106" s="32" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>USD/EGP average rate path</t>
+        </is>
+      </c>
+      <c r="B107" s="26" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="C107" s="26" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="D107" s="26" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E107" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="F107" s="26" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>Capital expenditure, % of revenue</t>
+        </is>
+      </c>
+      <c r="B108" s="32" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="C108" s="32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D108" s="32" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="E108" s="32" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F108" s="32" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>Operating cost load, % of revenue</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="C109" s="32" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D109" s="32" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="E109" s="32" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F109" s="32" t="n">
+        <v>0.0128</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>Base-oil volume growth</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C110" s="32" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D110" s="32" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E110" s="32" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F110" s="32" t="n">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Paraffin-wax volume growth</t>
+        </is>
+      </c>
+      <c r="B111" s="32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C111" s="32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D111" s="32" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E111" s="32" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F111" s="32" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>Fuel-slate volume growth</t>
+        </is>
+      </c>
+      <c r="B112" s="32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C112" s="32" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D112" s="32" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="E112" s="32" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F112" s="32" t="n">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Yield on cash path</t>
+        </is>
+      </c>
+      <c r="B113" s="32" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C113" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D113" s="32" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="E113" s="32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F113" s="32" t="n">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>HISTORICAL GROSS MARGIN — one column per period</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="6" t="n"/>
+      <c r="F115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>FY2022/23</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>FY2023/24</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>FY2024/25</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>CY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin (historical) — BUILT, see Product Lines</t>
+        </is>
+      </c>
+      <c r="B117" s="34">
+        <f>'Product Lines'!B66</f>
+        <v/>
+      </c>
+      <c r="C117" s="34">
+        <f>'Product Lines'!C66</f>
+        <v/>
+      </c>
+      <c r="D117" s="34">
+        <f>'Product Lines'!D66</f>
+        <v/>
+      </c>
+      <c r="E117" s="34">
+        <f>'Product Lines'!E66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>NOT an input. FY2022/23 is the DISCLOSED margin and the other three are PREDICTIONS of the cost build, which is calibrated on that one year alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>LENS WEIGHTS</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+      <c r="E120" s="6" t="n"/>
+      <c r="F120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>Discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Relative multiples</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>Normalised earnings power</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
           <t>Book and sustainable return</t>
         </is>
       </c>
-      <c r="C102" s="28" t="n">
+      <c r="C124" s="28" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="13" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C103" s="15">
-        <f>C99+C100+C101+C102</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+      <c r="C125" s="15">
+        <f>C121+C122+C123+C124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126"/>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="21" t="inlineStr">
         <is>
           <t>Blue cells are the only inputs in this workbook. Everything on every other sheet is a formula pointing back here, except audited history and the two whole-model re-run grids (Monte Carlo, Sensitivity), which are labelled as such on their own sheets.</t>
         </is>
@@ -8073,7 +8511,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A127:F127"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8151,7 +8589,7 @@
         </is>
       </c>
       <c r="B6" s="9">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$95</f>
         <v/>
       </c>
     </row>
@@ -8206,7 +8644,7 @@
           <t>EQUITY ATTRIBUTABLE TO SHAREHOLDERS</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="35">
         <f>B8-B9</f>
         <v/>
       </c>
@@ -8239,7 +8677,7 @@
           <t>TERMINAL VALUE AS A SHARE OF ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="36">
         <f>DCF!$B$35</f>
         <v/>
       </c>
@@ -8325,7 +8763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -8479,7 +8917,7 @@
         <f>Assumptions!$C$33-B6-B7</f>
         <v/>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="37">
         <f>Assumptions!$C$34-C6-C7</f>
         <v/>
       </c>
@@ -8506,11 +8944,11 @@
           <t>Total (disclosed)</t>
         </is>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="38">
         <f>Assumptions!$C$33</f>
         <v/>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="39">
         <f>Assumptions!$C$34</f>
         <v/>
       </c>
@@ -8543,7 +8981,7 @@
           <t>Jul-Dec 2025 tonnage (disclosed)</t>
         </is>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="40">
         <f>Assumptions!$C$28</f>
         <v/>
       </c>
@@ -8554,7 +8992,7 @@
           <t>Jul-Dec 2024, off the disclosed +14.5%</t>
         </is>
       </c>
-      <c r="B14" s="39">
+      <c r="B14" s="41">
         <f>B13/1.145</f>
         <v/>
       </c>
@@ -8565,7 +9003,7 @@
           <t>FY2024/25 tonnage (disclosed)</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="40">
         <f>Assumptions!$C$26</f>
         <v/>
       </c>
@@ -8576,7 +9014,7 @@
           <t>Jan-Jun 2025 (the residual half)</t>
         </is>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="41">
         <f>B15-B14</f>
         <v/>
       </c>
@@ -8587,7 +9025,7 @@
           <t>CALENDAR 2025 TONNAGE</t>
         </is>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="42">
         <f>B16+B13</f>
         <v/>
       </c>
@@ -8598,7 +9036,7 @@
           <t>Specialty tonnage (FY2024/25 disclosed, plus the export ramp)</t>
         </is>
       </c>
-      <c r="B18" s="39">
+      <c r="B18" s="41">
         <f>Assumptions!$C$27*(1+Assumptions!$C$36)</f>
         <v/>
       </c>
@@ -8607,7 +9045,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>BASE-YEAR LINES AND THE RECONCILIATION</t>
+          <t>THE CALENDAR-2025 BASE LINES</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
@@ -8625,21 +9063,9 @@
           <t>Tonnes (mn)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>USD / tonne</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>USD/EGP</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Revenue (EGP mn)</t>
-        </is>
-      </c>
+      <c r="C21" s="12" t="inlineStr"/>
+      <c r="D21" s="12" t="inlineStr"/>
+      <c r="E21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -8647,20 +9073,8 @@
           <t>Base oils</t>
         </is>
       </c>
-      <c r="B22" s="39">
+      <c r="B22" s="41">
         <f>B18*Assumptions!$C$37</f>
-        <v/>
-      </c>
-      <c r="C22" s="17">
-        <f>E6*(1+Assumptions!$B$88)^1.5</f>
-        <v/>
-      </c>
-      <c r="D22" s="23">
-        <f>Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E22" s="17">
-        <f>B22*C22*D22</f>
         <v/>
       </c>
     </row>
@@ -8670,20 +9084,8 @@
           <t>Paraffin wax</t>
         </is>
       </c>
-      <c r="B23" s="39">
+      <c r="B23" s="41">
         <f>B18*(1-Assumptions!$C$37)</f>
-        <v/>
-      </c>
-      <c r="C23" s="17">
-        <f>E7*(1+Assumptions!$B$89)^1.5</f>
-        <v/>
-      </c>
-      <c r="D23" s="23">
-        <f>Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E23" s="17">
-        <f>B23*C23*D23</f>
         <v/>
       </c>
     </row>
@@ -8693,617 +9095,1442 @@
           <t>Fuel and by-products</t>
         </is>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="41">
         <f>B17-B18</f>
         <v/>
       </c>
-      <c r="C24" s="17">
-        <f>E8*(1+Assumptions!$B$90)^1.5</f>
-        <v/>
-      </c>
-      <c r="D24" s="23">
-        <f>Assumptions!$C$39</f>
-        <v/>
-      </c>
-      <c r="E24" s="17">
-        <f>B24*C24*D24</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Bottom-up total</t>
-        </is>
-      </c>
-      <c r="E25" s="33">
-        <f>E22+E23+E24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Calendar-2025 revenue from two disclosed halves</t>
-        </is>
-      </c>
-      <c r="E26" s="17">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Calendar-2025 revenue from two disclosed halves (EGP mn)</t>
+        </is>
+      </c>
+      <c r="E25" s="17">
         <f>(Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18)/3-Assumptions!$C$20+Assumptions!$C$22</f>
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>RECONCILIATION FACTOR</t>
-        </is>
-      </c>
-      <c r="E27" s="41">
-        <f>E26/E25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>Two independent routes to the same base-year revenue, agreeing within the factor shown. The factor is APPLIED to every line and every forecast year and it is on the face of the sheet — a bottom-up build that absorbs its own gap into one residual line is not a bottom-up build.</t>
-        </is>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>THE CRACK STRUCTURE — solved from the disclosed table</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Brent average, year to June 2024 (USD / bbl)</t>
+        </is>
+      </c>
+      <c r="B28" s="23">
+        <f>Assumptions!$C$55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Crude parity (USD / tonne) = Brent x barrels per tonne</t>
+        </is>
+      </c>
+      <c r="B29" s="17">
+        <f>B28*Assumptions!$C$39</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>THE TWO LEG MARGINS, SOLVED FROM ONE DISCLOSED BLEND</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Base oils — realisation as a multiple of crude parity</t>
+        </is>
+      </c>
+      <c r="B30" s="43">
+        <f>E6/B29</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Specialty share of base-year revenue</t>
-        </is>
-      </c>
-      <c r="B31" s="16">
-        <f>(E22+E23)/E25</f>
+          <t>Paraffin wax — realisation as a multiple of crude parity</t>
+        </is>
+      </c>
+      <c r="B31" s="43">
+        <f>E7/B29</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Base-year blended gross margin (disclosed anchor path)</t>
-        </is>
-      </c>
-      <c r="B32" s="10">
-        <f>Assumptions!$E$95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Specialty margin as a multiple of the fuel margin</t>
-        </is>
-      </c>
-      <c r="B33" s="42">
-        <f>Assumptions!$C$38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Fuel and by-product gross margin (solved)</t>
-        </is>
-      </c>
-      <c r="B34" s="43">
-        <f>B32/(B31*B33+1-B31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Specialty gross margin (solved)</t>
-        </is>
-      </c>
-      <c r="B35" s="43">
-        <f>B33*B34</f>
-        <v/>
-      </c>
-    </row>
+          <t>Fuel and by-products — realisation as a multiple of crude parity</t>
+        </is>
+      </c>
+      <c r="B32" s="43">
+        <f>E8/B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>These are the disclosed product table divided by the crude price. They are not assumptions and they are not fitted to any margin. Base oil near 1.9x crude, wax near 1.7x and a gas-oil blend within a per cent of parity is the textbook shape of a lube refinery slate — the strongest single check that the product table is real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Check: the two remix to the disclosed blend</t>
-        </is>
-      </c>
-      <c r="B36" s="43">
-        <f>B31*B35+(1-B31)*B34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>THE FEEDSTOCK DIFFERENTIAL — solved on the ONE disclosed cost of sales</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Brent average, year to June 2023 (USD / bbl)</t>
+        </is>
+      </c>
+      <c r="B37" s="23">
+        <f>Assumptions!$C$54</f>
+        <v/>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>THE FORECAST</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Crude parity, year to June 2023 (USD / tonne)</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>B37*Assumptions!$C$39</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr"/>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Blended realisation at the disclosed mix (USD / tonne)</t>
+        </is>
+      </c>
+      <c r="B39" s="17">
+        <f>F6*B38*B30+F7*B38*B31+F8*B38*B32</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Base oils — tonnes (mn)</t>
-        </is>
-      </c>
-      <c r="C40" s="39">
-        <f>B22*(1+Assumptions!$B$85)</f>
-        <v/>
-      </c>
-      <c r="D40" s="39">
-        <f>C40*(1+Assumptions!$C$85)</f>
-        <v/>
-      </c>
-      <c r="E40" s="39">
-        <f>D40*(1+Assumptions!$D$85)</f>
-        <v/>
-      </c>
-      <c r="F40" s="39">
-        <f>E40*(1+Assumptions!$E$85)</f>
-        <v/>
-      </c>
-      <c r="G40" s="39">
-        <f>F40*(1+Assumptions!$F$85)</f>
+          <t>IMPLIED FY2022/23 THROUGHPUT (mn tonnes) — derived, not assumed</t>
+        </is>
+      </c>
+      <c r="B40" s="41">
+        <f>Assumptions!$C$9/(B39*Assumptions!$C$56)*1000000/1000000</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Paraffin wax — tonnes (mn)</t>
-        </is>
-      </c>
-      <c r="C41" s="39">
-        <f>B23*(1+Assumptions!$B$86)</f>
-        <v/>
-      </c>
-      <c r="D41" s="39">
-        <f>C41*(1+Assumptions!$C$86)</f>
-        <v/>
-      </c>
-      <c r="E41" s="39">
-        <f>D41*(1+Assumptions!$D$86)</f>
-        <v/>
-      </c>
-      <c r="F41" s="39">
-        <f>E41*(1+Assumptions!$E$86)</f>
-        <v/>
-      </c>
-      <c r="G41" s="39">
-        <f>F41*(1+Assumptions!$F$86)</f>
+          <t>Feedstock intake (mn tonnes) = product / (1 - process loss)</t>
+        </is>
+      </c>
+      <c r="B41" s="41">
+        <f>B40/(1-Assumptions!$C$38)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Fuel and by-products — tonnes (mn)</t>
-        </is>
-      </c>
-      <c r="C42" s="39">
-        <f>B24*(1+Assumptions!$B$87)</f>
-        <v/>
-      </c>
-      <c r="D42" s="39">
-        <f>C42*(1+Assumptions!$C$87)</f>
-        <v/>
-      </c>
-      <c r="E42" s="39">
-        <f>D42*(1+Assumptions!$D$87)</f>
-        <v/>
-      </c>
-      <c r="F42" s="39">
-        <f>E42*(1+Assumptions!$E$87)</f>
-        <v/>
-      </c>
-      <c r="G42" s="39">
-        <f>F42*(1+Assumptions!$F$87)</f>
+          <t>Energy and utilities (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B42" s="17">
+        <f>B41*Assumptions!$C$40*Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Base oils — USD / tonne</t>
-        </is>
-      </c>
-      <c r="C43" s="17">
-        <f>C22*(1+Assumptions!$B$88)</f>
-        <v/>
-      </c>
-      <c r="D43" s="17">
-        <f>C43*(1+Assumptions!$C$88)</f>
-        <v/>
-      </c>
-      <c r="E43" s="17">
-        <f>D43*(1+Assumptions!$D$88)</f>
-        <v/>
-      </c>
-      <c r="F43" s="17">
-        <f>E43*(1+Assumptions!$E$88)</f>
-        <v/>
-      </c>
-      <c r="G43" s="17">
-        <f>F43*(1+Assumptions!$F$88)</f>
+          <t>Chemicals, solvent and catalyst (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B43" s="17">
+        <f>(B40*F6*Assumptions!$C$41+B40*F7*Assumptions!$C$42+B40*F8*Assumptions!$C$43)*Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Paraffin wax — USD / tonne</t>
-        </is>
-      </c>
-      <c r="C44" s="17">
-        <f>C23*(1+Assumptions!$B$89)</f>
-        <v/>
-      </c>
-      <c r="D44" s="17">
-        <f>C44*(1+Assumptions!$C$89)</f>
-        <v/>
-      </c>
-      <c r="E44" s="17">
-        <f>D44*(1+Assumptions!$D$89)</f>
-        <v/>
-      </c>
-      <c r="F44" s="17">
-        <f>E44*(1+Assumptions!$E$89)</f>
-        <v/>
-      </c>
-      <c r="G44" s="17">
-        <f>F44*(1+Assumptions!$F$89)</f>
+          <t>Fixed conversion — labour, maintenance, plant overhead (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B44" s="18">
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Fuel and by-products — USD / tonne</t>
-        </is>
-      </c>
-      <c r="C45" s="17">
-        <f>C24*(1+Assumptions!$B$90)</f>
-        <v/>
-      </c>
-      <c r="D45" s="17">
-        <f>C45*(1+Assumptions!$C$90)</f>
-        <v/>
-      </c>
-      <c r="E45" s="17">
-        <f>D45*(1+Assumptions!$D$90)</f>
-        <v/>
-      </c>
-      <c r="F45" s="17">
-        <f>E45*(1+Assumptions!$E$90)</f>
-        <v/>
-      </c>
-      <c r="G45" s="17">
-        <f>F45*(1+Assumptions!$F$90)</f>
+          <t>DISCLOSED cost of sales, year to June 2023 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B45" s="18">
+        <f>Assumptions!$C$11</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>USD/EGP average</t>
-        </is>
-      </c>
-      <c r="C46" s="23">
-        <f>Assumptions!$B$82</f>
-        <v/>
-      </c>
-      <c r="D46" s="23">
-        <f>Assumptions!$C$82</f>
-        <v/>
-      </c>
-      <c r="E46" s="23">
-        <f>Assumptions!$D$82</f>
-        <v/>
-      </c>
-      <c r="F46" s="23">
-        <f>Assumptions!$E$82</f>
-        <v/>
-      </c>
-      <c r="G46" s="23">
-        <f>Assumptions!$F$82</f>
+          <t>Residual available for feedstock (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B46" s="17">
+        <f>B45-B42-B43-B44</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Base oils — revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C47" s="17">
-        <f>C40*C43*C46*$E$27</f>
-        <v/>
-      </c>
-      <c r="D47" s="17">
-        <f>D40*D43*D46*$E$27</f>
-        <v/>
-      </c>
-      <c r="E47" s="17">
-        <f>E40*E43*E46*$E$27</f>
-        <v/>
-      </c>
-      <c r="F47" s="17">
-        <f>F40*F43*F46*$E$27</f>
-        <v/>
-      </c>
-      <c r="G47" s="17">
-        <f>G40*G43*G46*$E$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Paraffin wax — revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C48" s="17">
-        <f>C41*C44*C46*$E$27</f>
-        <v/>
-      </c>
-      <c r="D48" s="17">
-        <f>D41*D44*D46*$E$27</f>
-        <v/>
-      </c>
-      <c r="E48" s="17">
-        <f>E41*E44*E46*$E$27</f>
-        <v/>
-      </c>
-      <c r="F48" s="17">
-        <f>F41*F44*F46*$E$27</f>
-        <v/>
-      </c>
-      <c r="G48" s="17">
-        <f>G41*G44*G46*$E$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Fuel and by-products — revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C49" s="17">
-        <f>C42*C45*C46*$E$27</f>
-        <v/>
-      </c>
-      <c r="D49" s="17">
-        <f>D42*D45*D46*$E$27</f>
-        <v/>
-      </c>
-      <c r="E49" s="17">
-        <f>E42*E45*E46*$E$27</f>
-        <v/>
-      </c>
-      <c r="F49" s="17">
-        <f>F42*F45*F46*$E$27</f>
-        <v/>
-      </c>
-      <c r="G49" s="17">
-        <f>G42*G45*G46*$E$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL REVENUE</t>
-        </is>
-      </c>
-      <c r="C50" s="33">
-        <f>C47+C48+C49</f>
-        <v/>
-      </c>
-      <c r="D50" s="33">
-        <f>D47+D48+D49</f>
-        <v/>
-      </c>
-      <c r="E50" s="33">
-        <f>E47+E48+E49</f>
-        <v/>
-      </c>
-      <c r="F50" s="33">
-        <f>F47+F48+F49</f>
-        <v/>
-      </c>
-      <c r="G50" s="33">
-        <f>G47+G48+G49</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>FEEDSTOCK DIFFERENTIAL vs crude parity — SOLVED</t>
+        </is>
+      </c>
+      <c r="B47" s="44">
+        <f>B46/(B41*B38*Assumptions!$C$56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>Nothing about the margin is assumed anywhere on this sheet. The year to June 2023 is the only period with a disclosed cost of sales; the feedstock charge is whatever it has to be for the build to reproduce it exactly. The answer — a small discount to crude parity — is what a lube plant drawing vacuum gas oil from the adjacent state complex should show. Change the crude deck, the loss rate or the energy assumption and this cell resolves; it is a solve, not an input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>Specialty share of revenue</t>
-        </is>
-      </c>
-      <c r="C51" s="16">
-        <f>(C47+C48)/C50</f>
-        <v/>
-      </c>
-      <c r="D51" s="16">
-        <f>(D47+D48)/D50</f>
-        <v/>
-      </c>
-      <c r="E51" s="16">
-        <f>(E47+E48)/E50</f>
-        <v/>
-      </c>
-      <c r="F51" s="16">
-        <f>(F47+F48)/F50</f>
-        <v/>
-      </c>
-      <c r="G51" s="16">
-        <f>(G47+G48)/G50</f>
-        <v/>
-      </c>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>THE HISTORICAL MARGIN — calibrated on ONE year, the other three PREDICTED</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>GROSS PROFIT — the two leg margins on that mix</t>
-        </is>
-      </c>
-      <c r="C52" s="33">
-        <f>(C47+C48)*$B$35+C49*$B$34</f>
-        <v/>
-      </c>
-      <c r="D52" s="33">
-        <f>(D47+D48)*$B$35+D49*$B$34</f>
-        <v/>
-      </c>
-      <c r="E52" s="33">
-        <f>(E47+E48)*$B$35+E49*$B$34</f>
-        <v/>
-      </c>
-      <c r="F52" s="33">
-        <f>(F47+F48)*$B$35+F49*$B$34</f>
-        <v/>
-      </c>
-      <c r="G52" s="33">
-        <f>(G47+G48)*$B$35+G49*$B$34</f>
-        <v/>
+      <c r="A52" s="12" t="inlineStr"/>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>FY2022/23</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>FY2023/24</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>FY2024/25</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>CY2025</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>BLENDED GROSS MARGIN — an output, not an input</t>
-        </is>
-      </c>
-      <c r="C53" s="44">
-        <f>C52/C50</f>
-        <v/>
-      </c>
-      <c r="D53" s="44">
-        <f>D52/D50</f>
-        <v/>
-      </c>
-      <c r="E53" s="44">
-        <f>E52/E50</f>
-        <v/>
-      </c>
-      <c r="F53" s="44">
-        <f>F52/F50</f>
-        <v/>
-      </c>
-      <c r="G53" s="44">
-        <f>G52/G50</f>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B53" s="17">
+        <f>Assumptions!$C$9</f>
+        <v/>
+      </c>
+      <c r="C53" s="17">
+        <f>Assumptions!$C$34</f>
+        <v/>
+      </c>
+      <c r="D53" s="17">
+        <f>(Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18)/3</f>
+        <v/>
+      </c>
+      <c r="E53" s="17">
+        <f>E25</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Total tonnes (mn)</t>
-        </is>
-      </c>
-      <c r="C54" s="39">
-        <f>C40+C41+C42</f>
-        <v/>
-      </c>
-      <c r="D54" s="39">
-        <f>D40+D41+D42</f>
-        <v/>
-      </c>
-      <c r="E54" s="39">
-        <f>E40+E41+E42</f>
-        <v/>
-      </c>
-      <c r="F54" s="39">
-        <f>F40+F41+F42</f>
-        <v/>
-      </c>
-      <c r="G54" s="39">
-        <f>G40+G41+G42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55"/>
+          <t>Base oils — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="B54" s="41">
+        <f>B40*F6</f>
+        <v/>
+      </c>
+      <c r="C54" s="41">
+        <f>B6/1000000</f>
+        <v/>
+      </c>
+      <c r="D54" s="41">
+        <f>Assumptions!$C$26*F6</f>
+        <v/>
+      </c>
+      <c r="E54" s="41">
+        <f>B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Paraffin wax — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="B55" s="41">
+        <f>B40*F7</f>
+        <v/>
+      </c>
+      <c r="C55" s="41">
+        <f>B7/1000000</f>
+        <v/>
+      </c>
+      <c r="D55" s="41">
+        <f>Assumptions!$C$26*F7</f>
+        <v/>
+      </c>
+      <c r="E55" s="41">
+        <f>B23</f>
+        <v/>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
+          <t>Fuel and by-products — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="B56" s="41">
+        <f>B40*F8</f>
+        <v/>
+      </c>
+      <c r="C56" s="41">
+        <f>B8/1000000</f>
+        <v/>
+      </c>
+      <c r="D56" s="41">
+        <f>Assumptions!$C$26*F8</f>
+        <v/>
+      </c>
+      <c r="E56" s="41">
+        <f>B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Total product tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="B57" s="41">
+        <f>B54+B55+B56</f>
+        <v/>
+      </c>
+      <c r="C57" s="41">
+        <f>C54+C55+C56</f>
+        <v/>
+      </c>
+      <c r="D57" s="41">
+        <f>D54+D55+D56</f>
+        <v/>
+      </c>
+      <c r="E57" s="41">
+        <f>E54+E55+E56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Feedstock intake (mn tonnes)</t>
+        </is>
+      </c>
+      <c r="B58" s="41">
+        <f>B57/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="C58" s="41">
+        <f>C57/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="D58" s="41">
+        <f>D57/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="E58" s="41">
+        <f>E57/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Crude parity implied by that revenue (USD / tonne)</t>
+        </is>
+      </c>
+      <c r="B59" s="17">
+        <f>B53*1000000/((B54*$B$30+B55*$B$31+B56*$B$32)*1000000*Assumptions!$C$56)</f>
+        <v/>
+      </c>
+      <c r="C59" s="17">
+        <f>C53*1000000/((C54*$B$30+C55*$B$31+C56*$B$32)*1000000*Assumptions!$C$35)</f>
+        <v/>
+      </c>
+      <c r="D59" s="17">
+        <f>D53*1000000/((D54*$B$30+D55*$B$31+D56*$B$32)*1000000*Assumptions!$C$57)</f>
+        <v/>
+      </c>
+      <c r="E59" s="17">
+        <f>E53*1000000/((E54*$B$30+E55*$B$31+E56*$B$32)*1000000*Assumptions!$C$64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Implied Brent equivalent (USD / bbl)</t>
+        </is>
+      </c>
+      <c r="B60" s="37">
+        <f>B59/Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="C60" s="37">
+        <f>C59/Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="D60" s="37">
+        <f>D59/Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="E60" s="37">
+        <f>E59/Assumptions!$C$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Feedstock cost (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B61" s="17">
+        <f>B58*B59*$B$47*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="C61" s="17">
+        <f>C58*C59*$B$47*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D61" s="17">
+        <f>D58*D59*$B$47*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="E61" s="17">
+        <f>E58*E59*$B$47*Assumptions!$C$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Energy and utilities (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B62" s="17">
+        <f>B58*Assumptions!$C$40*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="C62" s="17">
+        <f>C58*Assumptions!$C$40*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D62" s="17">
+        <f>D58*Assumptions!$C$40*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="E62" s="17">
+        <f>E58*Assumptions!$C$40*Assumptions!$C$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Chemicals, solvent and catalyst (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B63" s="17">
+        <f>(B54*Assumptions!$C$41+B55*Assumptions!$C$42+B56*Assumptions!$C$43)*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="C63" s="17">
+        <f>(C54*Assumptions!$C$41+C55*Assumptions!$C$42+C56*Assumptions!$C$43)*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D63" s="17">
+        <f>(D54*Assumptions!$C$41+D55*Assumptions!$C$42+D56*Assumptions!$C$43)*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="E63" s="17">
+        <f>(E54*Assumptions!$C$41+E55*Assumptions!$C$42+E56*Assumptions!$C$43)*Assumptions!$C$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Fixed conversion (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B64" s="17">
+        <f>Assumptions!$C$44</f>
+        <v/>
+      </c>
+      <c r="C64" s="17">
+        <f>B64*Assumptions!$C$45</f>
+        <v/>
+      </c>
+      <c r="D64" s="17">
+        <f>C64*Assumptions!$C$46</f>
+        <v/>
+      </c>
+      <c r="E64" s="17">
+        <f>D64*Assumptions!$C$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>COST OF SALES (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B65" s="35">
+        <f>B61+B62+B63+B64</f>
+        <v/>
+      </c>
+      <c r="C65" s="35">
+        <f>C61+C62+C63+C64</f>
+        <v/>
+      </c>
+      <c r="D65" s="35">
+        <f>D61+D62+D63+D64</f>
+        <v/>
+      </c>
+      <c r="E65" s="35">
+        <f>E61+E62+E63+E64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>HISTORICAL GROSS MARGIN — an OUTPUT</t>
+        </is>
+      </c>
+      <c r="B66" s="45">
+        <f>(B53-B65)/B53</f>
+        <v/>
+      </c>
+      <c r="C66" s="45">
+        <f>(C53-C65)/C53</f>
+        <v/>
+      </c>
+      <c r="D66" s="45">
+        <f>(D53-D65)/D53</f>
+        <v/>
+      </c>
+      <c r="E66" s="45">
+        <f>(E53-E65)/E53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>What the PREVIOUS edition assumed</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>0.064</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Difference (built less assumed)</t>
+        </is>
+      </c>
+      <c r="B68" s="34">
+        <f>B66-B67</f>
+        <v/>
+      </c>
+      <c r="C68" s="34">
+        <f>C66-C67</f>
+        <v/>
+      </c>
+      <c r="D68" s="34">
+        <f>D66-D67</f>
+        <v/>
+      </c>
+      <c r="E68" s="34">
+        <f>E66-E67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="21" t="inlineStr">
+        <is>
+          <t>The June-2023 column is the CALIBRATION: the feedstock differential above was solved so that this column reproduces the disclosed cost of sales exactly, so a zero difference there is arithmetic, not evidence. The other three columns are PREDICTIONS — nothing in the cost build was tuned to them — and they land within a point of a house margin path that was built by an entirely different route. That is the check. Where the two disagree, the BUILT number is the one this model carries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>THE FORECAST — margin falls out of the cost build</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr"/>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Base oils — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C74" s="41">
+        <f>B22*(1+Assumptions!$B$110)</f>
+        <v/>
+      </c>
+      <c r="D74" s="41">
+        <f>C74*(1+Assumptions!$C$110)</f>
+        <v/>
+      </c>
+      <c r="E74" s="41">
+        <f>D74*(1+Assumptions!$D$110)</f>
+        <v/>
+      </c>
+      <c r="F74" s="41">
+        <f>E74*(1+Assumptions!$E$110)</f>
+        <v/>
+      </c>
+      <c r="G74" s="41">
+        <f>F74*(1+Assumptions!$F$110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Paraffin wax — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C75" s="41">
+        <f>B23*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="D75" s="41">
+        <f>C75*(1+Assumptions!$C$111)</f>
+        <v/>
+      </c>
+      <c r="E75" s="41">
+        <f>D75*(1+Assumptions!$D$111)</f>
+        <v/>
+      </c>
+      <c r="F75" s="41">
+        <f>E75*(1+Assumptions!$E$111)</f>
+        <v/>
+      </c>
+      <c r="G75" s="41">
+        <f>F75*(1+Assumptions!$F$111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Fuel and by-products — tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C76" s="41">
+        <f>B24*(1+Assumptions!$B$112)</f>
+        <v/>
+      </c>
+      <c r="D76" s="41">
+        <f>C76*(1+Assumptions!$C$112)</f>
+        <v/>
+      </c>
+      <c r="E76" s="41">
+        <f>D76*(1+Assumptions!$D$112)</f>
+        <v/>
+      </c>
+      <c r="F76" s="41">
+        <f>E76*(1+Assumptions!$E$112)</f>
+        <v/>
+      </c>
+      <c r="G76" s="41">
+        <f>F76*(1+Assumptions!$F$112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Total tonnes (mn)</t>
+        </is>
+      </c>
+      <c r="C77" s="41">
+        <f>C74+C75+C76</f>
+        <v/>
+      </c>
+      <c r="D77" s="41">
+        <f>D74+D75+D76</f>
+        <v/>
+      </c>
+      <c r="E77" s="41">
+        <f>E74+E75+E76</f>
+        <v/>
+      </c>
+      <c r="F77" s="41">
+        <f>F74+F75+F76</f>
+        <v/>
+      </c>
+      <c r="G77" s="41">
+        <f>G74+G75+G76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Feedstock intake (mn tonnes)</t>
+        </is>
+      </c>
+      <c r="C78" s="41">
+        <f>C77/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="D78" s="41">
+        <f>D77/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="E78" s="41">
+        <f>E77/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="F78" s="41">
+        <f>F77/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="G78" s="41">
+        <f>G77/(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Brent deck (USD / bbl)</t>
+        </is>
+      </c>
+      <c r="C79" s="23">
+        <f>Assumptions!$C$59</f>
+        <v/>
+      </c>
+      <c r="D79" s="23">
+        <f>Assumptions!$C$60</f>
+        <v/>
+      </c>
+      <c r="E79" s="23">
+        <f>Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="F79" s="23">
+        <f>Assumptions!$C$62</f>
+        <v/>
+      </c>
+      <c r="G79" s="23">
+        <f>Assumptions!$C$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Crude parity, carrying the base-year realisation premium (USD / tonne)</t>
+        </is>
+      </c>
+      <c r="C80" s="17">
+        <f>C79*Assumptions!$C$39*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="D80" s="17">
+        <f>D79*Assumptions!$C$39*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="E80" s="17">
+        <f>E79*Assumptions!$C$39*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="F80" s="17">
+        <f>F79*Assumptions!$C$39*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="G80" s="17">
+        <f>G79*Assumptions!$C$39*Assumptions!$C$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>USD/EGP average</t>
+        </is>
+      </c>
+      <c r="C81" s="23">
+        <f>Assumptions!$B$107</f>
+        <v/>
+      </c>
+      <c r="D81" s="23">
+        <f>Assumptions!$C$107</f>
+        <v/>
+      </c>
+      <c r="E81" s="23">
+        <f>Assumptions!$D$107</f>
+        <v/>
+      </c>
+      <c r="F81" s="23">
+        <f>Assumptions!$E$107</f>
+        <v/>
+      </c>
+      <c r="G81" s="23">
+        <f>Assumptions!$F$107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Base oils — revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C82" s="17">
+        <f>C74*C80*$B$30*C81</f>
+        <v/>
+      </c>
+      <c r="D82" s="17">
+        <f>D74*D80*$B$30*D81</f>
+        <v/>
+      </c>
+      <c r="E82" s="17">
+        <f>E74*E80*$B$30*E81</f>
+        <v/>
+      </c>
+      <c r="F82" s="17">
+        <f>F74*F80*$B$30*F81</f>
+        <v/>
+      </c>
+      <c r="G82" s="17">
+        <f>G74*G80*$B$30*G81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Paraffin wax — revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C83" s="17">
+        <f>C75*C80*$B$31*C81</f>
+        <v/>
+      </c>
+      <c r="D83" s="17">
+        <f>D75*D80*$B$31*D81</f>
+        <v/>
+      </c>
+      <c r="E83" s="17">
+        <f>E75*E80*$B$31*E81</f>
+        <v/>
+      </c>
+      <c r="F83" s="17">
+        <f>F75*F80*$B$31*F81</f>
+        <v/>
+      </c>
+      <c r="G83" s="17">
+        <f>G75*G80*$B$31*G81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>Fuel and by-products — revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C84" s="17">
+        <f>C76*C80*$B$32*C81</f>
+        <v/>
+      </c>
+      <c r="D84" s="17">
+        <f>D76*D80*$B$32*D81</f>
+        <v/>
+      </c>
+      <c r="E84" s="17">
+        <f>E76*E80*$B$32*E81</f>
+        <v/>
+      </c>
+      <c r="F84" s="17">
+        <f>F76*F80*$B$32*F81</f>
+        <v/>
+      </c>
+      <c r="G84" s="17">
+        <f>G76*G80*$B$32*G81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C85" s="35">
+        <f>C82+C83+C84</f>
+        <v/>
+      </c>
+      <c r="D85" s="35">
+        <f>D82+D83+D84</f>
+        <v/>
+      </c>
+      <c r="E85" s="35">
+        <f>E82+E83+E84</f>
+        <v/>
+      </c>
+      <c r="F85" s="35">
+        <f>F82+F83+F84</f>
+        <v/>
+      </c>
+      <c r="G85" s="35">
+        <f>G82+G83+G84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>Specialty share of revenue</t>
+        </is>
+      </c>
+      <c r="C86" s="16">
+        <f>(C82+C83)/C85</f>
+        <v/>
+      </c>
+      <c r="D86" s="16">
+        <f>(D82+D83)/D85</f>
+        <v/>
+      </c>
+      <c r="E86" s="16">
+        <f>(E82+E83)/E85</f>
+        <v/>
+      </c>
+      <c r="F86" s="16">
+        <f>(F82+F83)/F85</f>
+        <v/>
+      </c>
+      <c r="G86" s="16">
+        <f>(G82+G83)/G85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Feedstock cost (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C87" s="17">
+        <f>C78*C80*$B$47*C81</f>
+        <v/>
+      </c>
+      <c r="D87" s="17">
+        <f>D78*D80*$B$47*D81</f>
+        <v/>
+      </c>
+      <c r="E87" s="17">
+        <f>E78*E80*$B$47*E81</f>
+        <v/>
+      </c>
+      <c r="F87" s="17">
+        <f>F78*F80*$B$47*F81</f>
+        <v/>
+      </c>
+      <c r="G87" s="17">
+        <f>G78*G80*$B$47*G81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Energy and utilities (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C88" s="17">
+        <f>C78*Assumptions!$C$40*C81</f>
+        <v/>
+      </c>
+      <c r="D88" s="17">
+        <f>D78*Assumptions!$C$40*D81</f>
+        <v/>
+      </c>
+      <c r="E88" s="17">
+        <f>E78*Assumptions!$C$40*E81</f>
+        <v/>
+      </c>
+      <c r="F88" s="17">
+        <f>F78*Assumptions!$C$40*F81</f>
+        <v/>
+      </c>
+      <c r="G88" s="17">
+        <f>G78*Assumptions!$C$40*G81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Chemicals, solvent and catalyst (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C89" s="17">
+        <f>(C74*Assumptions!$C$41+C75*Assumptions!$C$42+C76*Assumptions!$C$43)*C81</f>
+        <v/>
+      </c>
+      <c r="D89" s="17">
+        <f>(D74*Assumptions!$C$41+D75*Assumptions!$C$42+D76*Assumptions!$C$43)*D81</f>
+        <v/>
+      </c>
+      <c r="E89" s="17">
+        <f>(E74*Assumptions!$C$41+E75*Assumptions!$C$42+E76*Assumptions!$C$43)*E81</f>
+        <v/>
+      </c>
+      <c r="F89" s="17">
+        <f>(F74*Assumptions!$C$41+F75*Assumptions!$C$42+F76*Assumptions!$C$43)*F81</f>
+        <v/>
+      </c>
+      <c r="G89" s="17">
+        <f>(G74*Assumptions!$C$41+G75*Assumptions!$C$42+G76*Assumptions!$C$43)*G81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Fixed conversion (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C90" s="17">
+        <f>Assumptions!$C$44*Assumptions!$C$45*Assumptions!$C$46*Assumptions!$C$47*Assumptions!$C$48</f>
+        <v/>
+      </c>
+      <c r="D90" s="17">
+        <f>C90*Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="E90" s="17">
+        <f>D90*Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="F90" s="17">
+        <f>E90*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="G90" s="17">
+        <f>F90*Assumptions!$C$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>COST OF SALES (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C91" s="35">
+        <f>C87+C88+C89+C90</f>
+        <v/>
+      </c>
+      <c r="D91" s="35">
+        <f>D87+D88+D89+D90</f>
+        <v/>
+      </c>
+      <c r="E91" s="35">
+        <f>E87+E88+E89+E90</f>
+        <v/>
+      </c>
+      <c r="F91" s="35">
+        <f>F87+F88+F89+F90</f>
+        <v/>
+      </c>
+      <c r="G91" s="35">
+        <f>G87+G88+G89+G90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>GROSS PROFIT (EGP mn) — revenue less the built cost</t>
+        </is>
+      </c>
+      <c r="C92" s="35">
+        <f>C85-C91</f>
+        <v/>
+      </c>
+      <c r="D92" s="35">
+        <f>D85-D91</f>
+        <v/>
+      </c>
+      <c r="E92" s="35">
+        <f>E85-E91</f>
+        <v/>
+      </c>
+      <c r="F92" s="35">
+        <f>F85-F91</f>
+        <v/>
+      </c>
+      <c r="G92" s="35">
+        <f>G85-G91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>BLENDED GROSS MARGIN — an OUTPUT of the cost build</t>
+        </is>
+      </c>
+      <c r="C93" s="45">
+        <f>C92/C85</f>
+        <v/>
+      </c>
+      <c r="D93" s="45">
+        <f>D92/D85</f>
+        <v/>
+      </c>
+      <c r="E93" s="45">
+        <f>E92/E85</f>
+        <v/>
+      </c>
+      <c r="F93" s="45">
+        <f>F92/F85</f>
+        <v/>
+      </c>
+      <c r="G93" s="45">
+        <f>G92/G85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>MARGIN BY LINE — the finding the old model could not produce</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="6" t="n"/>
+      <c r="G95" s="6" t="n"/>
+      <c r="H95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr"/>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Feedstock + energy per tonne of PRODUCT (USD)</t>
+        </is>
+      </c>
+      <c r="C97" s="17">
+        <f>(C87+C88)/C81/C77</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>(D87+D88)/D81/D77</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>(E87+E88)/E81/E77</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>(F87+F88)/F81/F77</f>
+        <v/>
+      </c>
+      <c r="G97" s="17">
+        <f>(G87+G88)/G81/G77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Fixed conversion per WEIGHTED tonne (USD)</t>
+        </is>
+      </c>
+      <c r="C98" s="37">
+        <f>C90/C81/(C74*Assumptions!$C$53+C75*Assumptions!$C$53+C76)</f>
+        <v/>
+      </c>
+      <c r="D98" s="37">
+        <f>D90/D81/(D74*Assumptions!$C$53+D75*Assumptions!$C$53+D76)</f>
+        <v/>
+      </c>
+      <c r="E98" s="37">
+        <f>E90/E81/(E74*Assumptions!$C$53+E75*Assumptions!$C$53+E76)</f>
+        <v/>
+      </c>
+      <c r="F98" s="37">
+        <f>F90/F81/(F74*Assumptions!$C$53+F75*Assumptions!$C$53+F76)</f>
+        <v/>
+      </c>
+      <c r="G98" s="37">
+        <f>G90/G81/(G74*Assumptions!$C$53+G75*Assumptions!$C$53+G76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>Base oils — GROSS MARGIN (output)</t>
+        </is>
+      </c>
+      <c r="C99" s="45">
+        <f>(C80*$B$30-C97-Assumptions!$C$41-C98*Assumptions!$C$53)/(C80*$B$30)</f>
+        <v/>
+      </c>
+      <c r="D99" s="45">
+        <f>(D80*$B$30-D97-Assumptions!$C$41-D98*Assumptions!$C$53)/(D80*$B$30)</f>
+        <v/>
+      </c>
+      <c r="E99" s="45">
+        <f>(E80*$B$30-E97-Assumptions!$C$41-E98*Assumptions!$C$53)/(E80*$B$30)</f>
+        <v/>
+      </c>
+      <c r="F99" s="45">
+        <f>(F80*$B$30-F97-Assumptions!$C$41-F98*Assumptions!$C$53)/(F80*$B$30)</f>
+        <v/>
+      </c>
+      <c r="G99" s="45">
+        <f>(G80*$B$30-G97-Assumptions!$C$41-G98*Assumptions!$C$53)/(G80*$B$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>Paraffin wax — GROSS MARGIN (output)</t>
+        </is>
+      </c>
+      <c r="C100" s="45">
+        <f>(C80*$B$31-C97-Assumptions!$C$42-C98*Assumptions!$C$53)/(C80*$B$31)</f>
+        <v/>
+      </c>
+      <c r="D100" s="45">
+        <f>(D80*$B$31-D97-Assumptions!$C$42-D98*Assumptions!$C$53)/(D80*$B$31)</f>
+        <v/>
+      </c>
+      <c r="E100" s="45">
+        <f>(E80*$B$31-E97-Assumptions!$C$42-E98*Assumptions!$C$53)/(E80*$B$31)</f>
+        <v/>
+      </c>
+      <c r="F100" s="45">
+        <f>(F80*$B$31-F97-Assumptions!$C$42-F98*Assumptions!$C$53)/(F80*$B$31)</f>
+        <v/>
+      </c>
+      <c r="G100" s="45">
+        <f>(G80*$B$31-G97-Assumptions!$C$42-G98*Assumptions!$C$53)/(G80*$B$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>Fuel and by-products — GROSS MARGIN (output)</t>
+        </is>
+      </c>
+      <c r="C101" s="45">
+        <f>(C80*$B$32-C97-Assumptions!$C$43-C98*1)/(C80*$B$32)</f>
+        <v/>
+      </c>
+      <c r="D101" s="45">
+        <f>(D80*$B$32-D97-Assumptions!$C$43-D98*1)/(D80*$B$32)</f>
+        <v/>
+      </c>
+      <c r="E101" s="45">
+        <f>(E80*$B$32-E97-Assumptions!$C$43-E98*1)/(E80*$B$32)</f>
+        <v/>
+      </c>
+      <c r="F101" s="45">
+        <f>(F80*$B$32-F97-Assumptions!$C$43-F98*1)/(F80*$B$32)</f>
+        <v/>
+      </c>
+      <c r="G101" s="45">
+        <f>(G80*$B$32-G97-Assumptions!$C$43-G98*1)/(G80*$B$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>Read the fuel row before anything else on this sheet. The specialty lines earn tens of per cent and the fuel and by-product slate runs at or below break-even, because it sells at crude parity and the feedstock costs almost as much as the product fetches. The previous edition ASSUMED the specialty slate earned 3.5x the fuel slate, which put them at roughly 14% against 4%. The build says the gap is far wider than that and that essentially all of this company's gross profit is made on about a seventh of its tonnage. Nothing here was fitted to produce that result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
           <t>Calendar-2025 profit after tax, same halves construction</t>
         </is>
       </c>
-      <c r="B56" s="17">
+      <c r="B105" s="17">
         <f>(Assumptions!$C$19-Assumptions!$C$21)+Assumptions!$C$23</f>
         <v/>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="21" t="inlineStr">
-        <is>
-          <t>The blended margin widens across the forecast ONLY because the specialty share of revenue rises against two fixed leg margins. Neither leg margin improves. That is what "the margin widens on mix" has to mean if it is to mean anything, and it is now a property of the arithmetic on this sheet rather than a caption on a chart.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9376,7 +10603,7 @@
         </is>
       </c>
       <c r="B6" s="19">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -9397,7 +10624,7 @@
           <t>Year-2 discount factor</t>
         </is>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="46">
         <f>DCF!C19</f>
         <v/>
       </c>
@@ -9442,7 +10669,7 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>(B9+B10)*(1-Assumptions!$C$70)/Assumptions!$C$6-B11/Assumptions!$C$6</f>
+        <f>(B9+B10)*(1-Assumptions!$C$95)/Assumptions!$C$6-B11/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -9452,7 +10679,7 @@
           <t>Trailing enterprise value / EBITDA (company)</t>
         </is>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="47">
         <f>(Assumptions!$C$5*Assumptions!$C$6+DCF!$B$49)/'Income Statement'!E9</f>
         <v/>
       </c>
@@ -9463,7 +10690,7 @@
           <t>Trailing price / earnings (company)</t>
         </is>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="47">
         <f>Assumptions!$C$5/'Income Statement'!E20</f>
         <v/>
       </c>
@@ -9532,7 +10759,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>(B19+B20)*(1-Assumptions!$C$61)*(1-Assumptions!$C$70)</f>
+        <f>(B19+B20)*(1-Assumptions!$C$86)*(1-Assumptions!$C$95)</f>
         <v/>
       </c>
     </row>
@@ -9554,7 +10781,7 @@
         </is>
       </c>
       <c r="B23" s="19">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
     </row>
@@ -9600,7 +10827,7 @@
         </is>
       </c>
       <c r="B28" s="9">
-        <f>Assumptions!$C$76</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
     </row>
@@ -9622,7 +10849,7 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>Assumptions!$C$66</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -9632,7 +10859,7 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="B31" s="46">
+      <c r="B31" s="47">
         <f>(B28-B30)/(B29-B30)</f>
         <v/>
       </c>
@@ -9753,23 +10980,23 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>'Product Lines'!$C$50</f>
+        <f>'Product Lines'!$C$85</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>'Product Lines'!$D$50</f>
+        <f>'Product Lines'!$D$85</f>
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>'Product Lines'!$E$50</f>
+        <f>'Product Lines'!$E$85</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>'Product Lines'!$F$50</f>
+        <f>'Product Lines'!$F$85</f>
         <v/>
       </c>
       <c r="F5" s="18">
-        <f>'Product Lines'!$G$50</f>
+        <f>'Product Lines'!$G$85</f>
         <v/>
       </c>
     </row>
@@ -9780,23 +11007,23 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>'Product Lines'!$C$53</f>
+        <f>'Product Lines'!$C$93</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>'Product Lines'!$D$53</f>
+        <f>'Product Lines'!$D$93</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>'Product Lines'!$E$53</f>
+        <f>'Product Lines'!$E$93</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>'Product Lines'!$F$53</f>
+        <f>'Product Lines'!$F$93</f>
         <v/>
       </c>
       <c r="F6" s="10">
-        <f>'Product Lines'!$G$53</f>
+        <f>'Product Lines'!$G$93</f>
         <v/>
       </c>
     </row>
@@ -9807,23 +11034,23 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>'Product Lines'!$C$52</f>
+        <f>'Product Lines'!$C$92</f>
         <v/>
       </c>
       <c r="C7" s="18">
-        <f>'Product Lines'!$D$52</f>
+        <f>'Product Lines'!$D$92</f>
         <v/>
       </c>
       <c r="D7" s="18">
-        <f>'Product Lines'!$E$52</f>
+        <f>'Product Lines'!$E$92</f>
         <v/>
       </c>
       <c r="E7" s="18">
-        <f>'Product Lines'!$F$52</f>
+        <f>'Product Lines'!$F$92</f>
         <v/>
       </c>
       <c r="F7" s="18">
-        <f>'Product Lines'!$G$52</f>
+        <f>'Product Lines'!$G$92</f>
         <v/>
       </c>
     </row>
@@ -9834,23 +11061,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B5*Assumptions!$B$84</f>
+        <f>B5*Assumptions!$B$109</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C5*Assumptions!$C$84</f>
+        <f>C5*Assumptions!$C$109</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D5*Assumptions!$D$84</f>
+        <f>D5*Assumptions!$D$109</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E5*Assumptions!$E$84</f>
+        <f>E5*Assumptions!$E$109</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>F5*Assumptions!$F$84</f>
+        <f>F5*Assumptions!$F$109</f>
         <v/>
       </c>
     </row>
@@ -9860,23 +11087,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="35">
         <f>B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="35">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="35">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="35">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="35">
         <f>F7-F8</f>
         <v/>
       </c>
@@ -9915,23 +11142,23 @@
         </is>
       </c>
       <c r="B11" s="17">
-        <f>B5*Assumptions!$C$69</f>
+        <f>B5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>C5*Assumptions!$C$69</f>
+        <f>C5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>D5*Assumptions!$C$69</f>
+        <f>D5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>E5*Assumptions!$C$69</f>
+        <f>E5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>F5*Assumptions!$C$69</f>
+        <f>F5*Assumptions!$C$94</f>
         <v/>
       </c>
     </row>
@@ -9941,23 +11168,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="35">
         <f>B9-B11</f>
         <v/>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="35">
         <f>C9-C11</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="35">
         <f>D9-D11</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="35">
         <f>E9-E11</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="35">
         <f>F9-F11</f>
         <v/>
       </c>
@@ -9969,23 +11196,23 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>B12*(1-Assumptions!$C$61)</f>
+        <f>B12*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>C12*(1-Assumptions!$C$61)</f>
+        <f>C12*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>D12*(1-Assumptions!$C$61)</f>
+        <f>D12*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>E12*(1-Assumptions!$C$61)</f>
+        <f>E12*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>F12*(1-Assumptions!$C$61)</f>
+        <f>F12*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
     </row>
@@ -10023,23 +11250,23 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>B5*Assumptions!$B$83</f>
+        <f>B5*Assumptions!$B$108</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>C5*Assumptions!$C$83</f>
+        <f>C5*Assumptions!$C$108</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>D5*Assumptions!$D$83</f>
+        <f>D5*Assumptions!$D$108</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>E5*Assumptions!$E$83</f>
+        <f>E5*Assumptions!$E$108</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>F5*Assumptions!$F$83</f>
+        <f>F5*Assumptions!$F$108</f>
         <v/>
       </c>
     </row>
@@ -10103,23 +11330,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="35">
         <f>B13+B11-B15-B17</f>
         <v/>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="35">
         <f>C13+C11-C15-C17</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="35">
         <f>D13+D11-D15-D17</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="35">
         <f>E13+E11-E15-E17</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="35">
         <f>F13+F11-F15-F17</f>
         <v/>
       </c>
@@ -10157,23 +11384,23 @@
           <t>PRESENT VALUE OF FREE CASH FLOW</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="35">
         <f>B18*B19</f>
         <v/>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="35">
         <f>C18*C19</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="35">
         <f>D18*D19</f>
         <v/>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="35">
         <f>E18*E19</f>
         <v/>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="35">
         <f>F18*F19</f>
         <v/>
       </c>
@@ -10280,7 +11507,7 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>Assumptions!$C$66</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -10323,7 +11550,7 @@
           <t>TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="35">
         <f>B29*(1-B28)/(B62-B26)</f>
         <v/>
       </c>
@@ -10381,7 +11608,7 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B36" s="33">
+      <c r="B36" s="35">
         <f>B33+B34</f>
         <v/>
       </c>
@@ -10392,7 +11619,7 @@
           <t>Fair value per share (from the bridge)</t>
         </is>
       </c>
-      <c r="B37" s="47">
+      <c r="B37" s="48">
         <f>'EV Bridge'!$B$12</f>
         <v/>
       </c>
@@ -10425,7 +11652,7 @@
         </is>
       </c>
       <c r="B41" s="10">
-        <f>Assumptions!$C$55</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -10436,7 +11663,7 @@
         </is>
       </c>
       <c r="B42" s="10">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -10446,7 +11673,7 @@
           <t>Risk-free net of sovereign risk</t>
         </is>
       </c>
-      <c r="B43" s="43">
+      <c r="B43" s="34">
         <f>B41-B42</f>
         <v/>
       </c>
@@ -10457,8 +11684,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B44" s="48">
-        <f>Assumptions!$C$58</f>
+      <c r="B44" s="49">
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -10469,7 +11696,7 @@
         </is>
       </c>
       <c r="B45" s="10">
-        <f>Assumptions!$C$57</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -10479,7 +11706,7 @@
           <t>Cost of equity</t>
         </is>
       </c>
-      <c r="B46" s="44">
+      <c r="B46" s="45">
         <f>B43+B44*B45</f>
         <v/>
       </c>
@@ -10491,7 +11718,7 @@
         </is>
       </c>
       <c r="B47" s="23">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -10502,7 +11729,7 @@
         </is>
       </c>
       <c r="B48" s="18">
-        <f>Assumptions!$C$45</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -10556,8 +11783,8 @@
           <t>After-tax cost of net debt</t>
         </is>
       </c>
-      <c r="B53" s="43">
-        <f>(Assumptions!$C$59*B47-Assumptions!$C$60*B48)/(B47-B48)*(1-Assumptions!$C$61)</f>
+      <c r="B53" s="34">
+        <f>(Assumptions!$C$84*B47-Assumptions!$C$85*B48)/(B47-B48)*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
     </row>
@@ -10567,7 +11794,7 @@
           <t>WEIGHTED COST OF CAPITAL — EXPLICIT</t>
         </is>
       </c>
-      <c r="B54" s="44">
+      <c r="B54" s="45">
         <f>B52*B46+B51*B53</f>
         <v/>
       </c>
@@ -10593,7 +11820,7 @@
         </is>
       </c>
       <c r="B57" s="10">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
     </row>
@@ -10604,7 +11831,7 @@
         </is>
       </c>
       <c r="B58" s="10">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$88</f>
         <v/>
       </c>
     </row>
@@ -10614,7 +11841,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="B59" s="43">
+      <c r="B59" s="34">
         <f>B57+B44*B58</f>
         <v/>
       </c>
@@ -10625,8 +11852,8 @@
           <t>Terminal after-tax cost of debt</t>
         </is>
       </c>
-      <c r="B60" s="43">
-        <f>Assumptions!$C$64*(1-Assumptions!$C$61)</f>
+      <c r="B60" s="34">
+        <f>Assumptions!$C$89*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
     </row>
@@ -10637,7 +11864,7 @@
         </is>
       </c>
       <c r="B61" s="9">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -10647,7 +11874,7 @@
           <t>WEIGHTED COST OF CAPITAL — TERMINAL</t>
         </is>
       </c>
-      <c r="B62" s="44">
+      <c r="B62" s="45">
         <f>(1-B61)*B59+B61*B60</f>
         <v/>
       </c>
@@ -10701,23 +11928,23 @@
         </is>
       </c>
       <c r="B66" s="10">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$106</f>
         <v/>
       </c>
       <c r="C66" s="10">
-        <f>Assumptions!$C$81</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
       <c r="D66" s="10">
-        <f>Assumptions!$D$81</f>
+        <f>Assumptions!$D$106</f>
         <v/>
       </c>
       <c r="E66" s="10">
-        <f>Assumptions!$E$81</f>
+        <f>Assumptions!$E$106</f>
         <v/>
       </c>
       <c r="F66" s="10">
-        <f>Assumptions!$F$81</f>
+        <f>Assumptions!$F$106</f>
         <v/>
       </c>
     </row>
@@ -10727,23 +11954,23 @@
           <t>Cumulative progress (glide fraction)</t>
         </is>
       </c>
-      <c r="B67" s="49">
+      <c r="B67" s="43">
         <f>(B66-B66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="C67" s="49">
+      <c r="C67" s="43">
         <f>(B66-C66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="D67" s="49">
+      <c r="D67" s="43">
         <f>(B66-D66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="E67" s="49">
+      <c r="E67" s="43">
         <f>(B66-E66)/(B66-F66)</f>
         <v/>
       </c>
-      <c r="F67" s="49">
+      <c r="F67" s="43">
         <f>(B66-F66)/(B66-F66)</f>
         <v/>
       </c>
@@ -10754,23 +11981,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B68" s="44">
+      <c r="B68" s="45">
         <f>$B$54-($B$54-$B$62)*B67</f>
         <v/>
       </c>
-      <c r="C68" s="44">
+      <c r="C68" s="45">
         <f>$B$54-($B$54-$B$62)*C67</f>
         <v/>
       </c>
-      <c r="D68" s="44">
+      <c r="D68" s="45">
         <f>$B$54-($B$54-$B$62)*D67</f>
         <v/>
       </c>
-      <c r="E68" s="44">
+      <c r="E68" s="45">
         <f>$B$54-($B$54-$B$62)*E67</f>
         <v/>
       </c>
-      <c r="F68" s="44">
+      <c r="F68" s="45">
         <f>$B$54-($B$54-$B$62)*F67</f>
         <v/>
       </c>
@@ -10928,7 +12155,7 @@
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>'Product Lines'!E26</f>
+        <f>'Product Lines'!E25</f>
         <v/>
       </c>
       <c r="F5" s="18">
@@ -10959,19 +12186,19 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>Assumptions!$B$95</f>
+        <f>Assumptions!$B$117</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$117</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>Assumptions!$D$95</f>
+        <f>Assumptions!$D$117</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>Assumptions!$E$95</f>
+        <f>Assumptions!$E$117</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -11045,19 +12272,19 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B5*Assumptions!$C$51</f>
+        <f>B5*Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C5*Assumptions!$C$51</f>
+        <f>C5*Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D5*Assumptions!$C$51</f>
+        <f>D5*Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E5*Assumptions!$C$51</f>
+        <f>E5*Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="F8" s="18">
@@ -11087,39 +12314,39 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="35">
         <f>B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="35">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="35">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="35">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="35">
         <f>F7-F8</f>
         <v/>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="35">
         <f>G7-G8</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="35">
         <f>H7-H8</f>
         <v/>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="35">
         <f>I7-I8</f>
         <v/>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="35">
         <f>J7-J8</f>
         <v/>
       </c>
@@ -11174,19 +12401,19 @@
         </is>
       </c>
       <c r="B11" s="17">
-        <f>B5*Assumptions!$C$69</f>
+        <f>B5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>C5*Assumptions!$C$69</f>
+        <f>C5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>D5*Assumptions!$C$69</f>
+        <f>D5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>E5*Assumptions!$C$69</f>
+        <f>E5*Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="F11" s="18">
@@ -11216,39 +12443,39 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="35">
         <f>B9-B11</f>
         <v/>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="35">
         <f>C9-C11</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="35">
         <f>D9-D11</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="35">
         <f>E9-E11</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="35">
         <f>F9-F11</f>
         <v/>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="35">
         <f>G9-G11</f>
         <v/>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="35">
         <f>H9-H11</f>
         <v/>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="35">
         <f>I9-I11</f>
         <v/>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="35">
         <f>J9-J11</f>
         <v/>
       </c>
@@ -11272,7 +12499,7 @@
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>Assumptions!$C$60*Assumptions!$C$45-Assumptions!$C$59*Assumptions!$C$46</f>
+        <f>Assumptions!$C$85*Assumptions!$C$70-Assumptions!$C$84*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F13" s="18">
@@ -11302,40 +12529,40 @@
           <t>Profit after tax (disclosed for history)</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="35">
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="35">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="35">
         <f>Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="E14" s="33">
-        <f>'Product Lines'!B56</f>
-        <v/>
-      </c>
-      <c r="F14" s="33">
-        <f>(F12+F13)*(1-Assumptions!$C$61)</f>
-        <v/>
-      </c>
-      <c r="G14" s="33">
-        <f>(G12+G13)*(1-Assumptions!$C$61)</f>
-        <v/>
-      </c>
-      <c r="H14" s="33">
-        <f>(H12+H13)*(1-Assumptions!$C$61)</f>
-        <v/>
-      </c>
-      <c r="I14" s="33">
-        <f>(I12+I13)*(1-Assumptions!$C$61)</f>
-        <v/>
-      </c>
-      <c r="J14" s="33">
-        <f>(J12+J13)*(1-Assumptions!$C$61)</f>
+      <c r="E14" s="35">
+        <f>'Product Lines'!B105</f>
+        <v/>
+      </c>
+      <c r="F14" s="35">
+        <f>(F12+F13)*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="G14" s="35">
+        <f>(G12+G13)*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="H14" s="35">
+        <f>(H12+H13)*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="I14" s="35">
+        <f>(I12+I13)*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="J14" s="35">
+        <f>(J12+J13)*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
     </row>
@@ -11346,39 +12573,39 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>B14/(1-Assumptions!$C$61)</f>
+        <f>B14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>C14/(1-Assumptions!$C$61)</f>
+        <f>C14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>D14/(1-Assumptions!$C$61)</f>
+        <f>D14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>E14/(1-Assumptions!$C$61)</f>
+        <f>E14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>F14/(1-Assumptions!$C$61)</f>
+        <f>F14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="G15" s="17">
-        <f>G14/(1-Assumptions!$C$61)</f>
+        <f>G14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>H14/(1-Assumptions!$C$61)</f>
+        <f>H14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>I14/(1-Assumptions!$C$61)</f>
+        <f>I14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>J14/(1-Assumptions!$C$61)</f>
+        <f>J14/(1-Assumptions!$C$86)</f>
         <v/>
       </c>
     </row>
@@ -11475,39 +12702,39 @@
         </is>
       </c>
       <c r="B18" s="17">
-        <f>B14*Assumptions!$C$70</f>
+        <f>B14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>C14*Assumptions!$C$70</f>
+        <f>C14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>D14*Assumptions!$C$70</f>
+        <f>D14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>E14*Assumptions!$C$70</f>
+        <f>E14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>F14*Assumptions!$C$70</f>
+        <f>F14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>G14*Assumptions!$C$70</f>
+        <f>G14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>H14*Assumptions!$C$70</f>
+        <f>H14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="I18" s="17">
-        <f>I14*Assumptions!$C$70</f>
+        <f>I14*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>J14*Assumptions!$C$70</f>
+        <f>J14*Assumptions!$C$95</f>
         <v/>
       </c>
     </row>
@@ -11517,39 +12744,39 @@
           <t>PROFIT ATTRIBUTABLE TO SHAREHOLDERS</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="35">
         <f>B14-B18</f>
         <v/>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="35">
         <f>C14-C18</f>
         <v/>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="35">
         <f>D14-D18</f>
         <v/>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="35">
         <f>E14-E18</f>
         <v/>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="35">
         <f>F14-F18</f>
         <v/>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="35">
         <f>G14-G18</f>
         <v/>
       </c>
-      <c r="H19" s="33">
+      <c r="H19" s="35">
         <f>H14-H18</f>
         <v/>
       </c>
-      <c r="I19" s="33">
+      <c r="I19" s="35">
         <f>I14-I18</f>
         <v/>
       </c>
-      <c r="J19" s="33">
+      <c r="J19" s="35">
         <f>J14-J18</f>
         <v/>
       </c>
